--- a/research/traditional_assets/database/data/saudi_arabia/saudi_arabia_household_products.xlsx
+++ b/research/traditional_assets/database/data/saudi_arabia/saudi_arabia_household_products.xlsx
@@ -1266,7 +1266,7 @@
 
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:Z101"/>
+  <dimension ref="A1:Z100"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
     <row r="1" s="1" customFormat="1">
@@ -1403,22 +1403,22 @@
     </row>
     <row r="2">
       <c r="A2">
-        <v>0</v>
+        <v>0.01</v>
       </c>
       <c r="B2">
-        <v>0.08051279835877043</v>
+        <v>0.08038777276205289</v>
       </c>
       <c r="C2">
-        <v>210.1052647124143</v>
+        <v>208.7475362806025</v>
       </c>
       <c r="D2">
-        <v>207.7252647124143</v>
+        <v>208.4761362806025</v>
       </c>
       <c r="E2">
-        <v>-7.06</v>
+        <v>-4.9514</v>
       </c>
       <c r="F2">
-        <v>0</v>
+        <v>2.1086</v>
       </c>
       <c r="G2">
         <v>2.38</v>
@@ -1439,28 +1439,28 @@
         <v>9.503</v>
       </c>
       <c r="M2">
-        <v>0</v>
+        <v>0.10606258</v>
       </c>
       <c r="N2">
-        <v>9.503</v>
+        <v>9.39693742</v>
       </c>
       <c r="O2">
-        <v>1.9006</v>
+        <v>1.879387484</v>
       </c>
       <c r="P2">
-        <v>7.6024</v>
+        <v>7.517549936</v>
       </c>
       <c r="Q2">
-        <v>7.9594</v>
+        <v>7.874549936</v>
       </c>
       <c r="R2">
-        <v>0</v>
+        <v>0.0101010101010101</v>
       </c>
       <c r="S2">
-        <v>0.08051279835877043</v>
+        <v>0.08079330582025544</v>
       </c>
       <c r="T2">
-        <v>0.6766170509100436</v>
+        <v>0.6820846634426501</v>
       </c>
       <c r="U2">
         <v>0.0503</v>
@@ -1477,7 +1477,7 @@
         </is>
       </c>
       <c r="Y2">
-        <v>10000000</v>
+        <v>89.5980467380673</v>
       </c>
       <c r="Z2">
         <v>0</v>
@@ -1485,22 +1485,22 @@
     </row>
     <row r="3">
       <c r="A3">
-        <v>0.01</v>
+        <v>0.02</v>
       </c>
       <c r="B3">
-        <v>0.08038777276205289</v>
+        <v>0.08026274716533534</v>
       </c>
       <c r="C3">
-        <v>208.7475362806025</v>
+        <v>207.3952559441164</v>
       </c>
       <c r="D3">
-        <v>208.4761362806025</v>
+        <v>209.2324559441164</v>
       </c>
       <c r="E3">
-        <v>-4.9514</v>
+        <v>-2.8428</v>
       </c>
       <c r="F3">
-        <v>2.1086</v>
+        <v>4.2172</v>
       </c>
       <c r="G3">
         <v>2.38</v>
@@ -1521,28 +1521,28 @@
         <v>9.503</v>
       </c>
       <c r="M3">
-        <v>0.10606258</v>
+        <v>0.21212516</v>
       </c>
       <c r="N3">
-        <v>9.39693742</v>
+        <v>9.290874840000001</v>
       </c>
       <c r="O3">
-        <v>1.879387484</v>
+        <v>1.858174968</v>
       </c>
       <c r="P3">
-        <v>7.517549936</v>
+        <v>7.432699872000001</v>
       </c>
       <c r="Q3">
-        <v>7.874549936</v>
+        <v>7.789699872000001</v>
       </c>
       <c r="R3">
-        <v>0.0101010101010101</v>
+        <v>0.02040816326530612</v>
       </c>
       <c r="S3">
-        <v>0.08079330582025544</v>
+        <v>0.08107953792381158</v>
       </c>
       <c r="T3">
-        <v>0.6820846634426501</v>
+        <v>0.6876638599044933</v>
       </c>
       <c r="U3">
         <v>0.0503</v>
@@ -1559,7 +1559,7 @@
         </is>
       </c>
       <c r="Y3">
-        <v>89.5980467380673</v>
+        <v>44.79902336903365</v>
       </c>
       <c r="Z3">
         <v>0</v>
@@ -1567,22 +1567,22 @@
     </row>
     <row r="4">
       <c r="A4">
-        <v>0.02</v>
+        <v>0.03</v>
       </c>
       <c r="B4">
-        <v>0.08026274716533534</v>
+        <v>0.0801377215686178</v>
       </c>
       <c r="C4">
-        <v>207.3952559441164</v>
+        <v>206.0484832134306</v>
       </c>
       <c r="D4">
-        <v>209.2324559441164</v>
+        <v>209.9942832134305</v>
       </c>
       <c r="E4">
-        <v>-2.8428</v>
+        <v>-0.7341999999999995</v>
       </c>
       <c r="F4">
-        <v>4.2172</v>
+        <v>6.3258</v>
       </c>
       <c r="G4">
         <v>2.38</v>
@@ -1603,28 +1603,28 @@
         <v>9.503</v>
       </c>
       <c r="M4">
-        <v>0.21212516</v>
+        <v>0.31818774</v>
       </c>
       <c r="N4">
-        <v>9.290874840000001</v>
+        <v>9.184812259999999</v>
       </c>
       <c r="O4">
-        <v>1.858174968</v>
+        <v>1.836962452</v>
       </c>
       <c r="P4">
-        <v>7.432699872000001</v>
+        <v>7.347849807999999</v>
       </c>
       <c r="Q4">
-        <v>7.789699872000001</v>
+        <v>7.704849808</v>
       </c>
       <c r="R4">
-        <v>0.02040816326530612</v>
+        <v>0.03092783505154639</v>
       </c>
       <c r="S4">
-        <v>0.08107953792381158</v>
+        <v>0.08137167172022454</v>
       </c>
       <c r="T4">
-        <v>0.6876638599044933</v>
+        <v>0.6933580913449313</v>
       </c>
       <c r="U4">
         <v>0.0503</v>
@@ -1641,7 +1641,7 @@
         </is>
       </c>
       <c r="Y4">
-        <v>44.79902336903365</v>
+        <v>29.86601557935576</v>
       </c>
       <c r="Z4">
         <v>0</v>
@@ -1649,22 +1649,22 @@
     </row>
     <row r="5">
       <c r="A5">
-        <v>0.03</v>
+        <v>0.04</v>
       </c>
       <c r="B5">
-        <v>0.0801377215686178</v>
+        <v>0.08001269597190026</v>
       </c>
       <c r="C5">
-        <v>206.0484832134306</v>
+        <v>204.7072784689109</v>
       </c>
       <c r="D5">
-        <v>209.9942832134305</v>
+        <v>210.761678468911</v>
       </c>
       <c r="E5">
-        <v>-0.7341999999999995</v>
+        <v>1.374400000000001</v>
       </c>
       <c r="F5">
-        <v>6.3258</v>
+        <v>8.4344</v>
       </c>
       <c r="G5">
         <v>2.38</v>
@@ -1685,28 +1685,28 @@
         <v>9.503</v>
       </c>
       <c r="M5">
-        <v>0.31818774</v>
+        <v>0.42425032</v>
       </c>
       <c r="N5">
-        <v>9.184812259999999</v>
+        <v>9.07874968</v>
       </c>
       <c r="O5">
-        <v>1.836962452</v>
+        <v>1.815749936</v>
       </c>
       <c r="P5">
-        <v>7.347849807999999</v>
+        <v>7.262999744</v>
       </c>
       <c r="Q5">
-        <v>7.704849808</v>
+        <v>7.619999744</v>
       </c>
       <c r="R5">
-        <v>0.03092783505154639</v>
+        <v>0.04166666666666667</v>
       </c>
       <c r="S5">
-        <v>0.08137167172022454</v>
+        <v>0.0816698916373961</v>
       </c>
       <c r="T5">
-        <v>0.6933580913449313</v>
+        <v>0.6991709526070452</v>
       </c>
       <c r="U5">
         <v>0.0503</v>
@@ -1723,7 +1723,7 @@
         </is>
       </c>
       <c r="Y5">
-        <v>29.86601557935576</v>
+        <v>22.39951168451682</v>
       </c>
       <c r="Z5">
         <v>0</v>
@@ -1731,22 +1731,22 @@
     </row>
     <row r="6">
       <c r="A6">
-        <v>0.04</v>
+        <v>0.05</v>
       </c>
       <c r="B6">
-        <v>0.08001269597190026</v>
+        <v>0.07988767037518271</v>
       </c>
       <c r="C6">
-        <v>204.7072784689109</v>
+        <v>203.3717029767679</v>
       </c>
       <c r="D6">
-        <v>210.761678468911</v>
+        <v>211.534702976768</v>
       </c>
       <c r="E6">
-        <v>1.374400000000001</v>
+        <v>3.483000000000001</v>
       </c>
       <c r="F6">
-        <v>8.4344</v>
+        <v>10.543</v>
       </c>
       <c r="G6">
         <v>2.38</v>
@@ -1767,28 +1767,28 @@
         <v>9.503</v>
       </c>
       <c r="M6">
-        <v>0.42425032</v>
+        <v>0.5303129</v>
       </c>
       <c r="N6">
-        <v>9.07874968</v>
+        <v>8.9726871</v>
       </c>
       <c r="O6">
-        <v>1.815749936</v>
+        <v>1.79453742</v>
       </c>
       <c r="P6">
-        <v>7.262999744</v>
+        <v>7.17814968</v>
       </c>
       <c r="Q6">
-        <v>7.619999744</v>
+        <v>7.53514968</v>
       </c>
       <c r="R6">
-        <v>0.04166666666666667</v>
+        <v>0.05263157894736843</v>
       </c>
       <c r="S6">
-        <v>0.0816698916373961</v>
+        <v>0.08197438986861338</v>
       </c>
       <c r="T6">
-        <v>0.6991709526070452</v>
+        <v>0.7051061898957296</v>
       </c>
       <c r="U6">
         <v>0.0503</v>
@@ -1805,7 +1805,7 @@
         </is>
       </c>
       <c r="Y6">
-        <v>22.39951168451682</v>
+        <v>17.91960934761346</v>
       </c>
       <c r="Z6">
         <v>0</v>
@@ -1813,22 +1813,22 @@
     </row>
     <row r="7">
       <c r="A7">
-        <v>0.05</v>
+        <v>0.06</v>
       </c>
       <c r="B7">
-        <v>0.07988767037518271</v>
+        <v>0.07976264477846516</v>
       </c>
       <c r="C7">
-        <v>203.3717029767679</v>
+        <v>202.0418189053611</v>
       </c>
       <c r="D7">
-        <v>211.534702976768</v>
+        <v>212.3134189053611</v>
       </c>
       <c r="E7">
-        <v>3.483000000000001</v>
+        <v>5.591600000000002</v>
       </c>
       <c r="F7">
-        <v>10.543</v>
+        <v>12.6516</v>
       </c>
       <c r="G7">
         <v>2.38</v>
@@ -1849,28 +1849,28 @@
         <v>9.503</v>
       </c>
       <c r="M7">
-        <v>0.5303129</v>
+        <v>0.6363754800000001</v>
       </c>
       <c r="N7">
-        <v>8.9726871</v>
+        <v>8.86662452</v>
       </c>
       <c r="O7">
-        <v>1.79453742</v>
+        <v>1.773324904</v>
       </c>
       <c r="P7">
-        <v>7.17814968</v>
+        <v>7.093299616</v>
       </c>
       <c r="Q7">
-        <v>7.53514968</v>
+        <v>7.450299616000001</v>
       </c>
       <c r="R7">
-        <v>0.05263157894736843</v>
+        <v>0.06382978723404256</v>
       </c>
       <c r="S7">
-        <v>0.08197438986861338</v>
+        <v>0.08228536678560125</v>
       </c>
       <c r="T7">
-        <v>0.7051061898957296</v>
+        <v>0.7111677088288544</v>
       </c>
       <c r="U7">
         <v>0.0503</v>
@@ -1887,7 +1887,7 @@
         </is>
       </c>
       <c r="Y7">
-        <v>17.91960934761346</v>
+        <v>14.93300778967788</v>
       </c>
       <c r="Z7">
         <v>0</v>
@@ -1895,22 +1895,22 @@
     </row>
     <row r="8">
       <c r="A8">
-        <v>0.06</v>
+        <v>0.06999999999999999</v>
       </c>
       <c r="B8">
-        <v>0.07976264477846516</v>
+        <v>0.07972161918174765</v>
       </c>
       <c r="C8">
-        <v>202.0418189053611</v>
+        <v>200.1899957017474</v>
       </c>
       <c r="D8">
-        <v>212.3134189053611</v>
+        <v>212.5701957017474</v>
       </c>
       <c r="E8">
-        <v>5.591600000000001</v>
+        <v>7.7002</v>
       </c>
       <c r="F8">
-        <v>12.6516</v>
+        <v>14.7602</v>
       </c>
       <c r="G8">
         <v>2.38</v>
@@ -1931,45 +1931,45 @@
         <v>9.503</v>
       </c>
       <c r="M8">
-        <v>0.63637548</v>
+        <v>0.7645783599999999</v>
       </c>
       <c r="N8">
-        <v>8.86662452</v>
+        <v>8.73842164</v>
       </c>
       <c r="O8">
-        <v>1.773324904</v>
+        <v>1.747684328</v>
       </c>
       <c r="P8">
-        <v>7.093299616</v>
+        <v>6.990737312</v>
       </c>
       <c r="Q8">
-        <v>7.450299616000001</v>
+        <v>7.347737312</v>
       </c>
       <c r="R8">
-        <v>0.06382978723404255</v>
+        <v>0.07526881720430106</v>
       </c>
       <c r="S8">
-        <v>0.08228536678560125</v>
+        <v>0.08260303137822328</v>
       </c>
       <c r="T8">
-        <v>0.7111677088288544</v>
+        <v>0.7173595830078527</v>
       </c>
       <c r="U8">
-        <v>0.0503</v>
+        <v>0.0518</v>
       </c>
       <c r="V8">
         <v>0.2</v>
       </c>
       <c r="W8">
-        <v>0.04024</v>
+        <v>0.04144</v>
       </c>
       <c r="X8" t="inlineStr">
         <is>
-          <t>Aaa/AAA</t>
+          <t>Aa2/AA</t>
         </is>
       </c>
       <c r="Y8">
-        <v>14.93300778967788</v>
+        <v>12.42907267215881</v>
       </c>
       <c r="Z8">
         <v>0</v>
@@ -1977,22 +1977,22 @@
     </row>
     <row r="9">
       <c r="A9">
-        <v>0.07000000000000001</v>
+        <v>0.08</v>
       </c>
       <c r="B9">
-        <v>0.07972161918174764</v>
+        <v>0.07960859358503011</v>
       </c>
       <c r="C9">
-        <v>200.1899957017475</v>
+        <v>198.7920396731723</v>
       </c>
       <c r="D9">
-        <v>212.5701957017475</v>
+        <v>213.2808396731723</v>
       </c>
       <c r="E9">
-        <v>7.700200000000003</v>
+        <v>9.808800000000002</v>
       </c>
       <c r="F9">
-        <v>14.7602</v>
+        <v>16.8688</v>
       </c>
       <c r="G9">
         <v>2.38</v>
@@ -2013,28 +2013,28 @@
         <v>9.503</v>
       </c>
       <c r="M9">
-        <v>0.7645783600000001</v>
+        <v>0.87380384</v>
       </c>
       <c r="N9">
-        <v>8.73842164</v>
+        <v>8.629196159999999</v>
       </c>
       <c r="O9">
-        <v>1.747684328</v>
+        <v>1.725839232</v>
       </c>
       <c r="P9">
-        <v>6.990737312</v>
+        <v>6.903356927999999</v>
       </c>
       <c r="Q9">
-        <v>7.347737312</v>
+        <v>7.260356927999999</v>
       </c>
       <c r="R9">
-        <v>0.07526881720430109</v>
+        <v>0.08695652173913043</v>
       </c>
       <c r="S9">
-        <v>0.08260303137822328</v>
+        <v>0.0829276017228588</v>
       </c>
       <c r="T9">
-        <v>0.7173595830078527</v>
+        <v>0.7236860631472641</v>
       </c>
       <c r="U9">
         <v>0.0518</v>
@@ -2051,7 +2051,7 @@
         </is>
       </c>
       <c r="Y9">
-        <v>12.42907267215881</v>
+        <v>10.87543858813896</v>
       </c>
       <c r="Z9">
         <v>0</v>
@@ -2059,22 +2059,22 @@
     </row>
     <row r="10">
       <c r="A10">
-        <v>0.08</v>
+        <v>0.09</v>
       </c>
       <c r="B10">
-        <v>0.07960859358503011</v>
+        <v>0.07961796798831257</v>
       </c>
       <c r="C10">
-        <v>198.7920396731723</v>
+        <v>196.6243178298904</v>
       </c>
       <c r="D10">
-        <v>213.2808396731723</v>
+        <v>213.2217178298904</v>
       </c>
       <c r="E10">
-        <v>9.808800000000002</v>
+        <v>11.9174</v>
       </c>
       <c r="F10">
-        <v>16.8688</v>
+        <v>18.9774</v>
       </c>
       <c r="G10">
         <v>2.38</v>
@@ -2095,45 +2095,45 @@
         <v>9.503</v>
       </c>
       <c r="M10">
-        <v>0.87380384</v>
+        <v>1.0152909</v>
       </c>
       <c r="N10">
-        <v>8.629196159999999</v>
+        <v>8.4877091</v>
       </c>
       <c r="O10">
-        <v>1.725839232</v>
+        <v>1.69754182</v>
       </c>
       <c r="P10">
-        <v>6.903356927999999</v>
+        <v>6.79016728</v>
       </c>
       <c r="Q10">
-        <v>7.260356927999999</v>
+        <v>7.147167280000001</v>
       </c>
       <c r="R10">
-        <v>0.08695652173913043</v>
+        <v>0.0989010989010989</v>
       </c>
       <c r="S10">
-        <v>0.0829276017228588</v>
+        <v>0.08325930548166216</v>
       </c>
       <c r="T10">
-        <v>0.7236860631472641</v>
+        <v>0.7301515868062229</v>
       </c>
       <c r="U10">
-        <v>0.0518</v>
+        <v>0.0535</v>
       </c>
       <c r="V10">
         <v>0.2</v>
       </c>
       <c r="W10">
-        <v>0.04144</v>
+        <v>0.0428</v>
       </c>
       <c r="X10" t="inlineStr">
         <is>
-          <t>Aa2/AA</t>
+          <t>A1/A+</t>
         </is>
       </c>
       <c r="Y10">
-        <v>10.87543858813896</v>
+        <v>9.359879025804329</v>
       </c>
       <c r="Z10">
         <v>0</v>
@@ -2141,22 +2141,22 @@
     </row>
     <row r="11">
       <c r="A11">
-        <v>0.09</v>
+        <v>0.09999999999999999</v>
       </c>
       <c r="B11">
-        <v>0.07961796798831257</v>
+        <v>0.07951854239159502</v>
       </c>
       <c r="C11">
-        <v>196.6243178298904</v>
+        <v>195.1444430067433</v>
       </c>
       <c r="D11">
-        <v>213.2217178298904</v>
+        <v>213.8504430067433</v>
       </c>
       <c r="E11">
-        <v>11.9174</v>
+        <v>14.026</v>
       </c>
       <c r="F11">
-        <v>18.9774</v>
+        <v>21.086</v>
       </c>
       <c r="G11">
         <v>2.38</v>
@@ -2177,28 +2177,28 @@
         <v>9.503</v>
       </c>
       <c r="M11">
-        <v>1.0152909</v>
+        <v>1.128101</v>
       </c>
       <c r="N11">
-        <v>8.4877091</v>
+        <v>8.374899000000001</v>
       </c>
       <c r="O11">
-        <v>1.69754182</v>
+        <v>1.6749798</v>
       </c>
       <c r="P11">
-        <v>6.79016728</v>
+        <v>6.699919200000001</v>
       </c>
       <c r="Q11">
-        <v>7.147167280000001</v>
+        <v>7.056919200000001</v>
       </c>
       <c r="R11">
-        <v>0.0989010989010989</v>
+        <v>0.1111111111111111</v>
       </c>
       <c r="S11">
-        <v>0.08325930548166216</v>
+        <v>0.08359838043510556</v>
       </c>
       <c r="T11">
-        <v>0.7301515868062229</v>
+        <v>0.7367607887687141</v>
       </c>
       <c r="U11">
         <v>0.0535</v>
@@ -2215,7 +2215,7 @@
         </is>
       </c>
       <c r="Y11">
-        <v>9.359879025804329</v>
+        <v>8.423891123223898</v>
       </c>
       <c r="Z11">
         <v>0</v>
@@ -2223,22 +2223,22 @@
     </row>
     <row r="12">
       <c r="A12">
-        <v>0.1</v>
+        <v>0.11</v>
       </c>
       <c r="B12">
-        <v>0.07951854239159505</v>
+        <v>0.07941911679487748</v>
       </c>
       <c r="C12">
-        <v>195.1444430067431</v>
+        <v>193.6682869830078</v>
       </c>
       <c r="D12">
-        <v>213.8504430067431</v>
+        <v>214.4828869830078</v>
       </c>
       <c r="E12">
-        <v>14.026</v>
+        <v>16.1346</v>
       </c>
       <c r="F12">
-        <v>21.086</v>
+        <v>23.1946</v>
       </c>
       <c r="G12">
         <v>2.38</v>
@@ -2259,28 +2259,28 @@
         <v>9.503</v>
       </c>
       <c r="M12">
-        <v>1.128101</v>
+        <v>1.2409111</v>
       </c>
       <c r="N12">
-        <v>8.374898999999999</v>
+        <v>8.2620889</v>
       </c>
       <c r="O12">
-        <v>1.6749798</v>
+        <v>1.65241778</v>
       </c>
       <c r="P12">
-        <v>6.699919199999999</v>
+        <v>6.60967112</v>
       </c>
       <c r="Q12">
-        <v>7.056919199999999</v>
+        <v>6.96667112</v>
       </c>
       <c r="R12">
-        <v>0.1111111111111111</v>
+        <v>0.1235955056179775</v>
       </c>
       <c r="S12">
-        <v>0.08359838043510559</v>
+        <v>0.08394507505042413</v>
       </c>
       <c r="T12">
-        <v>0.7367607887687143</v>
+        <v>0.743518512123621</v>
       </c>
       <c r="U12">
         <v>0.0535</v>
@@ -2297,7 +2297,7 @@
         </is>
       </c>
       <c r="Y12">
-        <v>8.423891123223896</v>
+        <v>7.658082839294451</v>
       </c>
       <c r="Z12">
         <v>0</v>
@@ -2305,22 +2305,22 @@
     </row>
     <row r="13">
       <c r="A13">
-        <v>0.11</v>
+        <v>0.12</v>
       </c>
       <c r="B13">
-        <v>0.07941911679487748</v>
+        <v>0.07939649119815995</v>
       </c>
       <c r="C13">
-        <v>193.6682869830078</v>
+        <v>191.7041307368233</v>
       </c>
       <c r="D13">
-        <v>214.4828869830078</v>
+        <v>214.6273307368233</v>
       </c>
       <c r="E13">
-        <v>16.1346</v>
+        <v>18.2432</v>
       </c>
       <c r="F13">
-        <v>23.1946</v>
+        <v>25.3032</v>
       </c>
       <c r="G13">
         <v>2.38</v>
@@ -2341,45 +2341,45 @@
         <v>9.503</v>
       </c>
       <c r="M13">
-        <v>1.2409111</v>
+        <v>1.37396376</v>
       </c>
       <c r="N13">
-        <v>8.2620889</v>
+        <v>8.12903624</v>
       </c>
       <c r="O13">
-        <v>1.65241778</v>
+        <v>1.625807248</v>
       </c>
       <c r="P13">
-        <v>6.60967112</v>
+        <v>6.503228991999999</v>
       </c>
       <c r="Q13">
-        <v>6.96667112</v>
+        <v>6.860228992</v>
       </c>
       <c r="R13">
-        <v>0.1235955056179775</v>
+        <v>0.1363636363636364</v>
       </c>
       <c r="S13">
-        <v>0.08394507505042413</v>
+        <v>0.08429964908881811</v>
       </c>
       <c r="T13">
-        <v>0.743518512123621</v>
+        <v>0.7504298201002303</v>
       </c>
       <c r="U13">
-        <v>0.0535</v>
+        <v>0.0543</v>
       </c>
       <c r="V13">
         <v>0.2</v>
       </c>
       <c r="W13">
-        <v>0.0428</v>
+        <v>0.04344000000000001</v>
       </c>
       <c r="X13" t="inlineStr">
         <is>
-          <t>A1/A+</t>
+          <t>A2/A</t>
         </is>
       </c>
       <c r="Y13">
-        <v>7.658082839294451</v>
+        <v>6.916485191720048</v>
       </c>
       <c r="Z13">
         <v>0</v>
@@ -2387,22 +2387,22 @@
     </row>
     <row r="14">
       <c r="A14">
-        <v>0.12</v>
+        <v>0.13</v>
       </c>
       <c r="B14">
-        <v>0.07939649119815995</v>
+        <v>0.0793034656014424</v>
       </c>
       <c r="C14">
-        <v>191.7041307368233</v>
+        <v>190.1914641769993</v>
       </c>
       <c r="D14">
-        <v>214.6273307368233</v>
+        <v>215.2232641769994</v>
       </c>
       <c r="E14">
-        <v>18.2432</v>
+        <v>20.3518</v>
       </c>
       <c r="F14">
-        <v>25.3032</v>
+        <v>27.4118</v>
       </c>
       <c r="G14">
         <v>2.38</v>
@@ -2423,28 +2423,28 @@
         <v>9.503</v>
       </c>
       <c r="M14">
-        <v>1.37396376</v>
+        <v>1.48846074</v>
       </c>
       <c r="N14">
-        <v>8.12903624</v>
+        <v>8.014539259999999</v>
       </c>
       <c r="O14">
-        <v>1.625807248</v>
+        <v>1.602907852</v>
       </c>
       <c r="P14">
-        <v>6.503228991999999</v>
+        <v>6.411631408</v>
       </c>
       <c r="Q14">
-        <v>6.860228992</v>
+        <v>6.768631408</v>
       </c>
       <c r="R14">
-        <v>0.1363636363636364</v>
+        <v>0.1494252873563219</v>
       </c>
       <c r="S14">
-        <v>0.08429964908881811</v>
+        <v>0.08466237425453149</v>
       </c>
       <c r="T14">
-        <v>0.7504298201002303</v>
+        <v>0.7575000087199799</v>
       </c>
       <c r="U14">
         <v>0.0543</v>
@@ -2461,7 +2461,7 @@
         </is>
       </c>
       <c r="Y14">
-        <v>6.916485191720048</v>
+        <v>6.384447869280044</v>
       </c>
       <c r="Z14">
         <v>0</v>
@@ -2469,22 +2469,22 @@
     </row>
     <row r="15">
       <c r="A15">
-        <v>0.13</v>
+        <v>0.14</v>
       </c>
       <c r="B15">
-        <v>0.0793034656014424</v>
+        <v>0.07932244000472485</v>
       </c>
       <c r="C15">
-        <v>190.1914641769993</v>
+        <v>187.9610433009031</v>
       </c>
       <c r="D15">
-        <v>215.2232641769994</v>
+        <v>215.1014433009031</v>
       </c>
       <c r="E15">
-        <v>20.3518</v>
+        <v>22.46040000000001</v>
       </c>
       <c r="F15">
-        <v>27.4118</v>
+        <v>29.52040000000001</v>
       </c>
       <c r="G15">
         <v>2.38</v>
@@ -2505,45 +2505,45 @@
         <v>9.503</v>
       </c>
       <c r="M15">
-        <v>1.48846074</v>
+        <v>1.63247812</v>
       </c>
       <c r="N15">
-        <v>8.014539259999999</v>
+        <v>7.87052188</v>
       </c>
       <c r="O15">
-        <v>1.602907852</v>
+        <v>1.574104376</v>
       </c>
       <c r="P15">
-        <v>6.411631408</v>
+        <v>6.296417504</v>
       </c>
       <c r="Q15">
-        <v>6.768631408</v>
+        <v>6.653417504</v>
       </c>
       <c r="R15">
-        <v>0.1494252873563219</v>
+        <v>0.1627906976744186</v>
       </c>
       <c r="S15">
-        <v>0.08466237425453149</v>
+        <v>0.08503353488921495</v>
       </c>
       <c r="T15">
-        <v>0.7575000087199799</v>
+        <v>0.7647346203308866</v>
       </c>
       <c r="U15">
-        <v>0.0543</v>
+        <v>0.0553</v>
       </c>
       <c r="V15">
         <v>0.2</v>
       </c>
       <c r="W15">
-        <v>0.04344000000000001</v>
+        <v>0.04424</v>
       </c>
       <c r="X15" t="inlineStr">
         <is>
-          <t>A2/A</t>
+          <t>A3/A-</t>
         </is>
       </c>
       <c r="Y15">
-        <v>6.384447869280044</v>
+        <v>5.821211251517416</v>
       </c>
       <c r="Z15">
         <v>0</v>
@@ -2551,22 +2551,22 @@
     </row>
     <row r="16">
       <c r="A16">
-        <v>0.14</v>
+        <v>0.15</v>
       </c>
       <c r="B16">
-        <v>0.07932244000472485</v>
+        <v>0.07923741440800731</v>
       </c>
       <c r="C16">
-        <v>187.9610433009031</v>
+        <v>186.3994092937965</v>
       </c>
       <c r="D16">
-        <v>215.1014433009031</v>
+        <v>215.6484092937965</v>
       </c>
       <c r="E16">
-        <v>22.46040000000001</v>
+        <v>24.56900000000001</v>
       </c>
       <c r="F16">
-        <v>29.52040000000001</v>
+        <v>31.62900000000001</v>
       </c>
       <c r="G16">
         <v>2.38</v>
@@ -2587,28 +2587,28 @@
         <v>9.503</v>
       </c>
       <c r="M16">
-        <v>1.63247812</v>
+        <v>1.749083700000001</v>
       </c>
       <c r="N16">
-        <v>7.87052188</v>
+        <v>7.753916299999999</v>
       </c>
       <c r="O16">
-        <v>1.574104376</v>
+        <v>1.55078326</v>
       </c>
       <c r="P16">
-        <v>6.296417504</v>
+        <v>6.203133039999999</v>
       </c>
       <c r="Q16">
-        <v>6.653417504</v>
+        <v>6.560133039999999</v>
       </c>
       <c r="R16">
-        <v>0.1627906976744186</v>
+        <v>0.1764705882352942</v>
       </c>
       <c r="S16">
-        <v>0.08503353488921495</v>
+        <v>0.08541342871530272</v>
       </c>
       <c r="T16">
-        <v>0.7647346203308866</v>
+        <v>0.7721394580973439</v>
       </c>
       <c r="U16">
         <v>0.0553</v>
@@ -2625,7 +2625,7 @@
         </is>
       </c>
       <c r="Y16">
-        <v>5.821211251517416</v>
+        <v>5.433130501416254</v>
       </c>
       <c r="Z16">
         <v>0</v>
@@ -2633,22 +2633,22 @@
     </row>
     <row r="17">
       <c r="A17">
-        <v>0.15</v>
+        <v>0.16</v>
       </c>
       <c r="B17">
-        <v>0.07923741440800731</v>
+        <v>0.07915238881128978</v>
       </c>
       <c r="C17">
-        <v>186.3994092937965</v>
+        <v>184.8405640590439</v>
       </c>
       <c r="D17">
-        <v>215.6484092937965</v>
+        <v>216.1981640590439</v>
       </c>
       <c r="E17">
-        <v>24.569</v>
+        <v>26.6776</v>
       </c>
       <c r="F17">
-        <v>31.629</v>
+        <v>33.7376</v>
       </c>
       <c r="G17">
         <v>2.38</v>
@@ -2669,28 +2669,28 @@
         <v>9.503</v>
       </c>
       <c r="M17">
-        <v>1.7490837</v>
+        <v>1.86568928</v>
       </c>
       <c r="N17">
-        <v>7.7539163</v>
+        <v>7.63731072</v>
       </c>
       <c r="O17">
-        <v>1.55078326</v>
+        <v>1.527462144</v>
       </c>
       <c r="P17">
-        <v>6.20313304</v>
+        <v>6.109848576</v>
       </c>
       <c r="Q17">
-        <v>6.56013304</v>
+        <v>6.466848576</v>
       </c>
       <c r="R17">
-        <v>0.1764705882352941</v>
+        <v>0.1904761904761905</v>
       </c>
       <c r="S17">
-        <v>0.08541342871530272</v>
+        <v>0.08580236763248783</v>
       </c>
       <c r="T17">
-        <v>0.7721394580973439</v>
+        <v>0.7797206015249074</v>
       </c>
       <c r="U17">
         <v>0.0553</v>
@@ -2707,7 +2707,7 @@
         </is>
       </c>
       <c r="Y17">
-        <v>5.433130501416255</v>
+        <v>5.09355984507774</v>
       </c>
       <c r="Z17">
         <v>0</v>
@@ -2715,22 +2715,22 @@
     </row>
     <row r="18">
       <c r="A18">
-        <v>0.16</v>
+        <v>0.17</v>
       </c>
       <c r="B18">
-        <v>0.07915238881128978</v>
+        <v>0.07906736321457222</v>
       </c>
       <c r="C18">
-        <v>184.8405640590439</v>
+        <v>183.2845289794975</v>
       </c>
       <c r="D18">
-        <v>216.1981640590439</v>
+        <v>216.7507289794975</v>
       </c>
       <c r="E18">
-        <v>26.6776</v>
+        <v>28.7862</v>
       </c>
       <c r="F18">
-        <v>33.7376</v>
+        <v>35.8462</v>
       </c>
       <c r="G18">
         <v>2.38</v>
@@ -2751,28 +2751,28 @@
         <v>9.503</v>
       </c>
       <c r="M18">
-        <v>1.86568928</v>
+        <v>1.98229486</v>
       </c>
       <c r="N18">
-        <v>7.63731072</v>
+        <v>7.52070514</v>
       </c>
       <c r="O18">
-        <v>1.527462144</v>
+        <v>1.504141028</v>
       </c>
       <c r="P18">
-        <v>6.109848576</v>
+        <v>6.016564111999999</v>
       </c>
       <c r="Q18">
-        <v>6.466848576</v>
+        <v>6.373564112</v>
       </c>
       <c r="R18">
-        <v>0.1904761904761905</v>
+        <v>0.2048192771084338</v>
       </c>
       <c r="S18">
-        <v>0.08580236763248783</v>
+        <v>0.08620067857177377</v>
       </c>
       <c r="T18">
-        <v>0.7797206015249074</v>
+        <v>0.787484423107352</v>
       </c>
       <c r="U18">
         <v>0.0553</v>
@@ -2789,7 +2789,7 @@
         </is>
       </c>
       <c r="Y18">
-        <v>5.09355984507774</v>
+        <v>4.793938677720226</v>
       </c>
       <c r="Z18">
         <v>0</v>
@@ -2797,22 +2797,22 @@
     </row>
     <row r="19">
       <c r="A19">
-        <v>0.17</v>
+        <v>0.18</v>
       </c>
       <c r="B19">
-        <v>0.07906736321457222</v>
+        <v>0.0789823376178547</v>
       </c>
       <c r="C19">
-        <v>183.2845289794975</v>
+        <v>181.7313256571723</v>
       </c>
       <c r="D19">
-        <v>216.7507289794975</v>
+        <v>217.3061256571723</v>
       </c>
       <c r="E19">
-        <v>28.7862</v>
+        <v>30.89480000000001</v>
       </c>
       <c r="F19">
-        <v>35.8462</v>
+        <v>37.95480000000001</v>
       </c>
       <c r="G19">
         <v>2.38</v>
@@ -2833,28 +2833,28 @@
         <v>9.503</v>
       </c>
       <c r="M19">
-        <v>1.98229486</v>
+        <v>2.09890044</v>
       </c>
       <c r="N19">
-        <v>7.52070514</v>
+        <v>7.40409956</v>
       </c>
       <c r="O19">
-        <v>1.504141028</v>
+        <v>1.480819912</v>
       </c>
       <c r="P19">
-        <v>6.016564111999999</v>
+        <v>5.923279647999999</v>
       </c>
       <c r="Q19">
-        <v>6.373564112</v>
+        <v>6.280279648</v>
       </c>
       <c r="R19">
-        <v>0.2048192771084338</v>
+        <v>0.2195121951219512</v>
       </c>
       <c r="S19">
-        <v>0.08620067857177377</v>
+        <v>0.08660870441201793</v>
       </c>
       <c r="T19">
-        <v>0.787484423107352</v>
+        <v>0.7954376061918075</v>
       </c>
       <c r="U19">
         <v>0.0553</v>
@@ -2871,7 +2871,7 @@
         </is>
       </c>
       <c r="Y19">
-        <v>4.793938677720226</v>
+        <v>4.527608751180212</v>
       </c>
       <c r="Z19">
         <v>0</v>
@@ -2879,22 +2879,22 @@
     </row>
     <row r="20">
       <c r="A20">
-        <v>0.18</v>
+        <v>0.19</v>
       </c>
       <c r="B20">
-        <v>0.0789823376178547</v>
+        <v>0.07927731202113716</v>
       </c>
       <c r="C20">
-        <v>181.7313256571723</v>
+        <v>177.7080036895042</v>
       </c>
       <c r="D20">
-        <v>217.3061256571723</v>
+        <v>215.3914036895042</v>
       </c>
       <c r="E20">
-        <v>30.8948</v>
+        <v>33.0034</v>
       </c>
       <c r="F20">
-        <v>37.9548</v>
+        <v>40.0634</v>
       </c>
       <c r="G20">
         <v>2.38</v>
@@ -2915,45 +2915,45 @@
         <v>9.503</v>
       </c>
       <c r="M20">
-        <v>2.09890044</v>
+        <v>2.31566452</v>
       </c>
       <c r="N20">
-        <v>7.404099560000001</v>
+        <v>7.18733548</v>
       </c>
       <c r="O20">
-        <v>1.480819912</v>
+        <v>1.437467096</v>
       </c>
       <c r="P20">
-        <v>5.923279648</v>
+        <v>5.749868384</v>
       </c>
       <c r="Q20">
-        <v>6.280279648</v>
+        <v>6.106868384</v>
       </c>
       <c r="R20">
-        <v>0.2195121951219512</v>
+        <v>0.2345679012345679</v>
       </c>
       <c r="S20">
-        <v>0.08660870441201791</v>
+        <v>0.08702680496436685</v>
       </c>
       <c r="T20">
-        <v>0.7954376061918074</v>
+        <v>0.8035871641672371</v>
       </c>
       <c r="U20">
-        <v>0.0553</v>
+        <v>0.0578</v>
       </c>
       <c r="V20">
         <v>0.2</v>
       </c>
       <c r="W20">
-        <v>0.04424</v>
+        <v>0.04624</v>
       </c>
       <c r="X20" t="inlineStr">
         <is>
-          <t>A3/A-</t>
+          <t>Baa2/BBB</t>
         </is>
       </c>
       <c r="Y20">
-        <v>4.527608751180214</v>
+        <v>4.103789611113443</v>
       </c>
       <c r="Z20">
         <v>0</v>
@@ -2961,22 +2961,22 @@
     </row>
     <row r="21">
       <c r="A21">
-        <v>0.19</v>
+        <v>0.2</v>
       </c>
       <c r="B21">
-        <v>0.07927731202113716</v>
+        <v>0.07977228642441961</v>
       </c>
       <c r="C21">
-        <v>177.7080036895042</v>
+        <v>172.4611624130282</v>
       </c>
       <c r="D21">
-        <v>215.3914036895042</v>
+        <v>212.2531624130282</v>
       </c>
       <c r="E21">
-        <v>33.0034</v>
+        <v>35.112</v>
       </c>
       <c r="F21">
-        <v>40.0634</v>
+        <v>42.172</v>
       </c>
       <c r="G21">
         <v>2.38</v>
@@ -2997,45 +2997,45 @@
         <v>9.503</v>
       </c>
       <c r="M21">
-        <v>2.31566452</v>
+        <v>2.5851436</v>
       </c>
       <c r="N21">
-        <v>7.18733548</v>
+        <v>6.9178564</v>
       </c>
       <c r="O21">
-        <v>1.437467096</v>
+        <v>1.38357128</v>
       </c>
       <c r="P21">
-        <v>5.749868384</v>
+        <v>5.53428512</v>
       </c>
       <c r="Q21">
-        <v>6.106868384</v>
+        <v>5.89128512</v>
       </c>
       <c r="R21">
-        <v>0.2345679012345679</v>
+        <v>0.25</v>
       </c>
       <c r="S21">
-        <v>0.08702680496436685</v>
+        <v>0.08745535803052451</v>
       </c>
       <c r="T21">
-        <v>0.8035871641672371</v>
+        <v>0.8119404610920523</v>
       </c>
       <c r="U21">
-        <v>0.0578</v>
+        <v>0.0613</v>
       </c>
       <c r="V21">
         <v>0.2</v>
       </c>
       <c r="W21">
-        <v>0.04624</v>
+        <v>0.04904</v>
       </c>
       <c r="X21" t="inlineStr">
         <is>
-          <t>Baa2/BBB</t>
+          <t>Ba1/BB+</t>
         </is>
       </c>
       <c r="Y21">
-        <v>4.103789611113443</v>
+        <v>3.67600469080325</v>
       </c>
       <c r="Z21">
         <v>0</v>
@@ -3043,22 +3043,22 @@
     </row>
     <row r="22">
       <c r="A22">
-        <v>0.2</v>
+        <v>0.21</v>
       </c>
       <c r="B22">
-        <v>0.07977228642441961</v>
+        <v>0.07973526082770208</v>
       </c>
       <c r="C22">
-        <v>172.4611624130282</v>
+        <v>170.5841445432916</v>
       </c>
       <c r="D22">
-        <v>212.2531624130282</v>
+        <v>212.4847445432917</v>
       </c>
       <c r="E22">
-        <v>35.112</v>
+        <v>37.2206</v>
       </c>
       <c r="F22">
-        <v>42.172</v>
+        <v>44.28060000000001</v>
       </c>
       <c r="G22">
         <v>2.38</v>
@@ -3079,28 +3079,28 @@
         <v>9.503</v>
       </c>
       <c r="M22">
-        <v>2.5851436</v>
+        <v>2.714400780000001</v>
       </c>
       <c r="N22">
-        <v>6.9178564</v>
+        <v>6.78859922</v>
       </c>
       <c r="O22">
-        <v>1.38357128</v>
+        <v>1.357719844</v>
       </c>
       <c r="P22">
-        <v>5.53428512</v>
+        <v>5.430879376</v>
       </c>
       <c r="Q22">
-        <v>5.89128512</v>
+        <v>5.787879376</v>
       </c>
       <c r="R22">
-        <v>0.25</v>
+        <v>0.2658227848101266</v>
       </c>
       <c r="S22">
-        <v>0.08745535803052451</v>
+        <v>0.08789476054139503</v>
       </c>
       <c r="T22">
-        <v>0.8119404610920523</v>
+        <v>0.820505233888382</v>
       </c>
       <c r="U22">
         <v>0.0613</v>
@@ -3117,7 +3117,7 @@
         </is>
       </c>
       <c r="Y22">
-        <v>3.67600469080325</v>
+        <v>3.500956848384047</v>
       </c>
       <c r="Z22">
         <v>0</v>
@@ -3125,22 +3125,22 @@
     </row>
     <row r="23">
       <c r="A23">
-        <v>0.21</v>
+        <v>0.22</v>
       </c>
       <c r="B23">
-        <v>0.07973526082770208</v>
+        <v>0.08019103523098453</v>
       </c>
       <c r="C23">
-        <v>170.5841445432917</v>
+        <v>165.6595459261988</v>
       </c>
       <c r="D23">
-        <v>212.4847445432917</v>
+        <v>209.6687459261988</v>
       </c>
       <c r="E23">
-        <v>37.2206</v>
+        <v>39.3292</v>
       </c>
       <c r="F23">
-        <v>44.2806</v>
+        <v>46.3892</v>
       </c>
       <c r="G23">
         <v>2.38</v>
@@ -3161,45 +3161,45 @@
         <v>9.503</v>
       </c>
       <c r="M23">
-        <v>2.71440078</v>
+        <v>2.97354772</v>
       </c>
       <c r="N23">
-        <v>6.78859922</v>
+        <v>6.529452279999999</v>
       </c>
       <c r="O23">
-        <v>1.357719844</v>
+        <v>1.305890456</v>
       </c>
       <c r="P23">
-        <v>5.430879376</v>
+        <v>5.223561823999999</v>
       </c>
       <c r="Q23">
-        <v>5.787879376</v>
+        <v>5.580561823999999</v>
       </c>
       <c r="R23">
-        <v>0.2658227848101266</v>
+        <v>0.282051282051282</v>
       </c>
       <c r="S23">
-        <v>0.08789476054139503</v>
+        <v>0.0883454297833135</v>
       </c>
       <c r="T23">
-        <v>0.820505233888382</v>
+        <v>0.829289616243592</v>
       </c>
       <c r="U23">
-        <v>0.0613</v>
+        <v>0.0641</v>
       </c>
       <c r="V23">
         <v>0.2</v>
       </c>
       <c r="W23">
-        <v>0.04904</v>
+        <v>0.05128000000000001</v>
       </c>
       <c r="X23" t="inlineStr">
         <is>
-          <t>Ba1/BB+</t>
+          <t>Ba2/BB</t>
         </is>
       </c>
       <c r="Y23">
-        <v>3.500956848384047</v>
+        <v>3.19584580266968</v>
       </c>
       <c r="Z23">
         <v>0</v>
@@ -3207,22 +3207,22 @@
     </row>
     <row r="24">
       <c r="A24">
-        <v>0.22</v>
+        <v>0.23</v>
       </c>
       <c r="B24">
-        <v>0.08019103523098453</v>
+        <v>0.08017640963426699</v>
       </c>
       <c r="C24">
-        <v>165.6595459261988</v>
+        <v>163.6401504287869</v>
       </c>
       <c r="D24">
-        <v>209.6687459261988</v>
+        <v>209.7579504287869</v>
       </c>
       <c r="E24">
-        <v>39.3292</v>
+        <v>41.4378</v>
       </c>
       <c r="F24">
-        <v>46.3892</v>
+        <v>48.49780000000001</v>
       </c>
       <c r="G24">
         <v>2.38</v>
@@ -3243,28 +3243,28 @@
         <v>9.503</v>
       </c>
       <c r="M24">
-        <v>2.97354772</v>
+        <v>3.108708980000001</v>
       </c>
       <c r="N24">
-        <v>6.529452279999999</v>
+        <v>6.394291019999999</v>
       </c>
       <c r="O24">
-        <v>1.305890456</v>
+        <v>1.278858204</v>
       </c>
       <c r="P24">
-        <v>5.223561823999999</v>
+        <v>5.115432815999999</v>
       </c>
       <c r="Q24">
-        <v>5.580561823999999</v>
+        <v>5.472432816</v>
       </c>
       <c r="R24">
-        <v>0.282051282051282</v>
+        <v>0.2987012987012987</v>
       </c>
       <c r="S24">
-        <v>0.0883454297833135</v>
+        <v>0.08880780471982726</v>
       </c>
       <c r="T24">
-        <v>0.829289616243592</v>
+        <v>0.838302164374262</v>
       </c>
       <c r="U24">
         <v>0.0641</v>
@@ -3281,7 +3281,7 @@
         </is>
       </c>
       <c r="Y24">
-        <v>3.19584580266968</v>
+        <v>3.056895985162303</v>
       </c>
       <c r="Z24">
         <v>0</v>
@@ -3289,22 +3289,22 @@
     </row>
     <row r="25">
       <c r="A25">
-        <v>0.23</v>
+        <v>0.24</v>
       </c>
       <c r="B25">
-        <v>0.08017640963426699</v>
+        <v>0.08165938403754947</v>
       </c>
       <c r="C25">
-        <v>163.6401504287869</v>
+        <v>152.8569543720014</v>
       </c>
       <c r="D25">
-        <v>209.7579504287869</v>
+        <v>201.0833543720014</v>
       </c>
       <c r="E25">
-        <v>41.4378</v>
+        <v>43.54640000000001</v>
       </c>
       <c r="F25">
-        <v>48.49780000000001</v>
+        <v>50.60640000000001</v>
       </c>
       <c r="G25">
         <v>2.38</v>
@@ -3325,45 +3325,45 @@
         <v>9.503</v>
       </c>
       <c r="M25">
-        <v>3.108708980000001</v>
+        <v>3.638600160000001</v>
       </c>
       <c r="N25">
-        <v>6.394291019999999</v>
+        <v>5.864399839999999</v>
       </c>
       <c r="O25">
-        <v>1.278858204</v>
+        <v>1.172879968</v>
       </c>
       <c r="P25">
-        <v>5.115432815999999</v>
+        <v>4.691519871999999</v>
       </c>
       <c r="Q25">
-        <v>5.472432816</v>
+        <v>5.048519871999999</v>
       </c>
       <c r="R25">
-        <v>0.2987012987012987</v>
+        <v>0.3157894736842106</v>
       </c>
       <c r="S25">
-        <v>0.08880780471982726</v>
+        <v>0.08928234741782823</v>
       </c>
       <c r="T25">
-        <v>0.838302164374262</v>
+        <v>0.84755188482416</v>
       </c>
       <c r="U25">
-        <v>0.0641</v>
+        <v>0.07190000000000001</v>
       </c>
       <c r="V25">
         <v>0.2</v>
       </c>
       <c r="W25">
-        <v>0.05128000000000001</v>
+        <v>0.05752000000000001</v>
       </c>
       <c r="X25" t="inlineStr">
         <is>
-          <t>Ba2/BB</t>
+          <t>B1/B+</t>
         </is>
       </c>
       <c r="Y25">
-        <v>3.056895985162303</v>
+        <v>2.611718678097348</v>
       </c>
       <c r="Z25">
         <v>0</v>
@@ -3371,22 +3371,22 @@
     </row>
     <row r="26">
       <c r="A26">
-        <v>0.24</v>
+        <v>0.25</v>
       </c>
       <c r="B26">
-        <v>0.08165938403754945</v>
+        <v>0.0817071584408319</v>
       </c>
       <c r="C26">
-        <v>152.8569543720014</v>
+        <v>150.4808133667452</v>
       </c>
       <c r="D26">
-        <v>201.0833543720014</v>
+        <v>200.8158133667452</v>
       </c>
       <c r="E26">
-        <v>43.5464</v>
+        <v>45.655</v>
       </c>
       <c r="F26">
-        <v>50.6064</v>
+        <v>52.715</v>
       </c>
       <c r="G26">
         <v>2.38</v>
@@ -3407,28 +3407,28 @@
         <v>9.503</v>
       </c>
       <c r="M26">
-        <v>3.63860016</v>
+        <v>3.790208500000001</v>
       </c>
       <c r="N26">
-        <v>5.86439984</v>
+        <v>5.7127915</v>
       </c>
       <c r="O26">
-        <v>1.172879968</v>
+        <v>1.1425583</v>
       </c>
       <c r="P26">
-        <v>4.691519872</v>
+        <v>4.5702332</v>
       </c>
       <c r="Q26">
-        <v>5.048519872</v>
+        <v>4.9272332</v>
       </c>
       <c r="R26">
-        <v>0.3157894736842105</v>
+        <v>0.3333333333333333</v>
       </c>
       <c r="S26">
-        <v>0.08928234741782821</v>
+        <v>0.08976954458777586</v>
       </c>
       <c r="T26">
-        <v>0.8475518848241599</v>
+        <v>0.8570482644860552</v>
       </c>
       <c r="U26">
         <v>0.07190000000000001</v>
@@ -3445,7 +3445,7 @@
         </is>
       </c>
       <c r="Y26">
-        <v>2.611718678097348</v>
+        <v>2.507249930973454</v>
       </c>
       <c r="Z26">
         <v>0</v>
@@ -3453,22 +3453,22 @@
     </row>
     <row r="27">
       <c r="A27">
-        <v>0.25</v>
+        <v>0.26</v>
       </c>
       <c r="B27">
-        <v>0.0817071584408319</v>
+        <v>0.08256613284411436</v>
       </c>
       <c r="C27">
-        <v>150.4808133667452</v>
+        <v>143.680513965349</v>
       </c>
       <c r="D27">
-        <v>200.8158133667452</v>
+        <v>196.124113965349</v>
       </c>
       <c r="E27">
-        <v>45.655</v>
+        <v>47.7636</v>
       </c>
       <c r="F27">
-        <v>52.715</v>
+        <v>54.82360000000001</v>
       </c>
       <c r="G27">
         <v>2.38</v>
@@ -3489,45 +3489,45 @@
         <v>9.503</v>
       </c>
       <c r="M27">
-        <v>3.790208500000001</v>
+        <v>4.155628880000001</v>
       </c>
       <c r="N27">
-        <v>5.7127915</v>
+        <v>5.347371119999999</v>
       </c>
       <c r="O27">
-        <v>1.1425583</v>
+        <v>1.069474224</v>
       </c>
       <c r="P27">
-        <v>4.5702332</v>
+        <v>4.277896896</v>
       </c>
       <c r="Q27">
-        <v>4.9272332</v>
+        <v>4.634896896</v>
       </c>
       <c r="R27">
-        <v>0.3333333333333333</v>
+        <v>0.3513513513513514</v>
       </c>
       <c r="S27">
-        <v>0.08976954458777586</v>
+        <v>0.0902699092488032</v>
       </c>
       <c r="T27">
-        <v>0.8570482644860552</v>
+        <v>0.8668013030577316</v>
       </c>
       <c r="U27">
-        <v>0.07190000000000001</v>
+        <v>0.07580000000000001</v>
       </c>
       <c r="V27">
         <v>0.2</v>
       </c>
       <c r="W27">
-        <v>0.05752000000000001</v>
+        <v>0.06064000000000001</v>
       </c>
       <c r="X27" t="inlineStr">
         <is>
-          <t>B1/B+</t>
+          <t>B2/B</t>
         </is>
       </c>
       <c r="Y27">
-        <v>2.507249930973454</v>
+        <v>2.28677783180677</v>
       </c>
       <c r="Z27">
         <v>0</v>
@@ -3535,22 +3535,22 @@
     </row>
     <row r="28">
       <c r="A28">
-        <v>0.26</v>
+        <v>0.27</v>
       </c>
       <c r="B28">
-        <v>0.08256613284411436</v>
+        <v>0.08264510724739683</v>
       </c>
       <c r="C28">
-        <v>143.680513965349</v>
+        <v>141.1515383435408</v>
       </c>
       <c r="D28">
-        <v>196.124113965349</v>
+        <v>195.7037383435408</v>
       </c>
       <c r="E28">
-        <v>47.7636</v>
+        <v>49.87220000000001</v>
       </c>
       <c r="F28">
-        <v>54.82360000000001</v>
+        <v>56.93220000000001</v>
       </c>
       <c r="G28">
         <v>2.38</v>
@@ -3571,28 +3571,28 @@
         <v>9.503</v>
       </c>
       <c r="M28">
-        <v>4.155628880000001</v>
+        <v>4.315460760000001</v>
       </c>
       <c r="N28">
-        <v>5.347371119999999</v>
+        <v>5.187539239999999</v>
       </c>
       <c r="O28">
-        <v>1.069474224</v>
+        <v>1.037507848</v>
       </c>
       <c r="P28">
-        <v>4.277896896</v>
+        <v>4.150031391999999</v>
       </c>
       <c r="Q28">
-        <v>4.634896896</v>
+        <v>4.507031391999999</v>
       </c>
       <c r="R28">
-        <v>0.3513513513513514</v>
+        <v>0.3698630136986302</v>
       </c>
       <c r="S28">
-        <v>0.0902699092488032</v>
+        <v>0.09078398253068058</v>
       </c>
       <c r="T28">
-        <v>0.8668013030577316</v>
+        <v>0.8768215481656183</v>
       </c>
       <c r="U28">
         <v>0.07580000000000001</v>
@@ -3609,7 +3609,7 @@
         </is>
       </c>
       <c r="Y28">
-        <v>2.28677783180677</v>
+        <v>2.202082356554667</v>
       </c>
       <c r="Z28">
         <v>0</v>
@@ -3617,22 +3617,22 @@
     </row>
     <row r="29">
       <c r="A29">
-        <v>0.27</v>
+        <v>0.28</v>
       </c>
       <c r="B29">
-        <v>0.08264510724739683</v>
+        <v>0.08272408165067928</v>
       </c>
       <c r="C29">
-        <v>141.1515383435408</v>
+        <v>138.6243609473026</v>
       </c>
       <c r="D29">
-        <v>195.7037383435408</v>
+        <v>195.2851609473027</v>
       </c>
       <c r="E29">
-        <v>49.87220000000001</v>
+        <v>51.98080000000001</v>
       </c>
       <c r="F29">
-        <v>56.93220000000001</v>
+        <v>59.04080000000001</v>
       </c>
       <c r="G29">
         <v>2.38</v>
@@ -3653,28 +3653,28 @@
         <v>9.503</v>
       </c>
       <c r="M29">
-        <v>4.315460760000001</v>
+        <v>4.475292640000001</v>
       </c>
       <c r="N29">
-        <v>5.187539239999999</v>
+        <v>5.027707359999999</v>
       </c>
       <c r="O29">
-        <v>1.037507848</v>
+        <v>1.005541472</v>
       </c>
       <c r="P29">
-        <v>4.150031391999999</v>
+        <v>4.022165887999999</v>
       </c>
       <c r="Q29">
-        <v>4.507031391999999</v>
+        <v>4.379165887999999</v>
       </c>
       <c r="R29">
-        <v>0.3698630136986302</v>
+        <v>0.388888888888889</v>
       </c>
       <c r="S29">
-        <v>0.09078398253068058</v>
+        <v>0.09131233562594344</v>
       </c>
       <c r="T29">
-        <v>0.8768215481656183</v>
+        <v>0.8871201334153905</v>
       </c>
       <c r="U29">
         <v>0.07580000000000001</v>
@@ -3691,7 +3691,7 @@
         </is>
       </c>
       <c r="Y29">
-        <v>2.202082356554667</v>
+        <v>2.123436558106287</v>
       </c>
       <c r="Z29">
         <v>0</v>
@@ -3699,22 +3699,22 @@
     </row>
     <row r="30">
       <c r="A30">
-        <v>0.28</v>
+        <v>0.29</v>
       </c>
       <c r="B30">
-        <v>0.08272408165067928</v>
+        <v>0.08280305605396175</v>
       </c>
       <c r="C30">
-        <v>138.6243609473026</v>
+        <v>136.0989702629537</v>
       </c>
       <c r="D30">
-        <v>195.2851609473027</v>
+        <v>194.8683702629537</v>
       </c>
       <c r="E30">
-        <v>51.98080000000001</v>
+        <v>54.08940000000001</v>
       </c>
       <c r="F30">
-        <v>59.04080000000001</v>
+        <v>61.14940000000001</v>
       </c>
       <c r="G30">
         <v>2.38</v>
@@ -3735,28 +3735,28 @@
         <v>9.503</v>
       </c>
       <c r="M30">
-        <v>4.475292640000001</v>
+        <v>4.635124520000002</v>
       </c>
       <c r="N30">
-        <v>5.027707359999999</v>
+        <v>4.867875479999999</v>
       </c>
       <c r="O30">
-        <v>1.005541472</v>
+        <v>0.9735750959999998</v>
       </c>
       <c r="P30">
-        <v>4.022165887999999</v>
+        <v>3.894300383999999</v>
       </c>
       <c r="Q30">
-        <v>4.379165887999999</v>
+        <v>4.251300383999999</v>
       </c>
       <c r="R30">
-        <v>0.388888888888889</v>
+        <v>0.4084507042253522</v>
       </c>
       <c r="S30">
-        <v>0.09131233562594344</v>
+        <v>0.09185557190698837</v>
       </c>
       <c r="T30">
-        <v>0.8871201334153905</v>
+        <v>0.8977088196581142</v>
       </c>
       <c r="U30">
         <v>0.07580000000000001</v>
@@ -3773,7 +3773,7 @@
         </is>
       </c>
       <c r="Y30">
-        <v>2.123436558106287</v>
+        <v>2.05021460782676</v>
       </c>
       <c r="Z30">
         <v>0</v>
@@ -3781,22 +3781,22 @@
     </row>
     <row r="31">
       <c r="A31">
-        <v>0.29</v>
+        <v>0.3</v>
       </c>
       <c r="B31">
-        <v>0.08280305605396174</v>
+        <v>0.08629003045724419</v>
       </c>
       <c r="C31">
-        <v>136.0989702629537</v>
+        <v>117.2084362549314</v>
       </c>
       <c r="D31">
-        <v>194.8683702629537</v>
+        <v>178.0864362549314</v>
       </c>
       <c r="E31">
-        <v>54.0894</v>
+        <v>56.198</v>
       </c>
       <c r="F31">
-        <v>61.1494</v>
+        <v>63.258</v>
       </c>
       <c r="G31">
         <v>2.38</v>
@@ -3817,45 +3817,45 @@
         <v>9.503</v>
       </c>
       <c r="M31">
-        <v>4.635124520000001</v>
+        <v>5.69322</v>
       </c>
       <c r="N31">
-        <v>4.867875479999999</v>
+        <v>3.80978</v>
       </c>
       <c r="O31">
-        <v>0.9735750959999999</v>
+        <v>0.7619560000000001</v>
       </c>
       <c r="P31">
-        <v>3.894300384</v>
+        <v>3.047824</v>
       </c>
       <c r="Q31">
-        <v>4.251300383999999</v>
+        <v>3.404824</v>
       </c>
       <c r="R31">
-        <v>0.4084507042253521</v>
+        <v>0.4285714285714286</v>
       </c>
       <c r="S31">
-        <v>0.09185557190698837</v>
+        <v>0.09241432922463458</v>
       </c>
       <c r="T31">
-        <v>0.8977088196581142</v>
+        <v>0.9086000397934872</v>
       </c>
       <c r="U31">
-        <v>0.07580000000000001</v>
+        <v>0.09</v>
       </c>
       <c r="V31">
         <v>0.2</v>
       </c>
       <c r="W31">
-        <v>0.06064000000000001</v>
+        <v>0.07199999999999999</v>
       </c>
       <c r="X31" t="inlineStr">
         <is>
-          <t>B2/B</t>
+          <t>B3/B-</t>
         </is>
       </c>
       <c r="Y31">
-        <v>2.05021460782676</v>
+        <v>1.669178426268439</v>
       </c>
       <c r="Z31">
         <v>0</v>
@@ -3863,22 +3863,22 @@
     </row>
     <row r="32">
       <c r="A32">
-        <v>0.3</v>
+        <v>0.31</v>
       </c>
       <c r="B32">
-        <v>0.08629003045724419</v>
+        <v>0.08648260486052664</v>
       </c>
       <c r="C32">
-        <v>117.2084362549314</v>
+        <v>114.2568496931793</v>
       </c>
       <c r="D32">
-        <v>178.0864362549314</v>
+        <v>177.2434496931793</v>
       </c>
       <c r="E32">
-        <v>56.198</v>
+        <v>58.3066</v>
       </c>
       <c r="F32">
-        <v>63.258</v>
+        <v>65.36660000000001</v>
       </c>
       <c r="G32">
         <v>2.38</v>
@@ -3899,28 +3899,28 @@
         <v>9.503</v>
       </c>
       <c r="M32">
-        <v>5.69322</v>
+        <v>5.882994</v>
       </c>
       <c r="N32">
-        <v>3.80978</v>
+        <v>3.620006</v>
       </c>
       <c r="O32">
-        <v>0.7619560000000001</v>
+        <v>0.7240012</v>
       </c>
       <c r="P32">
-        <v>3.047824</v>
+        <v>2.8960048</v>
       </c>
       <c r="Q32">
-        <v>3.404824</v>
+        <v>3.2530048</v>
       </c>
       <c r="R32">
-        <v>0.4285714285714286</v>
+        <v>0.4492753623188406</v>
       </c>
       <c r="S32">
-        <v>0.09241432922463458</v>
+        <v>0.09298928240656038</v>
       </c>
       <c r="T32">
-        <v>0.9086000397934872</v>
+        <v>0.9198069474690158</v>
       </c>
       <c r="U32">
         <v>0.09</v>
@@ -3937,7 +3937,7 @@
         </is>
       </c>
       <c r="Y32">
-        <v>1.669178426268439</v>
+        <v>1.615333960904941</v>
       </c>
       <c r="Z32">
         <v>0</v>
@@ -3945,22 +3945,22 @@
     </row>
     <row r="33">
       <c r="A33">
-        <v>0.31</v>
+        <v>0.32</v>
       </c>
       <c r="B33">
-        <v>0.08648260486052664</v>
+        <v>0.0866751792638091</v>
       </c>
       <c r="C33">
-        <v>114.2568496931793</v>
+        <v>111.3132062224193</v>
       </c>
       <c r="D33">
-        <v>177.2434496931793</v>
+        <v>176.4084062224193</v>
       </c>
       <c r="E33">
-        <v>58.3066</v>
+        <v>60.4152</v>
       </c>
       <c r="F33">
-        <v>65.36660000000001</v>
+        <v>67.4752</v>
       </c>
       <c r="G33">
         <v>2.38</v>
@@ -3981,28 +3981,28 @@
         <v>9.503</v>
       </c>
       <c r="M33">
-        <v>5.882994</v>
+        <v>6.072768</v>
       </c>
       <c r="N33">
-        <v>3.620006</v>
+        <v>3.430232</v>
       </c>
       <c r="O33">
-        <v>0.7240012</v>
+        <v>0.6860464000000001</v>
       </c>
       <c r="P33">
-        <v>2.8960048</v>
+        <v>2.7441856</v>
       </c>
       <c r="Q33">
-        <v>3.2530048</v>
+        <v>3.1011856</v>
       </c>
       <c r="R33">
-        <v>0.4492753623188406</v>
+        <v>0.4705882352941177</v>
       </c>
       <c r="S33">
-        <v>0.09298928240656038</v>
+        <v>0.09358114597618988</v>
       </c>
       <c r="T33">
-        <v>0.9198069474690158</v>
+        <v>0.9313434700761777</v>
       </c>
       <c r="U33">
         <v>0.09</v>
@@ -4019,7 +4019,7 @@
         </is>
       </c>
       <c r="Y33">
-        <v>1.615333960904941</v>
+        <v>1.564854774626661</v>
       </c>
       <c r="Z33">
         <v>0</v>
@@ -4027,22 +4027,22 @@
     </row>
     <row r="34">
       <c r="A34">
-        <v>0.32</v>
+        <v>0.33</v>
       </c>
       <c r="B34">
-        <v>0.0866751792638091</v>
+        <v>0.08686775366709157</v>
       </c>
       <c r="C34">
-        <v>111.3132062224193</v>
+        <v>108.3773941027188</v>
       </c>
       <c r="D34">
-        <v>176.4084062224193</v>
+        <v>175.5811941027188</v>
       </c>
       <c r="E34">
-        <v>60.4152</v>
+        <v>62.52380000000001</v>
       </c>
       <c r="F34">
-        <v>67.4752</v>
+        <v>69.58380000000001</v>
       </c>
       <c r="G34">
         <v>2.38</v>
@@ -4063,28 +4063,28 @@
         <v>9.503</v>
       </c>
       <c r="M34">
-        <v>6.072768</v>
+        <v>6.262542000000001</v>
       </c>
       <c r="N34">
-        <v>3.430232</v>
+        <v>3.240457999999999</v>
       </c>
       <c r="O34">
-        <v>0.6860464000000001</v>
+        <v>0.6480915999999999</v>
       </c>
       <c r="P34">
-        <v>2.7441856</v>
+        <v>2.5923664</v>
       </c>
       <c r="Q34">
-        <v>3.1011856</v>
+        <v>2.9493664</v>
       </c>
       <c r="R34">
-        <v>0.4705882352941177</v>
+        <v>0.4925373134328359</v>
       </c>
       <c r="S34">
-        <v>0.09358114597618988</v>
+        <v>0.09419067711506206</v>
       </c>
       <c r="T34">
-        <v>0.9313434700761777</v>
+        <v>0.9432243664925086</v>
       </c>
       <c r="U34">
         <v>0.09</v>
@@ -4101,7 +4101,7 @@
         </is>
       </c>
       <c r="Y34">
-        <v>1.564854774626661</v>
+        <v>1.517434932971308</v>
       </c>
       <c r="Z34">
         <v>0</v>
@@ -4109,22 +4109,22 @@
     </row>
     <row r="35">
       <c r="A35">
-        <v>0.33</v>
+        <v>0.34</v>
       </c>
       <c r="B35">
-        <v>0.08686775366709157</v>
+        <v>0.1037078587511056</v>
       </c>
       <c r="C35">
-        <v>108.3773941027188</v>
+        <v>55.20826754836752</v>
       </c>
       <c r="D35">
-        <v>175.5811941027188</v>
+        <v>124.5206675483675</v>
       </c>
       <c r="E35">
-        <v>62.52380000000001</v>
+        <v>64.6324</v>
       </c>
       <c r="F35">
-        <v>69.58380000000001</v>
+        <v>71.69240000000001</v>
       </c>
       <c r="G35">
         <v>2.38</v>
@@ -4145,45 +4145,45 @@
         <v>9.503</v>
       </c>
       <c r="M35">
-        <v>6.262542000000001</v>
+        <v>10.52444432</v>
       </c>
       <c r="N35">
-        <v>3.240457999999999</v>
+        <v>-1.021444320000002</v>
       </c>
       <c r="O35">
-        <v>0.6480915999999999</v>
+        <v>-0.2042888640000005</v>
       </c>
       <c r="P35">
-        <v>2.5923664</v>
+        <v>-0.8171554560000018</v>
       </c>
       <c r="Q35">
-        <v>2.9493664</v>
+        <v>-0.4601554560000019</v>
       </c>
       <c r="R35">
-        <v>0.4925373134328359</v>
+        <v>0.5151515151515152</v>
       </c>
       <c r="S35">
-        <v>0.09419067711506206</v>
+        <v>0.09516579129235636</v>
       </c>
       <c r="T35">
-        <v>0.9432243664925086</v>
+        <v>0.9622311567870382</v>
       </c>
       <c r="U35">
-        <v>0.09</v>
+        <v>0.1468</v>
       </c>
       <c r="V35">
-        <v>0.2</v>
+        <v>0.1805891068650739</v>
       </c>
       <c r="W35">
-        <v>0.07199999999999999</v>
+        <v>0.1202895191122072</v>
       </c>
       <c r="X35" t="inlineStr">
         <is>
-          <t>B3/B-</t>
+          <t>Ca2/CC</t>
         </is>
       </c>
       <c r="Y35">
-        <v>1.517434932971308</v>
+        <v>0.9029455343253693</v>
       </c>
       <c r="Z35">
         <v>0</v>
@@ -4191,22 +4191,22 @@
     </row>
     <row r="36">
       <c r="A36">
-        <v>0.34</v>
+        <v>0.35</v>
       </c>
       <c r="B36">
-        <v>0.1037078587511056</v>
+        <v>0.1047178587511056</v>
       </c>
       <c r="C36">
-        <v>55.20826754836752</v>
+        <v>50.96507072340243</v>
       </c>
       <c r="D36">
-        <v>124.5206675483675</v>
+        <v>122.3860707234025</v>
       </c>
       <c r="E36">
-        <v>64.6324</v>
+        <v>66.74100000000001</v>
       </c>
       <c r="F36">
-        <v>71.69240000000001</v>
+        <v>73.80100000000002</v>
       </c>
       <c r="G36">
         <v>2.38</v>
@@ -4227,37 +4227,37 @@
         <v>9.503</v>
       </c>
       <c r="M36">
-        <v>10.52444432</v>
+        <v>10.8339868</v>
       </c>
       <c r="N36">
-        <v>-1.021444320000002</v>
+        <v>-1.330986800000003</v>
       </c>
       <c r="O36">
-        <v>-0.2042888640000005</v>
+        <v>-0.2661973600000007</v>
       </c>
       <c r="P36">
-        <v>-0.8171554560000018</v>
+        <v>-1.064789440000003</v>
       </c>
       <c r="Q36">
-        <v>-0.4601554560000019</v>
+        <v>-0.7077894400000027</v>
       </c>
       <c r="R36">
-        <v>0.5151515151515152</v>
+        <v>0.5384615384615385</v>
       </c>
       <c r="S36">
-        <v>0.09516579129235636</v>
+        <v>0.09592526500454644</v>
       </c>
       <c r="T36">
-        <v>0.9622311567870382</v>
+        <v>0.9770347130453002</v>
       </c>
       <c r="U36">
         <v>0.1468</v>
       </c>
       <c r="V36">
-        <v>0.1805891068650739</v>
+        <v>0.1754294180975003</v>
       </c>
       <c r="W36">
-        <v>0.1202895191122072</v>
+        <v>0.121046961423287</v>
       </c>
       <c r="X36" t="inlineStr">
         <is>
@@ -4265,7 +4265,7 @@
         </is>
       </c>
       <c r="Y36">
-        <v>0.9029455343253693</v>
+        <v>0.8771470904875015</v>
       </c>
       <c r="Z36">
         <v>0</v>
@@ -4273,22 +4273,22 @@
     </row>
     <row r="37">
       <c r="A37">
-        <v>0.35</v>
+        <v>0.36</v>
       </c>
       <c r="B37">
-        <v>0.1047178587511056</v>
+        <v>0.1057278587511056</v>
       </c>
       <c r="C37">
-        <v>50.96507072340243</v>
+        <v>46.79382516911993</v>
       </c>
       <c r="D37">
-        <v>122.3860707234025</v>
+        <v>120.3234251691199</v>
       </c>
       <c r="E37">
-        <v>66.74100000000001</v>
+        <v>68.84960000000001</v>
       </c>
       <c r="F37">
-        <v>73.80100000000002</v>
+        <v>75.90960000000001</v>
       </c>
       <c r="G37">
         <v>2.38</v>
@@ -4309,37 +4309,37 @@
         <v>9.503</v>
       </c>
       <c r="M37">
-        <v>10.8339868</v>
+        <v>11.14352928</v>
       </c>
       <c r="N37">
-        <v>-1.330986800000003</v>
+        <v>-1.640529280000003</v>
       </c>
       <c r="O37">
-        <v>-0.2661973600000007</v>
+        <v>-0.3281058560000005</v>
       </c>
       <c r="P37">
-        <v>-1.064789440000003</v>
+        <v>-1.312423424000002</v>
       </c>
       <c r="Q37">
-        <v>-0.7077894400000027</v>
+        <v>-0.9554234240000021</v>
       </c>
       <c r="R37">
-        <v>0.5384615384615385</v>
+        <v>0.5625000000000001</v>
       </c>
       <c r="S37">
-        <v>0.09592526500454644</v>
+        <v>0.09670847227024248</v>
       </c>
       <c r="T37">
-        <v>0.9770347130453002</v>
+        <v>0.9923008804366331</v>
       </c>
       <c r="U37">
         <v>0.1468</v>
       </c>
       <c r="V37">
-        <v>0.1754294180975003</v>
+        <v>0.1705563787059031</v>
       </c>
       <c r="W37">
-        <v>0.121046961423287</v>
+        <v>0.1217623236059734</v>
       </c>
       <c r="X37" t="inlineStr">
         <is>
@@ -4347,7 +4347,7 @@
         </is>
       </c>
       <c r="Y37">
-        <v>0.8771470904875015</v>
+        <v>0.8527818935295155</v>
       </c>
       <c r="Z37">
         <v>0</v>
@@ -4355,22 +4355,22 @@
     </row>
     <row r="38">
       <c r="A38">
-        <v>0.36</v>
+        <v>0.37</v>
       </c>
       <c r="B38">
-        <v>0.1057278587511056</v>
+        <v>0.1067378587511056</v>
       </c>
       <c r="C38">
-        <v>46.79382516911994</v>
+        <v>42.69095326801531</v>
       </c>
       <c r="D38">
-        <v>120.3234251691199</v>
+        <v>118.3291532680153</v>
       </c>
       <c r="E38">
-        <v>68.8496</v>
+        <v>70.95820000000001</v>
       </c>
       <c r="F38">
-        <v>75.9096</v>
+        <v>78.01820000000001</v>
       </c>
       <c r="G38">
         <v>2.38</v>
@@ -4391,37 +4391,37 @@
         <v>9.503</v>
       </c>
       <c r="M38">
-        <v>11.14352928</v>
+        <v>11.45307176</v>
       </c>
       <c r="N38">
-        <v>-1.640529280000001</v>
+        <v>-1.950071760000002</v>
       </c>
       <c r="O38">
-        <v>-0.3281058560000002</v>
+        <v>-0.3900143520000004</v>
       </c>
       <c r="P38">
-        <v>-1.312423424000001</v>
+        <v>-1.560057408000002</v>
       </c>
       <c r="Q38">
-        <v>-0.9554234240000008</v>
+        <v>-1.203057408000002</v>
       </c>
       <c r="R38">
-        <v>0.5625</v>
+        <v>0.5873015873015873</v>
       </c>
       <c r="S38">
-        <v>0.09670847227024248</v>
+        <v>0.09751654325865904</v>
       </c>
       <c r="T38">
-        <v>0.9923008804366331</v>
+        <v>1.008051688062611</v>
       </c>
       <c r="U38">
         <v>0.1468</v>
       </c>
       <c r="V38">
-        <v>0.1705563787059031</v>
+        <v>0.1659467468489868</v>
       </c>
       <c r="W38">
-        <v>0.1217623236059734</v>
+        <v>0.1224390175625688</v>
       </c>
       <c r="X38" t="inlineStr">
         <is>
@@ -4429,7 +4429,7 @@
         </is>
       </c>
       <c r="Y38">
-        <v>0.8527818935295155</v>
+        <v>0.829733734244934</v>
       </c>
       <c r="Z38">
         <v>0</v>
@@ -4437,22 +4437,22 @@
     </row>
     <row r="39">
       <c r="A39">
-        <v>0.37</v>
+        <v>0.38</v>
       </c>
       <c r="B39">
-        <v>0.1067378587511056</v>
+        <v>0.1077478587511056</v>
       </c>
       <c r="C39">
-        <v>42.69095326801531</v>
+        <v>38.65311072097472</v>
       </c>
       <c r="D39">
-        <v>118.3291532680153</v>
+        <v>116.3999107209747</v>
       </c>
       <c r="E39">
-        <v>70.95820000000001</v>
+        <v>73.0668</v>
       </c>
       <c r="F39">
-        <v>78.01820000000001</v>
+        <v>80.1268</v>
       </c>
       <c r="G39">
         <v>2.38</v>
@@ -4473,37 +4473,37 @@
         <v>9.503</v>
       </c>
       <c r="M39">
-        <v>11.45307176</v>
+        <v>11.76261424</v>
       </c>
       <c r="N39">
-        <v>-1.950071760000002</v>
+        <v>-2.259614240000001</v>
       </c>
       <c r="O39">
-        <v>-0.3900143520000004</v>
+        <v>-0.4519228480000003</v>
       </c>
       <c r="P39">
-        <v>-1.560057408000002</v>
+        <v>-1.807691392000001</v>
       </c>
       <c r="Q39">
-        <v>-1.203057408000002</v>
+        <v>-1.450691392000001</v>
       </c>
       <c r="R39">
-        <v>0.5873015873015873</v>
+        <v>0.6129032258064516</v>
       </c>
       <c r="S39">
-        <v>0.09751654325865904</v>
+        <v>0.09835068105315353</v>
       </c>
       <c r="T39">
-        <v>1.008051688062611</v>
+        <v>1.02431058625717</v>
       </c>
       <c r="U39">
         <v>0.1468</v>
       </c>
       <c r="V39">
-        <v>0.1659467468489868</v>
+        <v>0.1615797271950661</v>
       </c>
       <c r="W39">
-        <v>0.1224390175625688</v>
+        <v>0.1230800960477643</v>
       </c>
       <c r="X39" t="inlineStr">
         <is>
@@ -4511,7 +4511,7 @@
         </is>
       </c>
       <c r="Y39">
-        <v>0.829733734244934</v>
+        <v>0.8078986359753305</v>
       </c>
       <c r="Z39">
         <v>0</v>
@@ -4519,22 +4519,22 @@
     </row>
     <row r="40">
       <c r="A40">
-        <v>0.38</v>
+        <v>0.39</v>
       </c>
       <c r="B40">
-        <v>0.1077478587511056</v>
+        <v>0.1303910375843428</v>
       </c>
       <c r="C40">
-        <v>38.65311072097472</v>
+        <v>5.386789171573668</v>
       </c>
       <c r="D40">
-        <v>116.3999107209747</v>
+        <v>85.24218917157368</v>
       </c>
       <c r="E40">
-        <v>73.0668</v>
+        <v>75.17540000000001</v>
       </c>
       <c r="F40">
-        <v>80.1268</v>
+        <v>82.23540000000001</v>
       </c>
       <c r="G40">
         <v>2.38</v>
@@ -4555,45 +4555,45 @@
         <v>9.503</v>
       </c>
       <c r="M40">
-        <v>11.76261424</v>
+        <v>16.51286832</v>
       </c>
       <c r="N40">
-        <v>-2.259614240000001</v>
+        <v>-7.009868320000002</v>
       </c>
       <c r="O40">
-        <v>-0.4519228480000003</v>
+        <v>-1.401973664000001</v>
       </c>
       <c r="P40">
-        <v>-1.807691392000001</v>
+        <v>-5.607894656000002</v>
       </c>
       <c r="Q40">
-        <v>-1.450691392000001</v>
+        <v>-5.250894656000002</v>
       </c>
       <c r="R40">
-        <v>0.6129032258064516</v>
+        <v>0.639344262295082</v>
       </c>
       <c r="S40">
-        <v>0.09835068105315353</v>
+        <v>0.1001518050593317</v>
       </c>
       <c r="T40">
-        <v>1.02431058625717</v>
+        <v>1.059417845567932</v>
       </c>
       <c r="U40">
-        <v>0.1468</v>
+        <v>0.2008</v>
       </c>
       <c r="V40">
-        <v>0.1615797271950661</v>
+        <v>0.1150981139780566</v>
       </c>
       <c r="W40">
-        <v>0.1230800960477643</v>
+        <v>0.1776882987132062</v>
       </c>
       <c r="X40" t="inlineStr">
         <is>
-          <t>Ca2/CC</t>
+          <t>C2/C</t>
         </is>
       </c>
       <c r="Y40">
-        <v>0.8078986359753305</v>
+        <v>0.5754905698902829</v>
       </c>
       <c r="Z40">
         <v>0</v>
@@ -4601,22 +4601,22 @@
     </row>
     <row r="41">
       <c r="A41">
-        <v>0.39</v>
+        <v>0.4</v>
       </c>
       <c r="B41">
-        <v>0.1303910375843428</v>
+        <v>0.1319410375843428</v>
       </c>
       <c r="C41">
-        <v>5.386789171573668</v>
+        <v>1.744362822122383</v>
       </c>
       <c r="D41">
-        <v>85.24218917157368</v>
+        <v>83.7083628221224</v>
       </c>
       <c r="E41">
-        <v>75.17540000000001</v>
+        <v>77.28400000000001</v>
       </c>
       <c r="F41">
-        <v>82.23540000000001</v>
+        <v>84.34400000000001</v>
       </c>
       <c r="G41">
         <v>2.38</v>
@@ -4637,37 +4637,37 @@
         <v>9.503</v>
       </c>
       <c r="M41">
-        <v>16.51286832</v>
+        <v>16.9362752</v>
       </c>
       <c r="N41">
-        <v>-7.009868320000002</v>
+        <v>-7.433275200000001</v>
       </c>
       <c r="O41">
-        <v>-1.401973664000001</v>
+        <v>-1.48665504</v>
       </c>
       <c r="P41">
-        <v>-5.607894656000002</v>
+        <v>-5.94662016</v>
       </c>
       <c r="Q41">
-        <v>-5.250894656000002</v>
+        <v>-5.58962016</v>
       </c>
       <c r="R41">
-        <v>0.639344262295082</v>
+        <v>0.6666666666666667</v>
       </c>
       <c r="S41">
-        <v>0.1001518050593317</v>
+        <v>0.1010576684769873</v>
       </c>
       <c r="T41">
-        <v>1.059417845567932</v>
+        <v>1.077074809660731</v>
       </c>
       <c r="U41">
         <v>0.2008</v>
       </c>
       <c r="V41">
-        <v>0.1150981139780566</v>
+        <v>0.1122206611286052</v>
       </c>
       <c r="W41">
-        <v>0.1776882987132062</v>
+        <v>0.1782660912453761</v>
       </c>
       <c r="X41" t="inlineStr">
         <is>
@@ -4675,7 +4675,7 @@
         </is>
       </c>
       <c r="Y41">
-        <v>0.5754905698902829</v>
+        <v>0.5611033056430259</v>
       </c>
       <c r="Z41">
         <v>0</v>
@@ -4683,22 +4683,22 @@
     </row>
     <row r="42">
       <c r="A42">
-        <v>0.4</v>
+        <v>0.41</v>
       </c>
       <c r="B42">
-        <v>0.1319410375843428</v>
+        <v>0.1334910375843428</v>
       </c>
       <c r="C42">
-        <v>1.744362822122383</v>
+        <v>-1.843840635066684</v>
       </c>
       <c r="D42">
-        <v>83.7083628221224</v>
+        <v>82.22875936493334</v>
       </c>
       <c r="E42">
-        <v>77.28400000000001</v>
+        <v>79.39260000000002</v>
       </c>
       <c r="F42">
-        <v>84.34400000000001</v>
+        <v>86.45260000000002</v>
       </c>
       <c r="G42">
         <v>2.38</v>
@@ -4719,37 +4719,37 @@
         <v>9.503</v>
       </c>
       <c r="M42">
-        <v>16.9362752</v>
+        <v>17.35968208</v>
       </c>
       <c r="N42">
-        <v>-7.433275200000001</v>
+        <v>-7.856682080000002</v>
       </c>
       <c r="O42">
-        <v>-1.48665504</v>
+        <v>-1.571336416000001</v>
       </c>
       <c r="P42">
-        <v>-5.94662016</v>
+        <v>-6.285345664000002</v>
       </c>
       <c r="Q42">
-        <v>-5.58962016</v>
+        <v>-5.928345664000002</v>
       </c>
       <c r="R42">
-        <v>0.6666666666666667</v>
+        <v>0.6949152542372882</v>
       </c>
       <c r="S42">
-        <v>0.1010576684769873</v>
+        <v>0.1019942391291396</v>
       </c>
       <c r="T42">
-        <v>1.077074809660731</v>
+        <v>1.095330314909218</v>
       </c>
       <c r="U42">
         <v>0.2008</v>
       </c>
       <c r="V42">
-        <v>0.1122206611286052</v>
+        <v>0.1094835718327856</v>
       </c>
       <c r="W42">
-        <v>0.1782660912453761</v>
+        <v>0.1788156987759767</v>
       </c>
       <c r="X42" t="inlineStr">
         <is>
@@ -4757,7 +4757,7 @@
         </is>
       </c>
       <c r="Y42">
-        <v>0.5611033056430259</v>
+        <v>0.5474178591639276</v>
       </c>
       <c r="Z42">
         <v>0</v>
@@ -4765,22 +4765,22 @@
     </row>
     <row r="43">
       <c r="A43">
-        <v>0.41</v>
+        <v>0.42</v>
       </c>
       <c r="B43">
-        <v>0.1334910375843428</v>
+        <v>0.1350410375843428</v>
       </c>
       <c r="C43">
-        <v>-1.843840635066684</v>
+        <v>-5.380646541964509</v>
       </c>
       <c r="D43">
-        <v>82.22875936493334</v>
+        <v>80.80055345803551</v>
       </c>
       <c r="E43">
-        <v>79.39260000000002</v>
+        <v>81.50120000000001</v>
       </c>
       <c r="F43">
-        <v>86.45260000000002</v>
+        <v>88.56120000000001</v>
       </c>
       <c r="G43">
         <v>2.38</v>
@@ -4801,37 +4801,37 @@
         <v>9.503</v>
       </c>
       <c r="M43">
-        <v>17.35968208</v>
+        <v>17.78308896</v>
       </c>
       <c r="N43">
-        <v>-7.856682080000002</v>
+        <v>-8.280088960000004</v>
       </c>
       <c r="O43">
-        <v>-1.571336416000001</v>
+        <v>-1.656017792000001</v>
       </c>
       <c r="P43">
-        <v>-6.285345664000002</v>
+        <v>-6.624071168000003</v>
       </c>
       <c r="Q43">
-        <v>-5.928345664000002</v>
+        <v>-6.267071168000003</v>
       </c>
       <c r="R43">
-        <v>0.6949152542372882</v>
+        <v>0.7241379310344829</v>
       </c>
       <c r="S43">
-        <v>0.1019942391291396</v>
+        <v>0.1029631053210213</v>
       </c>
       <c r="T43">
-        <v>1.095330314909218</v>
+        <v>1.114215320338688</v>
       </c>
       <c r="U43">
         <v>0.2008</v>
       </c>
       <c r="V43">
-        <v>0.1094835718327856</v>
+        <v>0.1068768201224811</v>
       </c>
       <c r="W43">
-        <v>0.1788156987759767</v>
+        <v>0.1793391345194058</v>
       </c>
       <c r="X43" t="inlineStr">
         <is>
@@ -4839,7 +4839,7 @@
         </is>
       </c>
       <c r="Y43">
-        <v>0.5474178591639276</v>
+        <v>0.5343841006124055</v>
       </c>
       <c r="Z43">
         <v>0</v>
@@ -4847,22 +4847,22 @@
     </row>
     <row r="44">
       <c r="A44">
-        <v>0.42</v>
+        <v>0.43</v>
       </c>
       <c r="B44">
-        <v>0.1350410375843428</v>
+        <v>0.1365910375843428</v>
       </c>
       <c r="C44">
-        <v>-5.380646541964467</v>
+        <v>-8.868687301671713</v>
       </c>
       <c r="D44">
-        <v>80.80055345803554</v>
+        <v>79.4211126983283</v>
       </c>
       <c r="E44">
-        <v>81.5012</v>
+        <v>83.60980000000001</v>
       </c>
       <c r="F44">
-        <v>88.5612</v>
+        <v>90.66980000000001</v>
       </c>
       <c r="G44">
         <v>2.38</v>
@@ -4883,37 +4883,37 @@
         <v>9.503</v>
       </c>
       <c r="M44">
-        <v>17.78308896</v>
+        <v>18.20649584</v>
       </c>
       <c r="N44">
-        <v>-8.28008896</v>
+        <v>-8.703495840000002</v>
       </c>
       <c r="O44">
-        <v>-1.656017792</v>
+        <v>-1.740699168000001</v>
       </c>
       <c r="P44">
-        <v>-6.624071168</v>
+        <v>-6.962796672000001</v>
       </c>
       <c r="Q44">
-        <v>-6.267071168</v>
+        <v>-6.605796672000001</v>
       </c>
       <c r="R44">
-        <v>0.7241379310344827</v>
+        <v>0.7543859649122806</v>
       </c>
       <c r="S44">
-        <v>0.1029631053210213</v>
+        <v>0.1039659668178813</v>
       </c>
       <c r="T44">
-        <v>1.114215320338688</v>
+        <v>1.133762957537612</v>
       </c>
       <c r="U44">
         <v>0.2008</v>
       </c>
       <c r="V44">
-        <v>0.1068768201224811</v>
+        <v>0.1043913126777723</v>
       </c>
       <c r="W44">
-        <v>0.1793391345194058</v>
+        <v>0.1798382244143033</v>
       </c>
       <c r="X44" t="inlineStr">
         <is>
@@ -4921,7 +4921,7 @@
         </is>
       </c>
       <c r="Y44">
-        <v>0.5343841006124057</v>
+        <v>0.5219565633888612</v>
       </c>
       <c r="Z44">
         <v>0</v>
@@ -4929,22 +4929,22 @@
     </row>
     <row r="45">
       <c r="A45">
-        <v>0.43</v>
+        <v>0.44</v>
       </c>
       <c r="B45">
-        <v>0.1365910375843428</v>
+        <v>0.1381410375843428</v>
       </c>
       <c r="C45">
-        <v>-8.868687301671713</v>
+        <v>-12.31041857139535</v>
       </c>
       <c r="D45">
-        <v>79.4211126983283</v>
+        <v>78.08798142860466</v>
       </c>
       <c r="E45">
-        <v>83.60980000000001</v>
+        <v>85.7184</v>
       </c>
       <c r="F45">
-        <v>90.66980000000001</v>
+        <v>92.7784</v>
       </c>
       <c r="G45">
         <v>2.38</v>
@@ -4965,37 +4965,37 @@
         <v>9.503</v>
       </c>
       <c r="M45">
-        <v>18.20649584</v>
+        <v>18.62990272</v>
       </c>
       <c r="N45">
-        <v>-8.703495840000002</v>
+        <v>-9.12690272</v>
       </c>
       <c r="O45">
-        <v>-1.740699168000001</v>
+        <v>-1.825380544</v>
       </c>
       <c r="P45">
-        <v>-6.962796672000001</v>
+        <v>-7.301522176000001</v>
       </c>
       <c r="Q45">
-        <v>-6.605796672000001</v>
+        <v>-6.944522176</v>
       </c>
       <c r="R45">
-        <v>0.7543859649122806</v>
+        <v>0.7857142857142857</v>
       </c>
       <c r="S45">
-        <v>0.1039659668178813</v>
+        <v>0.1050046447967721</v>
       </c>
       <c r="T45">
-        <v>1.133762957537612</v>
+        <v>1.154008724636498</v>
       </c>
       <c r="U45">
         <v>0.2008</v>
       </c>
       <c r="V45">
-        <v>0.1043913126777723</v>
+        <v>0.1020187828441865</v>
       </c>
       <c r="W45">
-        <v>0.1798382244143033</v>
+        <v>0.1803146284048874</v>
       </c>
       <c r="X45" t="inlineStr">
         <is>
@@ -5003,7 +5003,7 @@
         </is>
       </c>
       <c r="Y45">
-        <v>0.5219565633888612</v>
+        <v>0.5100939142209326</v>
       </c>
       <c r="Z45">
         <v>0</v>
@@ -5011,22 +5011,22 @@
     </row>
     <row r="46">
       <c r="A46">
-        <v>0.44</v>
+        <v>0.45</v>
       </c>
       <c r="B46">
-        <v>0.1381410375843428</v>
+        <v>0.1556723221667865</v>
       </c>
       <c r="C46">
-        <v>-12.31041857139535</v>
+        <v>-26.87877729766791</v>
       </c>
       <c r="D46">
-        <v>78.08798142860466</v>
+        <v>65.62822270233211</v>
       </c>
       <c r="E46">
-        <v>85.7184</v>
+        <v>87.82700000000001</v>
       </c>
       <c r="F46">
-        <v>92.7784</v>
+        <v>94.88700000000001</v>
       </c>
       <c r="G46">
         <v>2.38</v>
@@ -5047,45 +5047,45 @@
         <v>9.503</v>
       </c>
       <c r="M46">
-        <v>18.62990272</v>
+        <v>22.3743546</v>
       </c>
       <c r="N46">
-        <v>-9.12690272</v>
+        <v>-12.8713546</v>
       </c>
       <c r="O46">
-        <v>-1.825380544</v>
+        <v>-2.574270920000001</v>
       </c>
       <c r="P46">
-        <v>-7.301522176000001</v>
+        <v>-10.29708368</v>
       </c>
       <c r="Q46">
-        <v>-6.944522176</v>
+        <v>-9.940083680000004</v>
       </c>
       <c r="R46">
-        <v>0.7857142857142857</v>
+        <v>0.8181818181818181</v>
       </c>
       <c r="S46">
-        <v>0.1050046447967721</v>
+        <v>0.1065016103066111</v>
       </c>
       <c r="T46">
-        <v>1.154008724636498</v>
+        <v>1.183187368723698</v>
       </c>
       <c r="U46">
-        <v>0.2008</v>
+        <v>0.2358</v>
       </c>
       <c r="V46">
-        <v>0.1020187828441865</v>
+        <v>0.08494546698567117</v>
       </c>
       <c r="W46">
-        <v>0.1803146284048874</v>
+        <v>0.2157698588847787</v>
       </c>
       <c r="X46" t="inlineStr">
         <is>
-          <t>C2/C</t>
+          <t>D2/D</t>
         </is>
       </c>
       <c r="Y46">
-        <v>0.5100939142209326</v>
+        <v>0.4247273349283558</v>
       </c>
       <c r="Z46">
         <v>0</v>
@@ -5093,22 +5093,22 @@
     </row>
     <row r="47">
       <c r="A47">
-        <v>0.45</v>
+        <v>0.46</v>
       </c>
       <c r="B47">
-        <v>0.1556723221667865</v>
+        <v>0.1575723221667865</v>
       </c>
       <c r="C47">
-        <v>-26.87877729766791</v>
+        <v>-30.10298106000511</v>
       </c>
       <c r="D47">
-        <v>65.62822270233211</v>
+        <v>64.51261893999491</v>
       </c>
       <c r="E47">
-        <v>87.82700000000001</v>
+        <v>89.93560000000001</v>
       </c>
       <c r="F47">
-        <v>94.88700000000001</v>
+        <v>96.99560000000001</v>
       </c>
       <c r="G47">
         <v>2.38</v>
@@ -5129,37 +5129,37 @@
         <v>9.503</v>
       </c>
       <c r="M47">
-        <v>22.3743546</v>
+        <v>22.87156248000001</v>
       </c>
       <c r="N47">
-        <v>-12.8713546</v>
+        <v>-13.36856248</v>
       </c>
       <c r="O47">
-        <v>-2.574270920000001</v>
+        <v>-2.673712496000001</v>
       </c>
       <c r="P47">
-        <v>-10.29708368</v>
+        <v>-10.694849984</v>
       </c>
       <c r="Q47">
-        <v>-9.940083680000004</v>
+        <v>-10.33784998400001</v>
       </c>
       <c r="R47">
-        <v>0.8181818181818181</v>
+        <v>0.8518518518518519</v>
       </c>
       <c r="S47">
-        <v>0.1065016103066111</v>
+        <v>0.1076257142011779</v>
       </c>
       <c r="T47">
-        <v>1.183187368723698</v>
+        <v>1.205098245922285</v>
       </c>
       <c r="U47">
         <v>0.2358</v>
       </c>
       <c r="V47">
-        <v>0.08494546698567117</v>
+        <v>0.08309882639902615</v>
       </c>
       <c r="W47">
-        <v>0.2157698588847787</v>
+        <v>0.2162052967351097</v>
       </c>
       <c r="X47" t="inlineStr">
         <is>
@@ -5167,7 +5167,7 @@
         </is>
       </c>
       <c r="Y47">
-        <v>0.4247273349283558</v>
+        <v>0.4154941319951306</v>
       </c>
       <c r="Z47">
         <v>0</v>
@@ -5175,22 +5175,22 @@
     </row>
     <row r="48">
       <c r="A48">
-        <v>0.46</v>
+        <v>0.47</v>
       </c>
       <c r="B48">
-        <v>0.1575723221667865</v>
+        <v>0.1594723221667865</v>
       </c>
       <c r="C48">
-        <v>-30.10298106000511</v>
+        <v>-33.28989083365555</v>
       </c>
       <c r="D48">
-        <v>64.51261893999491</v>
+        <v>63.43430916634446</v>
       </c>
       <c r="E48">
-        <v>89.93560000000001</v>
+        <v>92.0442</v>
       </c>
       <c r="F48">
-        <v>96.99560000000001</v>
+        <v>99.10420000000001</v>
       </c>
       <c r="G48">
         <v>2.38</v>
@@ -5211,37 +5211,37 @@
         <v>9.503</v>
       </c>
       <c r="M48">
-        <v>22.87156248000001</v>
+        <v>23.36877036</v>
       </c>
       <c r="N48">
-        <v>-13.36856248</v>
+        <v>-13.86577036</v>
       </c>
       <c r="O48">
-        <v>-2.673712496000001</v>
+        <v>-2.773154072000001</v>
       </c>
       <c r="P48">
-        <v>-10.694849984</v>
+        <v>-11.092616288</v>
       </c>
       <c r="Q48">
-        <v>-10.33784998400001</v>
+        <v>-10.735616288</v>
       </c>
       <c r="R48">
-        <v>0.8518518518518519</v>
+        <v>0.8867924528301887</v>
       </c>
       <c r="S48">
-        <v>0.1076257142011779</v>
+        <v>0.1087922371106341</v>
       </c>
       <c r="T48">
-        <v>1.205098245922285</v>
+        <v>1.227835948675536</v>
       </c>
       <c r="U48">
         <v>0.2358</v>
       </c>
       <c r="V48">
-        <v>0.08309882639902615</v>
+        <v>0.08133076626287666</v>
       </c>
       <c r="W48">
-        <v>0.2162052967351097</v>
+        <v>0.2166222053152137</v>
       </c>
       <c r="X48" t="inlineStr">
         <is>
@@ -5249,7 +5249,7 @@
         </is>
       </c>
       <c r="Y48">
-        <v>0.4154941319951306</v>
+        <v>0.4066538313143833</v>
       </c>
       <c r="Z48">
         <v>0</v>
@@ -5257,22 +5257,22 @@
     </row>
     <row r="49">
       <c r="A49">
-        <v>0.47</v>
+        <v>0.48</v>
       </c>
       <c r="B49">
-        <v>0.1594723221667865</v>
+        <v>0.1613723221667865</v>
       </c>
       <c r="C49">
-        <v>-33.28989083365555</v>
+        <v>-36.44134594945155</v>
       </c>
       <c r="D49">
-        <v>63.43430916634446</v>
+        <v>62.39145405054847</v>
       </c>
       <c r="E49">
-        <v>92.0442</v>
+        <v>94.15280000000001</v>
       </c>
       <c r="F49">
-        <v>99.10420000000001</v>
+        <v>101.2128</v>
       </c>
       <c r="G49">
         <v>2.38</v>
@@ -5293,37 +5293,37 @@
         <v>9.503</v>
       </c>
       <c r="M49">
-        <v>23.36877036</v>
+        <v>23.86597824</v>
       </c>
       <c r="N49">
-        <v>-13.86577036</v>
+        <v>-14.36297824</v>
       </c>
       <c r="O49">
-        <v>-2.773154072000001</v>
+        <v>-2.872595648000001</v>
       </c>
       <c r="P49">
-        <v>-11.092616288</v>
+        <v>-11.490382592</v>
       </c>
       <c r="Q49">
-        <v>-10.735616288</v>
+        <v>-11.133382592</v>
       </c>
       <c r="R49">
-        <v>0.8867924528301887</v>
+        <v>0.9230769230769231</v>
       </c>
       <c r="S49">
-        <v>0.1087922371106341</v>
+        <v>0.1100036262858386</v>
       </c>
       <c r="T49">
-        <v>1.227835948675536</v>
+        <v>1.251448178457758</v>
       </c>
       <c r="U49">
         <v>0.2358</v>
       </c>
       <c r="V49">
-        <v>0.08133076626287666</v>
+        <v>0.07963637529906673</v>
       </c>
       <c r="W49">
-        <v>0.2166222053152137</v>
+        <v>0.2170217427044801</v>
       </c>
       <c r="X49" t="inlineStr">
         <is>
@@ -5331,7 +5331,7 @@
         </is>
       </c>
       <c r="Y49">
-        <v>0.4066538313143833</v>
+        <v>0.3981818764953335</v>
       </c>
       <c r="Z49">
         <v>0</v>
@@ -5339,22 +5339,22 @@
     </row>
     <row r="50">
       <c r="A50">
-        <v>0.48</v>
+        <v>0.49</v>
       </c>
       <c r="B50">
-        <v>0.1613723221667865</v>
+        <v>0.1632723221667865</v>
       </c>
       <c r="C50">
-        <v>-36.4413459494515</v>
+        <v>-39.55906674071107</v>
       </c>
       <c r="D50">
-        <v>62.3914540505485</v>
+        <v>61.38233325928893</v>
       </c>
       <c r="E50">
-        <v>94.1528</v>
+        <v>96.26140000000001</v>
       </c>
       <c r="F50">
-        <v>101.2128</v>
+        <v>103.3214</v>
       </c>
       <c r="G50">
         <v>2.38</v>
@@ -5375,37 +5375,37 @@
         <v>9.503</v>
       </c>
       <c r="M50">
-        <v>23.86597824</v>
+        <v>24.36318612000001</v>
       </c>
       <c r="N50">
-        <v>-14.36297824</v>
+        <v>-14.86018612000001</v>
       </c>
       <c r="O50">
-        <v>-2.872595648</v>
+        <v>-2.972037224000001</v>
       </c>
       <c r="P50">
-        <v>-11.490382592</v>
+        <v>-11.888148896</v>
       </c>
       <c r="Q50">
-        <v>-11.133382592</v>
+        <v>-11.531148896</v>
       </c>
       <c r="R50">
-        <v>0.923076923076923</v>
+        <v>0.9607843137254901</v>
       </c>
       <c r="S50">
-        <v>0.1100036262858386</v>
+        <v>0.1112625209188943</v>
       </c>
       <c r="T50">
-        <v>1.251448178457758</v>
+        <v>1.275986378035361</v>
       </c>
       <c r="U50">
         <v>0.2358</v>
       </c>
       <c r="V50">
-        <v>0.07963637529906674</v>
+        <v>0.07801114315010617</v>
       </c>
       <c r="W50">
-        <v>0.2170217427044801</v>
+        <v>0.217404972445205</v>
       </c>
       <c r="X50" t="inlineStr">
         <is>
@@ -5413,7 +5413,7 @@
         </is>
       </c>
       <c r="Y50">
-        <v>0.3981818764953337</v>
+        <v>0.3900557157505308</v>
       </c>
       <c r="Z50">
         <v>0</v>
@@ -5421,22 +5421,22 @@
     </row>
     <row r="51">
       <c r="A51">
-        <v>0.49</v>
+        <v>0.5</v>
       </c>
       <c r="B51">
-        <v>0.1632723221667865</v>
+        <v>0.1651723221667865</v>
       </c>
       <c r="C51">
-        <v>-39.55906674071107</v>
+        <v>-42.64466401340965</v>
       </c>
       <c r="D51">
-        <v>61.38233325928893</v>
+        <v>60.40533598659036</v>
       </c>
       <c r="E51">
-        <v>96.26140000000001</v>
+        <v>98.37</v>
       </c>
       <c r="F51">
-        <v>103.3214</v>
+        <v>105.43</v>
       </c>
       <c r="G51">
         <v>2.38</v>
@@ -5457,37 +5457,37 @@
         <v>9.503</v>
       </c>
       <c r="M51">
-        <v>24.36318612000001</v>
+        <v>24.860394</v>
       </c>
       <c r="N51">
-        <v>-14.86018612000001</v>
+        <v>-15.357394</v>
       </c>
       <c r="O51">
-        <v>-2.972037224000001</v>
+        <v>-3.071478800000001</v>
       </c>
       <c r="P51">
-        <v>-11.888148896</v>
+        <v>-12.2859152</v>
       </c>
       <c r="Q51">
-        <v>-11.531148896</v>
+        <v>-11.9289152</v>
       </c>
       <c r="R51">
-        <v>0.9607843137254901</v>
+        <v>1</v>
       </c>
       <c r="S51">
-        <v>0.1112625209188943</v>
+        <v>0.1125717713372722</v>
       </c>
       <c r="T51">
-        <v>1.275986378035361</v>
+        <v>1.301506105596068</v>
       </c>
       <c r="U51">
         <v>0.2358</v>
       </c>
       <c r="V51">
-        <v>0.07801114315010617</v>
+        <v>0.07645092028710405</v>
       </c>
       <c r="W51">
-        <v>0.217404972445205</v>
+        <v>0.2177728729963009</v>
       </c>
       <c r="X51" t="inlineStr">
         <is>
@@ -5495,7 +5495,7 @@
         </is>
       </c>
       <c r="Y51">
-        <v>0.3900557157505308</v>
+        <v>0.3822546014355203</v>
       </c>
       <c r="Z51">
         <v>0</v>
@@ -5503,22 +5503,22 @@
     </row>
     <row r="52">
       <c r="A52">
-        <v>0.5</v>
+        <v>0.51</v>
       </c>
       <c r="B52">
-        <v>0.1651723221667865</v>
+        <v>0.1670723221667865</v>
       </c>
       <c r="C52">
-        <v>-42.64466401340965</v>
+        <v>-45.6996476261245</v>
       </c>
       <c r="D52">
-        <v>60.40533598659036</v>
+        <v>59.4589523738755</v>
       </c>
       <c r="E52">
-        <v>98.37</v>
+        <v>100.4786</v>
       </c>
       <c r="F52">
-        <v>105.43</v>
+        <v>107.5386</v>
       </c>
       <c r="G52">
         <v>2.38</v>
@@ -5539,37 +5539,37 @@
         <v>9.503</v>
       </c>
       <c r="M52">
-        <v>24.860394</v>
+        <v>25.35760188</v>
       </c>
       <c r="N52">
-        <v>-15.357394</v>
+        <v>-15.85460188</v>
       </c>
       <c r="O52">
-        <v>-3.071478800000001</v>
+        <v>-3.170920376</v>
       </c>
       <c r="P52">
-        <v>-12.2859152</v>
+        <v>-12.683681504</v>
       </c>
       <c r="Q52">
-        <v>-11.9289152</v>
+        <v>-12.326681504</v>
       </c>
       <c r="R52">
-        <v>1</v>
+        <v>1.040816326530612</v>
       </c>
       <c r="S52">
-        <v>0.1125717713372722</v>
+        <v>0.1139344605482369</v>
       </c>
       <c r="T52">
-        <v>1.301506105596068</v>
+        <v>1.328067454689866</v>
       </c>
       <c r="U52">
         <v>0.2358</v>
       </c>
       <c r="V52">
-        <v>0.07645092028710405</v>
+        <v>0.07495188263441575</v>
       </c>
       <c r="W52">
-        <v>0.2177728729963009</v>
+        <v>0.2181263460748048</v>
       </c>
       <c r="X52" t="inlineStr">
         <is>
@@ -5577,7 +5577,7 @@
         </is>
       </c>
       <c r="Y52">
-        <v>0.3822546014355203</v>
+        <v>0.3747594131720787</v>
       </c>
       <c r="Z52">
         <v>0</v>
@@ -5585,22 +5585,22 @@
     </row>
     <row r="53">
       <c r="A53">
-        <v>0.51</v>
+        <v>0.52</v>
       </c>
       <c r="B53">
-        <v>0.1670723221667865</v>
+        <v>0.1689723221667865</v>
       </c>
       <c r="C53">
-        <v>-45.6996476261245</v>
+        <v>-48.72543427587679</v>
       </c>
       <c r="D53">
-        <v>59.4589523738755</v>
+        <v>58.54176572412322</v>
       </c>
       <c r="E53">
-        <v>100.4786</v>
+        <v>102.5872</v>
       </c>
       <c r="F53">
-        <v>107.5386</v>
+        <v>109.6472</v>
       </c>
       <c r="G53">
         <v>2.38</v>
@@ -5621,37 +5621,37 @@
         <v>9.503</v>
       </c>
       <c r="M53">
-        <v>25.35760188</v>
+        <v>25.85480976000001</v>
       </c>
       <c r="N53">
-        <v>-15.85460188</v>
+        <v>-16.35180976000001</v>
       </c>
       <c r="O53">
-        <v>-3.170920376</v>
+        <v>-3.270361952000001</v>
       </c>
       <c r="P53">
-        <v>-12.683681504</v>
+        <v>-13.081447808</v>
       </c>
       <c r="Q53">
-        <v>-12.326681504</v>
+        <v>-12.724447808</v>
       </c>
       <c r="R53">
-        <v>1.040816326530612</v>
+        <v>1.083333333333333</v>
       </c>
       <c r="S53">
-        <v>0.1139344605482369</v>
+        <v>0.1153539284763252</v>
       </c>
       <c r="T53">
-        <v>1.328067454689866</v>
+        <v>1.355735526662571</v>
       </c>
       <c r="U53">
         <v>0.2358</v>
       </c>
       <c r="V53">
-        <v>0.07495188263441575</v>
+        <v>0.07351050027606158</v>
       </c>
       <c r="W53">
-        <v>0.2181263460748048</v>
+        <v>0.2184662240349047</v>
       </c>
       <c r="X53" t="inlineStr">
         <is>
@@ -5659,7 +5659,7 @@
         </is>
       </c>
       <c r="Y53">
-        <v>0.3747594131720787</v>
+        <v>0.3675525013803079</v>
       </c>
       <c r="Z53">
         <v>0</v>
@@ -5667,22 +5667,22 @@
     </row>
     <row r="54">
       <c r="A54">
-        <v>0.52</v>
+        <v>0.53</v>
       </c>
       <c r="B54">
-        <v>0.1689723221667865</v>
+        <v>0.1708723221667865</v>
       </c>
       <c r="C54">
-        <v>-48.72543427587679</v>
+        <v>-51.72335457431586</v>
       </c>
       <c r="D54">
-        <v>58.54176572412322</v>
+        <v>57.65244542568415</v>
       </c>
       <c r="E54">
-        <v>102.5872</v>
+        <v>104.6958</v>
       </c>
       <c r="F54">
-        <v>109.6472</v>
+        <v>111.7558</v>
       </c>
       <c r="G54">
         <v>2.38</v>
@@ -5703,37 +5703,37 @@
         <v>9.503</v>
       </c>
       <c r="M54">
-        <v>25.85480976000001</v>
+        <v>26.35201764</v>
       </c>
       <c r="N54">
-        <v>-16.35180976000001</v>
+        <v>-16.84901764</v>
       </c>
       <c r="O54">
-        <v>-3.270361952000001</v>
+        <v>-3.369803528000001</v>
       </c>
       <c r="P54">
-        <v>-13.081447808</v>
+        <v>-13.479214112</v>
       </c>
       <c r="Q54">
-        <v>-12.724447808</v>
+        <v>-13.122214112</v>
       </c>
       <c r="R54">
-        <v>1.083333333333333</v>
+        <v>1.127659574468085</v>
       </c>
       <c r="S54">
-        <v>0.1153539284763252</v>
+        <v>0.1168337992949704</v>
       </c>
       <c r="T54">
-        <v>1.355735526662571</v>
+        <v>1.384580963400073</v>
       </c>
       <c r="U54">
         <v>0.2358</v>
       </c>
       <c r="V54">
-        <v>0.07351050027606158</v>
+        <v>0.07212350970481514</v>
       </c>
       <c r="W54">
-        <v>0.2184662240349047</v>
+        <v>0.2187932764116046</v>
       </c>
       <c r="X54" t="inlineStr">
         <is>
@@ -5741,7 +5741,7 @@
         </is>
       </c>
       <c r="Y54">
-        <v>0.3675525013803079</v>
+        <v>0.3606175485240757</v>
       </c>
       <c r="Z54">
         <v>0</v>
@@ -5749,22 +5749,22 @@
     </row>
     <row r="55">
       <c r="A55">
-        <v>0.53</v>
+        <v>0.54</v>
       </c>
       <c r="B55">
-        <v>0.1708723221667865</v>
+        <v>0.1727723221667865</v>
       </c>
       <c r="C55">
-        <v>-51.72335457431586</v>
+        <v>-54.69465948857987</v>
       </c>
       <c r="D55">
-        <v>57.65244542568415</v>
+        <v>56.78974051142015</v>
       </c>
       <c r="E55">
-        <v>104.6958</v>
+        <v>106.8044</v>
       </c>
       <c r="F55">
-        <v>111.7558</v>
+        <v>113.8644</v>
       </c>
       <c r="G55">
         <v>2.38</v>
@@ -5785,37 +5785,37 @@
         <v>9.503</v>
       </c>
       <c r="M55">
-        <v>26.35201764</v>
+        <v>26.84922552</v>
       </c>
       <c r="N55">
-        <v>-16.84901764</v>
+        <v>-17.34622552</v>
       </c>
       <c r="O55">
-        <v>-3.369803528000001</v>
+        <v>-3.469245104000001</v>
       </c>
       <c r="P55">
-        <v>-13.479214112</v>
+        <v>-13.876980416</v>
       </c>
       <c r="Q55">
-        <v>-13.122214112</v>
+        <v>-13.519980416</v>
       </c>
       <c r="R55">
-        <v>1.127659574468085</v>
+        <v>1.173913043478261</v>
       </c>
       <c r="S55">
-        <v>0.1168337992949704</v>
+        <v>0.1183780123231219</v>
       </c>
       <c r="T55">
-        <v>1.384580963400073</v>
+        <v>1.414680549560944</v>
       </c>
       <c r="U55">
         <v>0.2358</v>
       </c>
       <c r="V55">
-        <v>0.07212350970481514</v>
+        <v>0.07078788915472597</v>
       </c>
       <c r="W55">
-        <v>0.2187932764116046</v>
+        <v>0.2191082157373156</v>
       </c>
       <c r="X55" t="inlineStr">
         <is>
@@ -5823,7 +5823,7 @@
         </is>
       </c>
       <c r="Y55">
-        <v>0.3606175485240757</v>
+        <v>0.3539394457736298</v>
       </c>
       <c r="Z55">
         <v>0</v>
@@ -5831,22 +5831,22 @@
     </row>
     <row r="56">
       <c r="A56">
-        <v>0.54</v>
+        <v>0.55</v>
       </c>
       <c r="B56">
-        <v>0.1727723221667865</v>
+        <v>0.1746723221667865</v>
       </c>
       <c r="C56">
-        <v>-54.69465948857987</v>
+        <v>-57.64052621240016</v>
       </c>
       <c r="D56">
-        <v>56.78974051142015</v>
+        <v>55.95247378759985</v>
       </c>
       <c r="E56">
-        <v>106.8044</v>
+        <v>108.913</v>
       </c>
       <c r="F56">
-        <v>113.8644</v>
+        <v>115.973</v>
       </c>
       <c r="G56">
         <v>2.38</v>
@@ -5867,37 +5867,37 @@
         <v>9.503</v>
       </c>
       <c r="M56">
-        <v>26.84922552</v>
+        <v>27.34643340000001</v>
       </c>
       <c r="N56">
-        <v>-17.34622552</v>
+        <v>-17.84343340000001</v>
       </c>
       <c r="O56">
-        <v>-3.469245104000001</v>
+        <v>-3.568686680000001</v>
       </c>
       <c r="P56">
-        <v>-13.876980416</v>
+        <v>-14.27474672</v>
       </c>
       <c r="Q56">
-        <v>-13.519980416</v>
+        <v>-13.91774672000001</v>
       </c>
       <c r="R56">
-        <v>1.173913043478261</v>
+        <v>1.222222222222223</v>
       </c>
       <c r="S56">
-        <v>0.1183780123231219</v>
+        <v>0.1199908570414135</v>
       </c>
       <c r="T56">
-        <v>1.414680549560944</v>
+        <v>1.446117895106743</v>
       </c>
       <c r="U56">
         <v>0.2358</v>
       </c>
       <c r="V56">
-        <v>0.07078788915472597</v>
+        <v>0.06950083662464004</v>
       </c>
       <c r="W56">
-        <v>0.2191082157373156</v>
+        <v>0.2194117027239099</v>
       </c>
       <c r="X56" t="inlineStr">
         <is>
@@ -5905,7 +5905,7 @@
         </is>
       </c>
       <c r="Y56">
-        <v>0.3539394457736298</v>
+        <v>0.3475041831232002</v>
       </c>
       <c r="Z56">
         <v>0</v>
@@ -5913,22 +5913,22 @@
     </row>
     <row r="57">
       <c r="A57">
-        <v>0.55</v>
+        <v>0.5600000000000001</v>
       </c>
       <c r="B57">
-        <v>0.1746723221667865</v>
+        <v>0.1765723221667865</v>
       </c>
       <c r="C57">
-        <v>-57.64052621240016</v>
+        <v>-60.5620635253956</v>
       </c>
       <c r="D57">
-        <v>55.95247378759985</v>
+        <v>55.13953647460442</v>
       </c>
       <c r="E57">
-        <v>108.913</v>
+        <v>111.0216</v>
       </c>
       <c r="F57">
-        <v>115.973</v>
+        <v>118.0816</v>
       </c>
       <c r="G57">
         <v>2.38</v>
@@ -5949,37 +5949,37 @@
         <v>9.503</v>
       </c>
       <c r="M57">
-        <v>27.34643340000001</v>
+        <v>27.84364128000001</v>
       </c>
       <c r="N57">
-        <v>-17.84343340000001</v>
+        <v>-18.34064128000001</v>
       </c>
       <c r="O57">
-        <v>-3.568686680000001</v>
+        <v>-3.668128256000001</v>
       </c>
       <c r="P57">
-        <v>-14.27474672</v>
+        <v>-14.67251302400001</v>
       </c>
       <c r="Q57">
-        <v>-13.91774672000001</v>
+        <v>-14.31551302400001</v>
       </c>
       <c r="R57">
-        <v>1.222222222222223</v>
+        <v>1.272727272727273</v>
       </c>
       <c r="S57">
-        <v>0.1199908570414135</v>
+        <v>0.1216770128832639</v>
       </c>
       <c r="T57">
-        <v>1.446117895106743</v>
+        <v>1.478984210904623</v>
       </c>
       <c r="U57">
         <v>0.2358</v>
       </c>
       <c r="V57">
-        <v>0.06950083662464004</v>
+        <v>0.06825975025634289</v>
       </c>
       <c r="W57">
-        <v>0.2194117027239099</v>
+        <v>0.2197043508895543</v>
       </c>
       <c r="X57" t="inlineStr">
         <is>
@@ -5987,7 +5987,7 @@
         </is>
       </c>
       <c r="Y57">
-        <v>0.3475041831232002</v>
+        <v>0.3412987512817145</v>
       </c>
       <c r="Z57">
         <v>0</v>
@@ -5995,22 +5995,22 @@
     </row>
     <row r="58">
       <c r="A58">
-        <v>0.5600000000000001</v>
+        <v>0.5700000000000001</v>
       </c>
       <c r="B58">
-        <v>0.1765723221667865</v>
+        <v>0.1784723221667865</v>
       </c>
       <c r="C58">
-        <v>-60.5620635253956</v>
+        <v>-63.46031669186422</v>
       </c>
       <c r="D58">
-        <v>55.13953647460442</v>
+        <v>54.34988330813579</v>
       </c>
       <c r="E58">
-        <v>111.0216</v>
+        <v>113.1302</v>
       </c>
       <c r="F58">
-        <v>118.0816</v>
+        <v>120.1902</v>
       </c>
       <c r="G58">
         <v>2.38</v>
@@ -6031,37 +6031,37 @@
         <v>9.503</v>
       </c>
       <c r="M58">
-        <v>27.84364128000001</v>
+        <v>28.34084916</v>
       </c>
       <c r="N58">
-        <v>-18.34064128000001</v>
+        <v>-18.83784916</v>
       </c>
       <c r="O58">
-        <v>-3.668128256000001</v>
+        <v>-3.767569832000001</v>
       </c>
       <c r="P58">
-        <v>-14.67251302400001</v>
+        <v>-15.070279328</v>
       </c>
       <c r="Q58">
-        <v>-14.31551302400001</v>
+        <v>-14.713279328</v>
       </c>
       <c r="R58">
-        <v>1.272727272727273</v>
+        <v>1.325581395348838</v>
       </c>
       <c r="S58">
-        <v>0.1216770128832639</v>
+        <v>0.1234415945782235</v>
       </c>
       <c r="T58">
-        <v>1.478984210904623</v>
+        <v>1.513379192553568</v>
       </c>
       <c r="U58">
         <v>0.2358</v>
       </c>
       <c r="V58">
-        <v>0.06825975025634289</v>
+        <v>0.06706221077816145</v>
       </c>
       <c r="W58">
-        <v>0.2197043508895543</v>
+        <v>0.2199867306985095</v>
       </c>
       <c r="X58" t="inlineStr">
         <is>
@@ -6069,7 +6069,7 @@
         </is>
       </c>
       <c r="Y58">
-        <v>0.3412987512817145</v>
+        <v>0.3353110538908072</v>
       </c>
       <c r="Z58">
         <v>0</v>
@@ -6077,22 +6077,22 @@
     </row>
     <row r="59">
       <c r="A59">
-        <v>0.5700000000000001</v>
+        <v>0.5800000000000001</v>
       </c>
       <c r="B59">
-        <v>0.1784723221667865</v>
+        <v>0.1803723221667866</v>
       </c>
       <c r="C59">
-        <v>-63.46031669186422</v>
+        <v>-66.33627194458458</v>
       </c>
       <c r="D59">
-        <v>54.34988330813579</v>
+        <v>53.58252805541544</v>
       </c>
       <c r="E59">
-        <v>113.1302</v>
+        <v>115.2388</v>
       </c>
       <c r="F59">
-        <v>120.1902</v>
+        <v>122.2988</v>
       </c>
       <c r="G59">
         <v>2.38</v>
@@ -6113,37 +6113,37 @@
         <v>9.503</v>
       </c>
       <c r="M59">
-        <v>28.34084916</v>
+        <v>28.83805704000001</v>
       </c>
       <c r="N59">
-        <v>-18.83784916</v>
+        <v>-19.33505704000001</v>
       </c>
       <c r="O59">
-        <v>-3.767569832000001</v>
+        <v>-3.867011408000002</v>
       </c>
       <c r="P59">
-        <v>-15.070279328</v>
+        <v>-15.46804563200001</v>
       </c>
       <c r="Q59">
-        <v>-14.713279328</v>
+        <v>-15.11104563200001</v>
       </c>
       <c r="R59">
-        <v>1.325581395348838</v>
+        <v>1.380952380952381</v>
       </c>
       <c r="S59">
-        <v>0.1234415945782235</v>
+        <v>0.1252902039729431</v>
       </c>
       <c r="T59">
-        <v>1.513379192553568</v>
+        <v>1.54941203047151</v>
       </c>
       <c r="U59">
         <v>0.2358</v>
       </c>
       <c r="V59">
-        <v>0.06706221077816145</v>
+        <v>0.06590596576474486</v>
       </c>
       <c r="W59">
-        <v>0.2199867306985095</v>
+        <v>0.2202593732726732</v>
       </c>
       <c r="X59" t="inlineStr">
         <is>
@@ -6151,7 +6151,7 @@
         </is>
       </c>
       <c r="Y59">
-        <v>0.3353110538908072</v>
+        <v>0.3295298288237243</v>
       </c>
       <c r="Z59">
         <v>0</v>
@@ -6159,22 +6159,22 @@
     </row>
     <row r="60">
       <c r="A60">
-        <v>0.58</v>
+        <v>0.59</v>
       </c>
       <c r="B60">
-        <v>0.1803723221667865</v>
+        <v>0.1822723221667865</v>
       </c>
       <c r="C60">
-        <v>-66.33627194458454</v>
+        <v>-69.19086059406959</v>
       </c>
       <c r="D60">
-        <v>53.58252805541546</v>
+        <v>52.83653940593041</v>
       </c>
       <c r="E60">
-        <v>115.2388</v>
+        <v>117.3474</v>
       </c>
       <c r="F60">
-        <v>122.2988</v>
+        <v>124.4074</v>
       </c>
       <c r="G60">
         <v>2.38</v>
@@ -6195,37 +6195,37 @@
         <v>9.503</v>
       </c>
       <c r="M60">
-        <v>28.83805704</v>
+        <v>29.33526492</v>
       </c>
       <c r="N60">
-        <v>-19.33505704</v>
+        <v>-19.83226492</v>
       </c>
       <c r="O60">
-        <v>-3.867011408000001</v>
+        <v>-3.966452984</v>
       </c>
       <c r="P60">
-        <v>-15.468045632</v>
+        <v>-15.865811936</v>
       </c>
       <c r="Q60">
-        <v>-15.111045632</v>
+        <v>-15.508811936</v>
       </c>
       <c r="R60">
-        <v>1.380952380952381</v>
+        <v>1.439024390243902</v>
       </c>
       <c r="S60">
-        <v>0.1252902039729431</v>
+        <v>0.1272289894356978</v>
       </c>
       <c r="T60">
-        <v>1.54941203047151</v>
+        <v>1.587202567800083</v>
       </c>
       <c r="U60">
         <v>0.2358</v>
       </c>
       <c r="V60">
-        <v>0.06590596576474488</v>
+        <v>0.06478891549754581</v>
       </c>
       <c r="W60">
-        <v>0.2202593732726732</v>
+        <v>0.2205227737256787</v>
       </c>
       <c r="X60" t="inlineStr">
         <is>
@@ -6233,7 +6233,7 @@
         </is>
       </c>
       <c r="Y60">
-        <v>0.3295298288237244</v>
+        <v>0.3239445774877291</v>
       </c>
       <c r="Z60">
         <v>0</v>
@@ -6241,22 +6241,22 @@
     </row>
     <row r="61">
       <c r="A61">
-        <v>0.59</v>
+        <v>0.6</v>
       </c>
       <c r="B61">
-        <v>0.1822723221667865</v>
+        <v>0.1841723221667865</v>
       </c>
       <c r="C61">
-        <v>-69.19086059406959</v>
+        <v>-72.02496279927408</v>
       </c>
       <c r="D61">
-        <v>52.83653940593041</v>
+        <v>52.11103720072593</v>
       </c>
       <c r="E61">
-        <v>117.3474</v>
+        <v>119.456</v>
       </c>
       <c r="F61">
-        <v>124.4074</v>
+        <v>126.516</v>
       </c>
       <c r="G61">
         <v>2.38</v>
@@ -6277,37 +6277,37 @@
         <v>9.503</v>
       </c>
       <c r="M61">
-        <v>29.33526492</v>
+        <v>29.8324728</v>
       </c>
       <c r="N61">
-        <v>-19.83226492</v>
+        <v>-20.3294728</v>
       </c>
       <c r="O61">
-        <v>-3.966452984</v>
+        <v>-4.06589456</v>
       </c>
       <c r="P61">
-        <v>-15.865811936</v>
+        <v>-16.26357824</v>
       </c>
       <c r="Q61">
-        <v>-15.508811936</v>
+        <v>-15.90657824</v>
       </c>
       <c r="R61">
-        <v>1.439024390243902</v>
+        <v>1.5</v>
       </c>
       <c r="S61">
-        <v>0.1272289894356978</v>
+        <v>0.1292647141715902</v>
       </c>
       <c r="T61">
-        <v>1.587202567800083</v>
+        <v>1.626882631995085</v>
       </c>
       <c r="U61">
         <v>0.2358</v>
       </c>
       <c r="V61">
-        <v>0.06478891549754581</v>
+        <v>0.06370910023925339</v>
       </c>
       <c r="W61">
-        <v>0.2205227737256787</v>
+        <v>0.2207773941635841</v>
       </c>
       <c r="X61" t="inlineStr">
         <is>
@@ -6315,7 +6315,7 @@
         </is>
       </c>
       <c r="Y61">
-        <v>0.3239445774877291</v>
+        <v>0.3185455011962669</v>
       </c>
       <c r="Z61">
         <v>0</v>
@@ -6323,22 +6323,22 @@
     </row>
     <row r="62">
       <c r="A62">
-        <v>0.6</v>
+        <v>0.61</v>
       </c>
       <c r="B62">
-        <v>0.1841723221667865</v>
+        <v>0.1860723221667865</v>
       </c>
       <c r="C62">
-        <v>-72.02496279927408</v>
+        <v>-74.83941103185451</v>
       </c>
       <c r="D62">
-        <v>52.11103720072593</v>
+        <v>51.4051889681455</v>
       </c>
       <c r="E62">
-        <v>119.456</v>
+        <v>121.5646</v>
       </c>
       <c r="F62">
-        <v>126.516</v>
+        <v>128.6246</v>
       </c>
       <c r="G62">
         <v>2.38</v>
@@ -6359,37 +6359,37 @@
         <v>9.503</v>
       </c>
       <c r="M62">
-        <v>29.8324728</v>
+        <v>30.32968068000001</v>
       </c>
       <c r="N62">
-        <v>-20.3294728</v>
+        <v>-20.82668068000001</v>
       </c>
       <c r="O62">
-        <v>-4.06589456</v>
+        <v>-4.165336136000001</v>
       </c>
       <c r="P62">
-        <v>-16.26357824</v>
+        <v>-16.66134454400001</v>
       </c>
       <c r="Q62">
-        <v>-15.90657824</v>
+        <v>-16.30434454400001</v>
       </c>
       <c r="R62">
-        <v>1.5</v>
+        <v>1.564102564102564</v>
       </c>
       <c r="S62">
-        <v>0.1292647141715902</v>
+        <v>0.1314048350477849</v>
       </c>
       <c r="T62">
-        <v>1.626882631995085</v>
+        <v>1.668597571277011</v>
       </c>
       <c r="U62">
         <v>0.2358</v>
       </c>
       <c r="V62">
-        <v>0.06370910023925339</v>
+        <v>0.06266468875992136</v>
       </c>
       <c r="W62">
-        <v>0.2207773941635841</v>
+        <v>0.2210236663904105</v>
       </c>
       <c r="X62" t="inlineStr">
         <is>
@@ -6397,7 +6397,7 @@
         </is>
       </c>
       <c r="Y62">
-        <v>0.3185455011962669</v>
+        <v>0.3133234437996067</v>
       </c>
       <c r="Z62">
         <v>0</v>
@@ -6405,22 +6405,22 @@
     </row>
     <row r="63">
       <c r="A63">
-        <v>0.61</v>
+        <v>0.62</v>
       </c>
       <c r="B63">
-        <v>0.1860723221667865</v>
+        <v>0.1879723221667865</v>
       </c>
       <c r="C63">
-        <v>-74.83941103185451</v>
+        <v>-77.63499326264974</v>
       </c>
       <c r="D63">
-        <v>51.4051889681455</v>
+        <v>50.71820673735027</v>
       </c>
       <c r="E63">
-        <v>121.5646</v>
+        <v>123.6732</v>
       </c>
       <c r="F63">
-        <v>128.6246</v>
+        <v>130.7332</v>
       </c>
       <c r="G63">
         <v>2.38</v>
@@ -6441,37 +6441,37 @@
         <v>9.503</v>
       </c>
       <c r="M63">
-        <v>30.32968068000001</v>
+        <v>30.82688856</v>
       </c>
       <c r="N63">
-        <v>-20.82668068000001</v>
+        <v>-21.32388856</v>
       </c>
       <c r="O63">
-        <v>-4.165336136000001</v>
+        <v>-4.264777712000001</v>
       </c>
       <c r="P63">
-        <v>-16.66134454400001</v>
+        <v>-17.059110848</v>
       </c>
       <c r="Q63">
-        <v>-16.30434454400001</v>
+        <v>-16.702110848</v>
       </c>
       <c r="R63">
-        <v>1.564102564102564</v>
+        <v>1.631578947368421</v>
       </c>
       <c r="S63">
-        <v>0.1314048350477849</v>
+        <v>0.1336575938648318</v>
       </c>
       <c r="T63">
-        <v>1.668597571277011</v>
+        <v>1.712508033679037</v>
       </c>
       <c r="U63">
         <v>0.2358</v>
       </c>
       <c r="V63">
-        <v>0.06266468875992136</v>
+        <v>0.061653967973471</v>
       </c>
       <c r="W63">
-        <v>0.2210236663904105</v>
+        <v>0.2212619943518555</v>
       </c>
       <c r="X63" t="inlineStr">
         <is>
@@ -6479,7 +6479,7 @@
         </is>
       </c>
       <c r="Y63">
-        <v>0.3133234437996067</v>
+        <v>0.308269839867355</v>
       </c>
       <c r="Z63">
         <v>0</v>
@@ -6487,22 +6487,22 @@
     </row>
     <row r="64">
       <c r="A64">
-        <v>0.62</v>
+        <v>0.63</v>
       </c>
       <c r="B64">
-        <v>0.1879723221667865</v>
+        <v>0.1898723221667865</v>
       </c>
       <c r="C64">
-        <v>-77.63499326264974</v>
+        <v>-80.41245589602498</v>
       </c>
       <c r="D64">
-        <v>50.71820673735027</v>
+        <v>50.04934410397502</v>
       </c>
       <c r="E64">
-        <v>123.6732</v>
+        <v>125.7818</v>
       </c>
       <c r="F64">
-        <v>130.7332</v>
+        <v>132.8418</v>
       </c>
       <c r="G64">
         <v>2.38</v>
@@ -6523,37 +6523,37 @@
         <v>9.503</v>
       </c>
       <c r="M64">
-        <v>30.82688856</v>
+        <v>31.32409644</v>
       </c>
       <c r="N64">
-        <v>-21.32388856</v>
+        <v>-21.82109644</v>
       </c>
       <c r="O64">
-        <v>-4.264777712000001</v>
+        <v>-4.364219288</v>
       </c>
       <c r="P64">
-        <v>-17.059110848</v>
+        <v>-17.456877152</v>
       </c>
       <c r="Q64">
-        <v>-16.702110848</v>
+        <v>-17.099877152</v>
       </c>
       <c r="R64">
-        <v>1.631578947368421</v>
+        <v>1.702702702702703</v>
       </c>
       <c r="S64">
-        <v>0.1336575938648318</v>
+        <v>0.1360321234287462</v>
       </c>
       <c r="T64">
-        <v>1.712508033679037</v>
+        <v>1.758792034589281</v>
       </c>
       <c r="U64">
         <v>0.2358</v>
       </c>
       <c r="V64">
-        <v>0.061653967973471</v>
+        <v>0.06067533356119369</v>
       </c>
       <c r="W64">
-        <v>0.2212619943518555</v>
+        <v>0.2214927563462705</v>
       </c>
       <c r="X64" t="inlineStr">
         <is>
@@ -6561,7 +6561,7 @@
         </is>
       </c>
       <c r="Y64">
-        <v>0.308269839867355</v>
+        <v>0.3033766678059685</v>
       </c>
       <c r="Z64">
         <v>0</v>
@@ -6569,22 +6569,22 @@
     </row>
     <row r="65">
       <c r="A65">
-        <v>0.63</v>
+        <v>0.64</v>
       </c>
       <c r="B65">
-        <v>0.1898723221667865</v>
+        <v>0.1917723221667866</v>
       </c>
       <c r="C65">
-        <v>-80.41245589602498</v>
+        <v>-83.17250647505256</v>
       </c>
       <c r="D65">
-        <v>50.04934410397502</v>
+        <v>49.39789352494745</v>
       </c>
       <c r="E65">
-        <v>125.7818</v>
+        <v>127.8904</v>
       </c>
       <c r="F65">
-        <v>132.8418</v>
+        <v>134.9504</v>
       </c>
       <c r="G65">
         <v>2.38</v>
@@ -6605,37 +6605,37 @@
         <v>9.503</v>
       </c>
       <c r="M65">
-        <v>31.32409644</v>
+        <v>31.82130432</v>
       </c>
       <c r="N65">
-        <v>-21.82109644</v>
+        <v>-22.31830432</v>
       </c>
       <c r="O65">
-        <v>-4.364219288</v>
+        <v>-4.463660864</v>
       </c>
       <c r="P65">
-        <v>-17.456877152</v>
+        <v>-17.854643456</v>
       </c>
       <c r="Q65">
-        <v>-17.099877152</v>
+        <v>-17.497643456</v>
       </c>
       <c r="R65">
-        <v>1.702702702702703</v>
+        <v>1.777777777777778</v>
       </c>
       <c r="S65">
-        <v>0.1360321234287462</v>
+        <v>0.1385385713017669</v>
       </c>
       <c r="T65">
-        <v>1.758792034589281</v>
+        <v>1.807647368883428</v>
       </c>
       <c r="U65">
         <v>0.2358</v>
       </c>
       <c r="V65">
-        <v>0.06067533356119369</v>
+        <v>0.05972728147430004</v>
       </c>
       <c r="W65">
-        <v>0.2214927563462705</v>
+        <v>0.2217163070283601</v>
       </c>
       <c r="X65" t="inlineStr">
         <is>
@@ -6643,7 +6643,7 @@
         </is>
       </c>
       <c r="Y65">
-        <v>0.3033766678059685</v>
+        <v>0.2986364073715002</v>
       </c>
       <c r="Z65">
         <v>0</v>
@@ -6651,22 +6651,22 @@
     </row>
     <row r="66">
       <c r="A66">
-        <v>0.64</v>
+        <v>0.65</v>
       </c>
       <c r="B66">
-        <v>0.1917723221667866</v>
+        <v>0.1936723221667865</v>
       </c>
       <c r="C66">
-        <v>-83.17250647505256</v>
+        <v>-85.91581617814047</v>
       </c>
       <c r="D66">
-        <v>49.39789352494745</v>
+        <v>48.76318382185955</v>
       </c>
       <c r="E66">
-        <v>127.8904</v>
+        <v>129.999</v>
       </c>
       <c r="F66">
-        <v>134.9504</v>
+        <v>137.059</v>
       </c>
       <c r="G66">
         <v>2.38</v>
@@ -6687,37 +6687,37 @@
         <v>9.503</v>
       </c>
       <c r="M66">
-        <v>31.82130432</v>
+        <v>32.31851220000001</v>
       </c>
       <c r="N66">
-        <v>-22.31830432</v>
+        <v>-22.81551220000001</v>
       </c>
       <c r="O66">
-        <v>-4.463660864</v>
+        <v>-4.563102440000002</v>
       </c>
       <c r="P66">
-        <v>-17.854643456</v>
+        <v>-18.25240976000001</v>
       </c>
       <c r="Q66">
-        <v>-17.497643456</v>
+        <v>-17.89540976000001</v>
       </c>
       <c r="R66">
-        <v>1.777777777777778</v>
+        <v>1.857142857142857</v>
       </c>
       <c r="S66">
-        <v>0.1385385713017669</v>
+        <v>0.1411882447675317</v>
       </c>
       <c r="T66">
-        <v>1.807647368883428</v>
+        <v>1.859294436565812</v>
       </c>
       <c r="U66">
         <v>0.2358</v>
       </c>
       <c r="V66">
-        <v>0.05972728147430004</v>
+        <v>0.05880840022084927</v>
       </c>
       <c r="W66">
-        <v>0.2217163070283601</v>
+        <v>0.2219329792279237</v>
       </c>
       <c r="X66" t="inlineStr">
         <is>
@@ -6725,7 +6725,7 @@
         </is>
       </c>
       <c r="Y66">
-        <v>0.2986364073715002</v>
+        <v>0.2940420011042463</v>
       </c>
       <c r="Z66">
         <v>0</v>
@@ -6733,22 +6733,22 @@
     </row>
     <row r="67">
       <c r="A67">
-        <v>0.65</v>
+        <v>0.66</v>
       </c>
       <c r="B67">
-        <v>0.1936723221667865</v>
+        <v>0.1955723221667865</v>
       </c>
       <c r="C67">
-        <v>-85.91581617814047</v>
+        <v>-88.64302212562896</v>
       </c>
       <c r="D67">
-        <v>48.76318382185955</v>
+        <v>48.14457787437106</v>
       </c>
       <c r="E67">
-        <v>129.999</v>
+        <v>132.1076</v>
       </c>
       <c r="F67">
-        <v>137.059</v>
+        <v>139.1676</v>
       </c>
       <c r="G67">
         <v>2.38</v>
@@ -6769,37 +6769,37 @@
         <v>9.503</v>
       </c>
       <c r="M67">
-        <v>32.31851220000001</v>
+        <v>32.81572008000001</v>
       </c>
       <c r="N67">
-        <v>-22.81551220000001</v>
+        <v>-23.31272008000001</v>
       </c>
       <c r="O67">
-        <v>-4.563102440000002</v>
+        <v>-4.662544016000001</v>
       </c>
       <c r="P67">
-        <v>-18.25240976000001</v>
+        <v>-18.650176064</v>
       </c>
       <c r="Q67">
-        <v>-17.89540976000001</v>
+        <v>-18.293176064</v>
       </c>
       <c r="R67">
-        <v>1.857142857142857</v>
+        <v>1.941176470588236</v>
       </c>
       <c r="S67">
-        <v>0.1411882447675317</v>
+        <v>0.1439937813783415</v>
       </c>
       <c r="T67">
-        <v>1.859294436565812</v>
+        <v>1.913979567053042</v>
       </c>
       <c r="U67">
         <v>0.2358</v>
       </c>
       <c r="V67">
-        <v>0.05880840022084927</v>
+        <v>0.0579173638538667</v>
       </c>
       <c r="W67">
-        <v>0.2219329792279237</v>
+        <v>0.2221430856032582</v>
       </c>
       <c r="X67" t="inlineStr">
         <is>
@@ -6807,7 +6807,7 @@
         </is>
       </c>
       <c r="Y67">
-        <v>0.2940420011042463</v>
+        <v>0.2895868192693335</v>
       </c>
       <c r="Z67">
         <v>0</v>
@@ -6815,22 +6815,22 @@
     </row>
     <row r="68">
       <c r="A68">
-        <v>0.66</v>
+        <v>0.67</v>
       </c>
       <c r="B68">
-        <v>0.1955723221667865</v>
+        <v>0.1974723221667865</v>
       </c>
       <c r="C68">
-        <v>-88.64302212562896</v>
+        <v>-91.35472951301843</v>
       </c>
       <c r="D68">
-        <v>48.14457787437106</v>
+        <v>47.54147048698159</v>
       </c>
       <c r="E68">
-        <v>132.1076</v>
+        <v>134.2162</v>
       </c>
       <c r="F68">
-        <v>139.1676</v>
+        <v>141.2762</v>
       </c>
       <c r="G68">
         <v>2.38</v>
@@ -6851,37 +6851,37 @@
         <v>9.503</v>
       </c>
       <c r="M68">
-        <v>32.81572008000001</v>
+        <v>33.31292796</v>
       </c>
       <c r="N68">
-        <v>-23.31272008000001</v>
+        <v>-23.80992796</v>
       </c>
       <c r="O68">
-        <v>-4.662544016000001</v>
+        <v>-4.761985592000001</v>
       </c>
       <c r="P68">
-        <v>-18.650176064</v>
+        <v>-19.047942368</v>
       </c>
       <c r="Q68">
-        <v>-18.293176064</v>
+        <v>-18.690942368</v>
       </c>
       <c r="R68">
-        <v>1.941176470588236</v>
+        <v>2.030303030303031</v>
       </c>
       <c r="S68">
-        <v>0.1439937813783415</v>
+        <v>0.1469693505110185</v>
       </c>
       <c r="T68">
-        <v>1.913979567053042</v>
+        <v>1.971978947872831</v>
       </c>
       <c r="U68">
         <v>0.2358</v>
       </c>
       <c r="V68">
-        <v>0.0579173638538667</v>
+        <v>0.05705292558739108</v>
       </c>
       <c r="W68">
-        <v>0.2221430856032582</v>
+        <v>0.2223469201464932</v>
       </c>
       <c r="X68" t="inlineStr">
         <is>
@@ -6889,7 +6889,7 @@
         </is>
       </c>
       <c r="Y68">
-        <v>0.2895868192693335</v>
+        <v>0.2852646279369554</v>
       </c>
       <c r="Z68">
         <v>0</v>
@@ -6897,22 +6897,22 @@
     </row>
     <row r="69">
       <c r="A69">
-        <v>0.67</v>
+        <v>0.68</v>
       </c>
       <c r="B69">
-        <v>0.1974723221667865</v>
+        <v>0.1993723221667865</v>
       </c>
       <c r="C69">
-        <v>-91.35472951301843</v>
+        <v>-94.05151358584348</v>
       </c>
       <c r="D69">
-        <v>47.54147048698159</v>
+        <v>46.95328641415653</v>
       </c>
       <c r="E69">
-        <v>134.2162</v>
+        <v>136.3248</v>
       </c>
       <c r="F69">
-        <v>141.2762</v>
+        <v>143.3848</v>
       </c>
       <c r="G69">
         <v>2.38</v>
@@ -6933,37 +6933,37 @@
         <v>9.503</v>
       </c>
       <c r="M69">
-        <v>33.31292796</v>
+        <v>33.81013584</v>
       </c>
       <c r="N69">
-        <v>-23.80992796</v>
+        <v>-24.30713584</v>
       </c>
       <c r="O69">
-        <v>-4.761985592000001</v>
+        <v>-4.861427168000001</v>
       </c>
       <c r="P69">
-        <v>-19.047942368</v>
+        <v>-19.445708672</v>
       </c>
       <c r="Q69">
-        <v>-18.690942368</v>
+        <v>-19.088708672</v>
       </c>
       <c r="R69">
-        <v>2.030303030303031</v>
+        <v>2.125</v>
       </c>
       <c r="S69">
-        <v>0.1469693505110185</v>
+        <v>0.1501308927144878</v>
       </c>
       <c r="T69">
-        <v>1.971978947872831</v>
+        <v>2.033603289993857</v>
       </c>
       <c r="U69">
         <v>0.2358</v>
       </c>
       <c r="V69">
-        <v>0.05705292558739108</v>
+        <v>0.0562139119758118</v>
       </c>
       <c r="W69">
-        <v>0.2223469201464932</v>
+        <v>0.2225447595561036</v>
       </c>
       <c r="X69" t="inlineStr">
         <is>
@@ -6971,7 +6971,7 @@
         </is>
       </c>
       <c r="Y69">
-        <v>0.2852646279369554</v>
+        <v>0.281069559879059</v>
       </c>
       <c r="Z69">
         <v>0</v>
@@ -6979,22 +6979,22 @@
     </row>
     <row r="70">
       <c r="A70">
-        <v>0.68</v>
+        <v>0.6900000000000001</v>
       </c>
       <c r="B70">
-        <v>0.1993723221667865</v>
+        <v>0.2012723221667865</v>
       </c>
       <c r="C70">
-        <v>-94.05151358584348</v>
+        <v>-96.73392146973933</v>
       </c>
       <c r="D70">
-        <v>46.95328641415653</v>
+        <v>46.37947853026068</v>
       </c>
       <c r="E70">
-        <v>136.3248</v>
+        <v>138.4334</v>
       </c>
       <c r="F70">
-        <v>143.3848</v>
+        <v>145.4934</v>
       </c>
       <c r="G70">
         <v>2.38</v>
@@ -7015,37 +7015,37 @@
         <v>9.503</v>
       </c>
       <c r="M70">
-        <v>33.81013584</v>
+        <v>34.30734372000001</v>
       </c>
       <c r="N70">
-        <v>-24.30713584</v>
+        <v>-24.80434372000001</v>
       </c>
       <c r="O70">
-        <v>-4.861427168000001</v>
+        <v>-4.960868744000002</v>
       </c>
       <c r="P70">
-        <v>-19.445708672</v>
+        <v>-19.843474976</v>
       </c>
       <c r="Q70">
-        <v>-19.088708672</v>
+        <v>-19.486474976</v>
       </c>
       <c r="R70">
-        <v>2.125</v>
+        <v>2.225806451612904</v>
       </c>
       <c r="S70">
-        <v>0.1501308927144878</v>
+        <v>0.1534964053826971</v>
       </c>
       <c r="T70">
-        <v>2.033603289993857</v>
+        <v>2.099203396122691</v>
       </c>
       <c r="U70">
         <v>0.2358</v>
       </c>
       <c r="V70">
-        <v>0.0562139119758118</v>
+        <v>0.05539921759935076</v>
       </c>
       <c r="W70">
-        <v>0.2225447595561036</v>
+        <v>0.2227368644900731</v>
       </c>
       <c r="X70" t="inlineStr">
         <is>
@@ -7053,7 +7053,7 @@
         </is>
       </c>
       <c r="Y70">
-        <v>0.281069559879059</v>
+        <v>0.2769960879967538</v>
       </c>
       <c r="Z70">
         <v>0</v>
@@ -7061,22 +7061,22 @@
     </row>
     <row r="71">
       <c r="A71">
-        <v>0.6900000000000001</v>
+        <v>0.7000000000000001</v>
       </c>
       <c r="B71">
-        <v>0.2012723221667865</v>
+        <v>0.2031723221667865</v>
       </c>
       <c r="C71">
-        <v>-96.73392146973933</v>
+        <v>-99.40247386793871</v>
       </c>
       <c r="D71">
-        <v>46.37947853026068</v>
+        <v>45.81952613206131</v>
       </c>
       <c r="E71">
-        <v>138.4334</v>
+        <v>140.542</v>
       </c>
       <c r="F71">
-        <v>145.4934</v>
+        <v>147.602</v>
       </c>
       <c r="G71">
         <v>2.38</v>
@@ -7097,37 +7097,37 @@
         <v>9.503</v>
       </c>
       <c r="M71">
-        <v>34.30734372000001</v>
+        <v>34.80455160000001</v>
       </c>
       <c r="N71">
-        <v>-24.80434372000001</v>
+        <v>-25.30155160000001</v>
       </c>
       <c r="O71">
-        <v>-4.960868744000002</v>
+        <v>-5.060310320000003</v>
       </c>
       <c r="P71">
-        <v>-19.843474976</v>
+        <v>-20.24124128000001</v>
       </c>
       <c r="Q71">
-        <v>-19.486474976</v>
+        <v>-19.88424128000001</v>
       </c>
       <c r="R71">
-        <v>2.225806451612904</v>
+        <v>2.333333333333334</v>
       </c>
       <c r="S71">
-        <v>0.1534964053826971</v>
+        <v>0.1570862855621203</v>
       </c>
       <c r="T71">
-        <v>2.099203396122691</v>
+        <v>2.169176842660114</v>
       </c>
       <c r="U71">
         <v>0.2358</v>
       </c>
       <c r="V71">
-        <v>0.05539921759935076</v>
+        <v>0.05460780020507431</v>
       </c>
       <c r="W71">
-        <v>0.2227368644900731</v>
+        <v>0.2229234807116435</v>
       </c>
       <c r="X71" t="inlineStr">
         <is>
@@ -7135,7 +7135,7 @@
         </is>
       </c>
       <c r="Y71">
-        <v>0.2769960879967538</v>
+        <v>0.2730390010253716</v>
       </c>
       <c r="Z71">
         <v>0</v>
@@ -7143,22 +7143,22 @@
     </row>
     <row r="72">
       <c r="A72">
-        <v>0.7000000000000001</v>
+        <v>0.7100000000000001</v>
       </c>
       <c r="B72">
-        <v>0.2031723221667865</v>
+        <v>0.2050723221667865</v>
       </c>
       <c r="C72">
-        <v>-99.40247386793871</v>
+        <v>-102.0576666372697</v>
       </c>
       <c r="D72">
-        <v>45.81952613206131</v>
+        <v>45.27293336273036</v>
       </c>
       <c r="E72">
-        <v>140.542</v>
+        <v>142.6506</v>
       </c>
       <c r="F72">
-        <v>147.602</v>
+        <v>149.7106</v>
       </c>
       <c r="G72">
         <v>2.38</v>
@@ -7179,37 +7179,37 @@
         <v>9.503</v>
       </c>
       <c r="M72">
-        <v>34.80455160000001</v>
+        <v>35.30175948000001</v>
       </c>
       <c r="N72">
-        <v>-25.30155160000001</v>
+        <v>-25.79875948000001</v>
       </c>
       <c r="O72">
-        <v>-5.060310320000003</v>
+        <v>-5.159751896000002</v>
       </c>
       <c r="P72">
-        <v>-20.24124128000001</v>
+        <v>-20.63900758400001</v>
       </c>
       <c r="Q72">
-        <v>-19.88424128000001</v>
+        <v>-20.28200758400001</v>
       </c>
       <c r="R72">
-        <v>2.333333333333334</v>
+        <v>2.448275862068967</v>
       </c>
       <c r="S72">
-        <v>0.1570862855621203</v>
+        <v>0.160923743684952</v>
       </c>
       <c r="T72">
-        <v>2.169176842660114</v>
+        <v>2.243976044131152</v>
       </c>
       <c r="U72">
         <v>0.2358</v>
       </c>
       <c r="V72">
-        <v>0.05460780020507431</v>
+        <v>0.05383867625852398</v>
       </c>
       <c r="W72">
-        <v>0.2229234807116435</v>
+        <v>0.2231048401382401</v>
       </c>
       <c r="X72" t="inlineStr">
         <is>
@@ -7217,7 +7217,7 @@
         </is>
       </c>
       <c r="Y72">
-        <v>0.2730390010253716</v>
+        <v>0.2691933812926198</v>
       </c>
       <c r="Z72">
         <v>0</v>
@@ -7225,22 +7225,22 @@
     </row>
     <row r="73">
       <c r="A73">
-        <v>0.71</v>
+        <v>0.72</v>
       </c>
       <c r="B73">
-        <v>0.2050723221667865</v>
+        <v>0.2069723221667865</v>
       </c>
       <c r="C73">
-        <v>-102.0576666372696</v>
+        <v>-104.6999722526803</v>
       </c>
       <c r="D73">
-        <v>45.27293336273036</v>
+        <v>44.7392277473197</v>
       </c>
       <c r="E73">
-        <v>142.6506</v>
+        <v>144.7592</v>
       </c>
       <c r="F73">
-        <v>149.7106</v>
+        <v>151.8192</v>
       </c>
       <c r="G73">
         <v>2.38</v>
@@ -7261,37 +7261,37 @@
         <v>9.503</v>
       </c>
       <c r="M73">
-        <v>35.30175948</v>
+        <v>35.79896736</v>
       </c>
       <c r="N73">
-        <v>-25.79875948</v>
+        <v>-26.29596736</v>
       </c>
       <c r="O73">
-        <v>-5.159751896</v>
+        <v>-5.259193472</v>
       </c>
       <c r="P73">
-        <v>-20.639007584</v>
+        <v>-21.036773888</v>
       </c>
       <c r="Q73">
-        <v>-20.282007584</v>
+        <v>-20.679773888</v>
       </c>
       <c r="R73">
-        <v>2.448275862068965</v>
+        <v>2.571428571428571</v>
       </c>
       <c r="S73">
-        <v>0.160923743684952</v>
+        <v>0.1650353059594146</v>
       </c>
       <c r="T73">
-        <v>2.243976044131152</v>
+        <v>2.324118045707265</v>
       </c>
       <c r="U73">
         <v>0.2358</v>
       </c>
       <c r="V73">
-        <v>0.05383867625852399</v>
+        <v>0.05309091686604449</v>
       </c>
       <c r="W73">
-        <v>0.2231048401382401</v>
+        <v>0.2232811618029867</v>
       </c>
       <c r="X73" t="inlineStr">
         <is>
@@ -7299,7 +7299,7 @@
         </is>
       </c>
       <c r="Y73">
-        <v>0.2691933812926199</v>
+        <v>0.2654545843302224</v>
       </c>
       <c r="Z73">
         <v>0</v>
@@ -7307,22 +7307,22 @@
     </row>
     <row r="74">
       <c r="A74">
-        <v>0.72</v>
+        <v>0.73</v>
       </c>
       <c r="B74">
-        <v>0.2069723221667865</v>
+        <v>0.2088723221667865</v>
       </c>
       <c r="C74">
-        <v>-104.6999722526803</v>
+        <v>-107.329841169382</v>
       </c>
       <c r="D74">
-        <v>44.7392277473197</v>
+        <v>44.21795883061802</v>
       </c>
       <c r="E74">
-        <v>144.7592</v>
+        <v>146.8678</v>
       </c>
       <c r="F74">
-        <v>151.8192</v>
+        <v>153.9278</v>
       </c>
       <c r="G74">
         <v>2.38</v>
@@ -7343,37 +7343,37 @@
         <v>9.503</v>
       </c>
       <c r="M74">
-        <v>35.79896736</v>
+        <v>36.29617524</v>
       </c>
       <c r="N74">
-        <v>-26.29596736</v>
+        <v>-26.79317524</v>
       </c>
       <c r="O74">
-        <v>-5.259193472</v>
+        <v>-5.358635048000001</v>
       </c>
       <c r="P74">
-        <v>-21.036773888</v>
+        <v>-21.434540192</v>
       </c>
       <c r="Q74">
-        <v>-20.679773888</v>
+        <v>-21.077540192</v>
       </c>
       <c r="R74">
-        <v>2.571428571428571</v>
+        <v>2.703703703703703</v>
       </c>
       <c r="S74">
-        <v>0.1650353059594146</v>
+        <v>0.1694514284023559</v>
       </c>
       <c r="T74">
-        <v>2.324118045707265</v>
+        <v>2.41019649184457</v>
       </c>
       <c r="U74">
         <v>0.2358</v>
       </c>
       <c r="V74">
-        <v>0.05309091686604449</v>
+        <v>0.05236364403226305</v>
       </c>
       <c r="W74">
-        <v>0.2232811618029867</v>
+        <v>0.2234526527371924</v>
       </c>
       <c r="X74" t="inlineStr">
         <is>
@@ -7381,7 +7381,7 @@
         </is>
       </c>
       <c r="Y74">
-        <v>0.2654545843302224</v>
+        <v>0.2618182201613153</v>
       </c>
       <c r="Z74">
         <v>0</v>
@@ -7389,22 +7389,22 @@
     </row>
     <row r="75">
       <c r="A75">
-        <v>0.73</v>
+        <v>0.74</v>
       </c>
       <c r="B75">
-        <v>0.2088723221667865</v>
+        <v>0.2107723221667865</v>
       </c>
       <c r="C75">
-        <v>-107.329841169382</v>
+        <v>-109.947703090865</v>
       </c>
       <c r="D75">
-        <v>44.21795883061802</v>
+        <v>43.70869690913501</v>
       </c>
       <c r="E75">
-        <v>146.8678</v>
+        <v>148.9764</v>
       </c>
       <c r="F75">
-        <v>153.9278</v>
+        <v>156.0364</v>
       </c>
       <c r="G75">
         <v>2.38</v>
@@ -7425,37 +7425,37 @@
         <v>9.503</v>
       </c>
       <c r="M75">
-        <v>36.29617524</v>
+        <v>36.79338312</v>
       </c>
       <c r="N75">
-        <v>-26.79317524</v>
+        <v>-27.29038312</v>
       </c>
       <c r="O75">
-        <v>-5.358635048000001</v>
+        <v>-5.458076624</v>
       </c>
       <c r="P75">
-        <v>-21.434540192</v>
+        <v>-21.832306496</v>
       </c>
       <c r="Q75">
-        <v>-21.077540192</v>
+        <v>-21.475306496</v>
       </c>
       <c r="R75">
-        <v>2.703703703703703</v>
+        <v>2.846153846153846</v>
       </c>
       <c r="S75">
-        <v>0.1694514284023559</v>
+        <v>0.1742072525716772</v>
       </c>
       <c r="T75">
-        <v>2.41019649184457</v>
+        <v>2.502896356915515</v>
       </c>
       <c r="U75">
         <v>0.2358</v>
       </c>
       <c r="V75">
-        <v>0.05236364403226305</v>
+        <v>0.05165602722101625</v>
       </c>
       <c r="W75">
-        <v>0.2234526527371924</v>
+        <v>0.2236195087812844</v>
       </c>
       <c r="X75" t="inlineStr">
         <is>
@@ -7463,7 +7463,7 @@
         </is>
       </c>
       <c r="Y75">
-        <v>0.2618182201613153</v>
+        <v>0.2582801361050813</v>
       </c>
       <c r="Z75">
         <v>0</v>
@@ -7471,22 +7471,22 @@
     </row>
     <row r="76">
       <c r="A76">
-        <v>0.74</v>
+        <v>0.75</v>
       </c>
       <c r="B76">
-        <v>0.2107723221667865</v>
+        <v>0.2126723221667865</v>
       </c>
       <c r="C76">
-        <v>-109.947703090865</v>
+        <v>-112.553968150289</v>
       </c>
       <c r="D76">
-        <v>43.70869690913501</v>
+        <v>43.211031849711</v>
       </c>
       <c r="E76">
-        <v>148.9764</v>
+        <v>151.085</v>
       </c>
       <c r="F76">
-        <v>156.0364</v>
+        <v>158.145</v>
       </c>
       <c r="G76">
         <v>2.38</v>
@@ -7507,37 +7507,37 @@
         <v>9.503</v>
       </c>
       <c r="M76">
-        <v>36.79338312</v>
+        <v>37.29059100000001</v>
       </c>
       <c r="N76">
-        <v>-27.29038312</v>
+        <v>-27.78759100000001</v>
       </c>
       <c r="O76">
-        <v>-5.458076624</v>
+        <v>-5.557518200000001</v>
       </c>
       <c r="P76">
-        <v>-21.832306496</v>
+        <v>-22.23007280000001</v>
       </c>
       <c r="Q76">
-        <v>-21.475306496</v>
+        <v>-21.87307280000001</v>
       </c>
       <c r="R76">
-        <v>2.846153846153846</v>
+        <v>3</v>
       </c>
       <c r="S76">
-        <v>0.1742072525716772</v>
+        <v>0.1793435426745443</v>
       </c>
       <c r="T76">
-        <v>2.502896356915515</v>
+        <v>2.603012211192136</v>
       </c>
       <c r="U76">
         <v>0.2358</v>
       </c>
       <c r="V76">
-        <v>0.05165602722101625</v>
+        <v>0.0509672801914027</v>
       </c>
       <c r="W76">
-        <v>0.2236195087812844</v>
+        <v>0.2237819153308672</v>
       </c>
       <c r="X76" t="inlineStr">
         <is>
@@ -7545,7 +7545,7 @@
         </is>
       </c>
       <c r="Y76">
-        <v>0.2582801361050813</v>
+        <v>0.2548364009570134</v>
       </c>
       <c r="Z76">
         <v>0</v>
@@ -7553,22 +7553,22 @@
     </row>
     <row r="77">
       <c r="A77">
-        <v>0.75</v>
+        <v>0.76</v>
       </c>
       <c r="B77">
-        <v>0.2126723221667865</v>
+        <v>0.2145723221667866</v>
       </c>
       <c r="C77">
-        <v>-112.553968150289</v>
+        <v>-115.1490280120744</v>
       </c>
       <c r="D77">
-        <v>43.211031849711</v>
+        <v>42.72457198792562</v>
       </c>
       <c r="E77">
-        <v>151.085</v>
+        <v>153.1936</v>
       </c>
       <c r="F77">
-        <v>158.145</v>
+        <v>160.2536</v>
       </c>
       <c r="G77">
         <v>2.38</v>
@@ -7589,37 +7589,37 @@
         <v>9.503</v>
       </c>
       <c r="M77">
-        <v>37.29059100000001</v>
+        <v>37.78779888</v>
       </c>
       <c r="N77">
-        <v>-27.78759100000001</v>
+        <v>-28.28479888</v>
       </c>
       <c r="O77">
-        <v>-5.557518200000001</v>
+        <v>-5.656959776000001</v>
       </c>
       <c r="P77">
-        <v>-22.23007280000001</v>
+        <v>-22.627839104</v>
       </c>
       <c r="Q77">
-        <v>-21.87307280000001</v>
+        <v>-22.270839104</v>
       </c>
       <c r="R77">
-        <v>3</v>
+        <v>3.166666666666667</v>
       </c>
       <c r="S77">
-        <v>0.1793435426745443</v>
+        <v>0.1849078569526504</v>
       </c>
       <c r="T77">
-        <v>2.603012211192136</v>
+        <v>2.711471053325142</v>
       </c>
       <c r="U77">
         <v>0.2358</v>
       </c>
       <c r="V77">
-        <v>0.0509672801914027</v>
+        <v>0.05029665808362108</v>
       </c>
       <c r="W77">
-        <v>0.2237819153308672</v>
+        <v>0.2239400480238822</v>
       </c>
       <c r="X77" t="inlineStr">
         <is>
@@ -7627,7 +7627,7 @@
         </is>
       </c>
       <c r="Y77">
-        <v>0.2548364009570134</v>
+        <v>0.2514832904181055</v>
       </c>
       <c r="Z77">
         <v>0</v>
@@ -7635,22 +7635,22 @@
     </row>
     <row r="78">
       <c r="A78">
-        <v>0.76</v>
+        <v>0.77</v>
       </c>
       <c r="B78">
-        <v>0.2145723221667866</v>
+        <v>0.2164723221667865</v>
       </c>
       <c r="C78">
-        <v>-115.1490280120744</v>
+        <v>-117.7332568999132</v>
       </c>
       <c r="D78">
-        <v>42.72457198792562</v>
+        <v>42.24894310008681</v>
       </c>
       <c r="E78">
-        <v>153.1936</v>
+        <v>155.3022</v>
       </c>
       <c r="F78">
-        <v>160.2536</v>
+        <v>162.3622</v>
       </c>
       <c r="G78">
         <v>2.38</v>
@@ -7671,37 +7671,37 @@
         <v>9.503</v>
       </c>
       <c r="M78">
-        <v>37.78779888</v>
+        <v>38.28500676</v>
       </c>
       <c r="N78">
-        <v>-28.28479888</v>
+        <v>-28.78200676</v>
       </c>
       <c r="O78">
-        <v>-5.656959776000001</v>
+        <v>-5.756401352000001</v>
       </c>
       <c r="P78">
-        <v>-22.627839104</v>
+        <v>-23.025605408</v>
       </c>
       <c r="Q78">
-        <v>-22.270839104</v>
+        <v>-22.668605408</v>
       </c>
       <c r="R78">
-        <v>3.166666666666667</v>
+        <v>3.347826086956522</v>
       </c>
       <c r="S78">
-        <v>0.1849078569526504</v>
+        <v>0.1909560246462439</v>
       </c>
       <c r="T78">
-        <v>2.711471053325142</v>
+        <v>2.829361099121887</v>
       </c>
       <c r="U78">
         <v>0.2358</v>
       </c>
       <c r="V78">
-        <v>0.05029665808362108</v>
+        <v>0.04964345473188575</v>
       </c>
       <c r="W78">
-        <v>0.2239400480238822</v>
+        <v>0.2240940733742213</v>
       </c>
       <c r="X78" t="inlineStr">
         <is>
@@ -7709,7 +7709,7 @@
         </is>
       </c>
       <c r="Y78">
-        <v>0.2514832904181055</v>
+        <v>0.2482172736594288</v>
       </c>
       <c r="Z78">
         <v>0</v>
@@ -7717,22 +7717,22 @@
     </row>
     <row r="79">
       <c r="A79">
-        <v>0.77</v>
+        <v>0.78</v>
       </c>
       <c r="B79">
-        <v>0.2164723221667865</v>
+        <v>0.2183723221667866</v>
       </c>
       <c r="C79">
-        <v>-117.7332568999132</v>
+        <v>-120.3070125568707</v>
       </c>
       <c r="D79">
-        <v>42.24894310008681</v>
+        <v>41.78378744312933</v>
       </c>
       <c r="E79">
-        <v>155.3022</v>
+        <v>157.4108</v>
       </c>
       <c r="F79">
-        <v>162.3622</v>
+        <v>164.4708</v>
       </c>
       <c r="G79">
         <v>2.38</v>
@@ -7753,37 +7753,37 @@
         <v>9.503</v>
       </c>
       <c r="M79">
-        <v>38.28500676</v>
+        <v>38.78221464000001</v>
       </c>
       <c r="N79">
-        <v>-28.78200676</v>
+        <v>-29.27921464000001</v>
       </c>
       <c r="O79">
-        <v>-5.756401352000001</v>
+        <v>-5.855842928000001</v>
       </c>
       <c r="P79">
-        <v>-23.025605408</v>
+        <v>-23.42337171200001</v>
       </c>
       <c r="Q79">
-        <v>-22.668605408</v>
+        <v>-23.06637171200001</v>
       </c>
       <c r="R79">
-        <v>3.347826086956522</v>
+        <v>3.545454545454546</v>
       </c>
       <c r="S79">
-        <v>0.1909560246462439</v>
+        <v>0.1975540257665277</v>
       </c>
       <c r="T79">
-        <v>2.829361099121887</v>
+        <v>2.957968421809246</v>
       </c>
       <c r="U79">
         <v>0.2358</v>
       </c>
       <c r="V79">
-        <v>0.04964345473188575</v>
+        <v>0.04900700018404106</v>
       </c>
       <c r="W79">
-        <v>0.2240940733742213</v>
+        <v>0.2242441493566031</v>
       </c>
       <c r="X79" t="inlineStr">
         <is>
@@ -7791,7 +7791,7 @@
         </is>
       </c>
       <c r="Y79">
-        <v>0.2482172736594288</v>
+        <v>0.2450350009202052</v>
       </c>
       <c r="Z79">
         <v>0</v>
@@ -7799,22 +7799,22 @@
     </row>
     <row r="80">
       <c r="A80">
-        <v>0.78</v>
+        <v>0.79</v>
       </c>
       <c r="B80">
-        <v>0.2183723221667866</v>
+        <v>0.2202723221667865</v>
       </c>
       <c r="C80">
-        <v>-120.3070125568707</v>
+        <v>-122.8706371427535</v>
       </c>
       <c r="D80">
-        <v>41.78378744312933</v>
+        <v>41.32876285724657</v>
       </c>
       <c r="E80">
-        <v>157.4108</v>
+        <v>159.5194</v>
       </c>
       <c r="F80">
-        <v>164.4708</v>
+        <v>166.5794</v>
       </c>
       <c r="G80">
         <v>2.38</v>
@@ -7835,37 +7835,37 @@
         <v>9.503</v>
       </c>
       <c r="M80">
-        <v>38.78221464000001</v>
+        <v>39.27942252</v>
       </c>
       <c r="N80">
-        <v>-29.27921464000001</v>
+        <v>-29.77642252</v>
       </c>
       <c r="O80">
-        <v>-5.855842928000001</v>
+        <v>-5.955284504000002</v>
       </c>
       <c r="P80">
-        <v>-23.42337171200001</v>
+        <v>-23.821138016</v>
       </c>
       <c r="Q80">
-        <v>-23.06637171200001</v>
+        <v>-23.464138016</v>
       </c>
       <c r="R80">
-        <v>3.545454545454546</v>
+        <v>3.761904761904763</v>
       </c>
       <c r="S80">
-        <v>0.1975540257665277</v>
+        <v>0.2047804079458861</v>
       </c>
       <c r="T80">
-        <v>2.957968421809246</v>
+        <v>3.09882406094302</v>
       </c>
       <c r="U80">
         <v>0.2358</v>
       </c>
       <c r="V80">
-        <v>0.04900700018404106</v>
+        <v>0.04838665840955952</v>
       </c>
       <c r="W80">
-        <v>0.2242441493566031</v>
+        <v>0.2243904259470259</v>
       </c>
       <c r="X80" t="inlineStr">
         <is>
@@ -7873,7 +7873,7 @@
         </is>
       </c>
       <c r="Y80">
-        <v>0.2450350009202052</v>
+        <v>0.2419332920477977</v>
       </c>
       <c r="Z80">
         <v>0</v>
@@ -7881,22 +7881,22 @@
     </row>
     <row r="81">
       <c r="A81">
-        <v>0.79</v>
+        <v>0.8</v>
       </c>
       <c r="B81">
-        <v>0.2202723221667865</v>
+        <v>0.2221723221667865</v>
       </c>
       <c r="C81">
-        <v>-122.8706371427535</v>
+        <v>-125.4244580734758</v>
       </c>
       <c r="D81">
-        <v>41.32876285724657</v>
+        <v>40.88354192652417</v>
       </c>
       <c r="E81">
-        <v>159.5194</v>
+        <v>161.628</v>
       </c>
       <c r="F81">
-        <v>166.5794</v>
+        <v>168.688</v>
       </c>
       <c r="G81">
         <v>2.38</v>
@@ -7917,37 +7917,37 @@
         <v>9.503</v>
       </c>
       <c r="M81">
-        <v>39.27942252</v>
+        <v>39.77663040000001</v>
       </c>
       <c r="N81">
-        <v>-29.77642252</v>
+        <v>-30.27363040000001</v>
       </c>
       <c r="O81">
-        <v>-5.955284504000002</v>
+        <v>-6.054726080000002</v>
       </c>
       <c r="P81">
-        <v>-23.821138016</v>
+        <v>-24.21890432000001</v>
       </c>
       <c r="Q81">
-        <v>-23.464138016</v>
+        <v>-23.86190432000001</v>
       </c>
       <c r="R81">
-        <v>3.761904761904763</v>
+        <v>4.000000000000001</v>
       </c>
       <c r="S81">
-        <v>0.2047804079458861</v>
+        <v>0.2127294283431805</v>
       </c>
       <c r="T81">
-        <v>3.09882406094302</v>
+        <v>3.253765263990171</v>
       </c>
       <c r="U81">
         <v>0.2358</v>
       </c>
       <c r="V81">
-        <v>0.04838665840955952</v>
+        <v>0.04778182517944003</v>
       </c>
       <c r="W81">
-        <v>0.2243904259470259</v>
+        <v>0.224533045622688</v>
       </c>
       <c r="X81" t="inlineStr">
         <is>
@@ -7955,7 +7955,7 @@
         </is>
       </c>
       <c r="Y81">
-        <v>0.2419332920477977</v>
+        <v>0.2389091258972001</v>
       </c>
       <c r="Z81">
         <v>0</v>
@@ -7963,22 +7963,22 @@
     </row>
     <row r="82">
       <c r="A82">
-        <v>0.8</v>
+        <v>0.8100000000000001</v>
       </c>
       <c r="B82">
-        <v>0.2221723221667865</v>
+        <v>0.2240723221667865</v>
       </c>
       <c r="C82">
-        <v>-125.4244580734758</v>
+        <v>-127.968788806751</v>
       </c>
       <c r="D82">
-        <v>40.88354192652417</v>
+        <v>40.44781119324903</v>
       </c>
       <c r="E82">
-        <v>161.628</v>
+        <v>163.7366</v>
       </c>
       <c r="F82">
-        <v>168.688</v>
+        <v>170.7966</v>
       </c>
       <c r="G82">
         <v>2.38</v>
@@ -7999,37 +7999,37 @@
         <v>9.503</v>
       </c>
       <c r="M82">
-        <v>39.77663040000001</v>
+        <v>40.27383828000001</v>
       </c>
       <c r="N82">
-        <v>-30.27363040000001</v>
+        <v>-30.77083828000001</v>
       </c>
       <c r="O82">
-        <v>-6.054726080000002</v>
+        <v>-6.154167656000002</v>
       </c>
       <c r="P82">
-        <v>-24.21890432000001</v>
+        <v>-24.616670624</v>
       </c>
       <c r="Q82">
-        <v>-23.86190432000001</v>
+        <v>-24.25967062400001</v>
       </c>
       <c r="R82">
-        <v>4.000000000000001</v>
+        <v>4.263157894736843</v>
       </c>
       <c r="S82">
-        <v>0.2127294283431805</v>
+        <v>0.2215151877296637</v>
       </c>
       <c r="T82">
-        <v>3.253765263990171</v>
+        <v>3.425016067358075</v>
       </c>
       <c r="U82">
         <v>0.2358</v>
       </c>
       <c r="V82">
-        <v>0.04778182517944003</v>
+        <v>0.04719192610315065</v>
       </c>
       <c r="W82">
-        <v>0.224533045622688</v>
+        <v>0.2246721438248771</v>
       </c>
       <c r="X82" t="inlineStr">
         <is>
@@ -8037,7 +8037,7 @@
         </is>
       </c>
       <c r="Y82">
-        <v>0.2389091258972001</v>
+        <v>0.2359596305157532</v>
       </c>
       <c r="Z82">
         <v>0</v>
@@ -8045,22 +8045,22 @@
     </row>
     <row r="83">
       <c r="A83">
-        <v>0.8100000000000001</v>
+        <v>0.8200000000000001</v>
       </c>
       <c r="B83">
-        <v>0.2240723221667865</v>
+        <v>0.2259723221667865</v>
       </c>
       <c r="C83">
-        <v>-127.968788806751</v>
+        <v>-130.503929578069</v>
       </c>
       <c r="D83">
-        <v>40.44781119324903</v>
+        <v>40.02127042193106</v>
       </c>
       <c r="E83">
-        <v>163.7366</v>
+        <v>165.8452</v>
       </c>
       <c r="F83">
-        <v>170.7966</v>
+        <v>172.9052</v>
       </c>
       <c r="G83">
         <v>2.38</v>
@@ -8081,37 +8081,37 @@
         <v>9.503</v>
       </c>
       <c r="M83">
-        <v>40.27383828000001</v>
+        <v>40.77104616000001</v>
       </c>
       <c r="N83">
-        <v>-30.77083828000001</v>
+        <v>-31.26804616000001</v>
       </c>
       <c r="O83">
-        <v>-6.154167656000002</v>
+        <v>-6.253609232000002</v>
       </c>
       <c r="P83">
-        <v>-24.616670624</v>
+        <v>-25.01443692800001</v>
       </c>
       <c r="Q83">
-        <v>-24.25967062400001</v>
+        <v>-24.65743692800001</v>
       </c>
       <c r="R83">
-        <v>4.263157894736843</v>
+        <v>4.555555555555557</v>
       </c>
       <c r="S83">
-        <v>0.2215151877296637</v>
+        <v>0.2312771426035339</v>
       </c>
       <c r="T83">
-        <v>3.425016067358075</v>
+        <v>3.615294737766857</v>
       </c>
       <c r="U83">
         <v>0.2358</v>
       </c>
       <c r="V83">
-        <v>0.04719192610315065</v>
+        <v>0.04661641480920978</v>
       </c>
       <c r="W83">
-        <v>0.2246721438248771</v>
+        <v>0.2248078493879883</v>
       </c>
       <c r="X83" t="inlineStr">
         <is>
@@ -8119,7 +8119,7 @@
         </is>
       </c>
       <c r="Y83">
-        <v>0.2359596305157532</v>
+        <v>0.2330820740460489</v>
       </c>
       <c r="Z83">
         <v>0</v>
@@ -8127,22 +8127,22 @@
     </row>
     <row r="84">
       <c r="A84">
-        <v>0.8200000000000001</v>
+        <v>0.8300000000000001</v>
       </c>
       <c r="B84">
-        <v>0.2259723221667865</v>
+        <v>0.2278723221667865</v>
       </c>
       <c r="C84">
-        <v>-130.503929578069</v>
+        <v>-133.0301680905937</v>
       </c>
       <c r="D84">
-        <v>40.02127042193106</v>
+        <v>39.60363190940627</v>
       </c>
       <c r="E84">
-        <v>165.8452</v>
+        <v>167.9538</v>
       </c>
       <c r="F84">
-        <v>172.9052</v>
+        <v>175.0138</v>
       </c>
       <c r="G84">
         <v>2.38</v>
@@ -8163,37 +8163,37 @@
         <v>9.503</v>
       </c>
       <c r="M84">
-        <v>40.77104616000001</v>
+        <v>41.26825404000001</v>
       </c>
       <c r="N84">
-        <v>-31.26804616000001</v>
+        <v>-31.76525404000001</v>
       </c>
       <c r="O84">
-        <v>-6.253609232000002</v>
+        <v>-6.353050808000003</v>
       </c>
       <c r="P84">
-        <v>-25.01443692800001</v>
+        <v>-25.41220323200001</v>
       </c>
       <c r="Q84">
-        <v>-24.65743692800001</v>
+        <v>-25.05520323200001</v>
       </c>
       <c r="R84">
-        <v>4.555555555555557</v>
+        <v>4.882352941176473</v>
       </c>
       <c r="S84">
-        <v>0.2312771426035339</v>
+        <v>0.242187562756683</v>
       </c>
       <c r="T84">
-        <v>3.615294737766857</v>
+        <v>3.827959134106084</v>
       </c>
       <c r="U84">
         <v>0.2358</v>
       </c>
       <c r="V84">
-        <v>0.04661641480920978</v>
+        <v>0.0460547712572916</v>
       </c>
       <c r="W84">
-        <v>0.2248078493879883</v>
+        <v>0.2249402849375307</v>
       </c>
       <c r="X84" t="inlineStr">
         <is>
@@ -8201,7 +8201,7 @@
         </is>
       </c>
       <c r="Y84">
-        <v>0.2330820740460489</v>
+        <v>0.2302738562864579</v>
       </c>
       <c r="Z84">
         <v>0</v>
@@ -8209,22 +8209,22 @@
     </row>
     <row r="85">
       <c r="A85">
-        <v>0.8300000000000001</v>
+        <v>0.8400000000000001</v>
       </c>
       <c r="B85">
-        <v>0.2278723221667865</v>
+        <v>0.2297723221667866</v>
       </c>
       <c r="C85">
-        <v>-133.0301680905937</v>
+        <v>-135.5477801623099</v>
       </c>
       <c r="D85">
-        <v>39.60363190940627</v>
+        <v>39.19461983769011</v>
       </c>
       <c r="E85">
-        <v>167.9538</v>
+        <v>170.0624</v>
       </c>
       <c r="F85">
-        <v>175.0138</v>
+        <v>177.1224</v>
       </c>
       <c r="G85">
         <v>2.38</v>
@@ -8245,37 +8245,37 @@
         <v>9.503</v>
       </c>
       <c r="M85">
-        <v>41.26825404000001</v>
+        <v>41.76546192000001</v>
       </c>
       <c r="N85">
-        <v>-31.76525404000001</v>
+        <v>-32.26246192000001</v>
       </c>
       <c r="O85">
-        <v>-6.353050808000003</v>
+        <v>-6.452492384000002</v>
       </c>
       <c r="P85">
-        <v>-25.41220323200001</v>
+        <v>-25.809969536</v>
       </c>
       <c r="Q85">
-        <v>-25.05520323200001</v>
+        <v>-25.452969536</v>
       </c>
       <c r="R85">
-        <v>4.882352941176473</v>
+        <v>5.250000000000004</v>
       </c>
       <c r="S85">
-        <v>0.242187562756683</v>
+        <v>0.2544617854289757</v>
       </c>
       <c r="T85">
-        <v>3.827959134106084</v>
+        <v>4.067206579987715</v>
       </c>
       <c r="U85">
         <v>0.2358</v>
       </c>
       <c r="V85">
-        <v>0.0460547712572916</v>
+        <v>0.04550650017089527</v>
       </c>
       <c r="W85">
-        <v>0.2249402849375307</v>
+        <v>0.2250695672597029</v>
       </c>
       <c r="X85" t="inlineStr">
         <is>
@@ -8283,7 +8283,7 @@
         </is>
       </c>
       <c r="Y85">
-        <v>0.2302738562864579</v>
+        <v>0.2275325008544763</v>
       </c>
       <c r="Z85">
         <v>0</v>
@@ -8291,22 +8291,22 @@
     </row>
     <row r="86">
       <c r="A86">
-        <v>0.84</v>
+        <v>0.85</v>
       </c>
       <c r="B86">
-        <v>0.2297723221667865</v>
+        <v>0.2316723221667865</v>
       </c>
       <c r="C86">
-        <v>-135.5477801623099</v>
+        <v>-138.0570303334784</v>
       </c>
       <c r="D86">
-        <v>39.19461983769011</v>
+        <v>38.7939696665216</v>
       </c>
       <c r="E86">
-        <v>170.0624</v>
+        <v>172.171</v>
       </c>
       <c r="F86">
-        <v>177.1224</v>
+        <v>179.231</v>
       </c>
       <c r="G86">
         <v>2.38</v>
@@ -8327,37 +8327,37 @@
         <v>9.503</v>
       </c>
       <c r="M86">
-        <v>41.76546192</v>
+        <v>42.2626698</v>
       </c>
       <c r="N86">
-        <v>-32.26246192</v>
+        <v>-32.7596698</v>
       </c>
       <c r="O86">
-        <v>-6.452492384</v>
+        <v>-6.55193396</v>
       </c>
       <c r="P86">
-        <v>-25.809969536</v>
+        <v>-26.20773584</v>
       </c>
       <c r="Q86">
-        <v>-25.452969536</v>
+        <v>-25.85073584</v>
       </c>
       <c r="R86">
-        <v>5.249999999999999</v>
+        <v>5.666666666666666</v>
       </c>
       <c r="S86">
-        <v>0.2544617854289755</v>
+        <v>0.2683725711242406</v>
       </c>
       <c r="T86">
-        <v>4.067206579987712</v>
+        <v>4.338353685320227</v>
       </c>
       <c r="U86">
         <v>0.2358</v>
       </c>
       <c r="V86">
-        <v>0.04550650017089528</v>
+        <v>0.04497112958064945</v>
       </c>
       <c r="W86">
-        <v>0.2250695672597029</v>
+        <v>0.2251958076448829</v>
       </c>
       <c r="X86" t="inlineStr">
         <is>
@@ -8365,7 +8365,7 @@
         </is>
       </c>
       <c r="Y86">
-        <v>0.2275325008544764</v>
+        <v>0.2248556479032472</v>
       </c>
       <c r="Z86">
         <v>0</v>
@@ -8373,22 +8373,22 @@
     </row>
     <row r="87">
       <c r="A87">
-        <v>0.85</v>
+        <v>0.86</v>
       </c>
       <c r="B87">
-        <v>0.2316723221667865</v>
+        <v>0.2335723221667865</v>
       </c>
       <c r="C87">
-        <v>-138.0570303334784</v>
+        <v>-140.5581724372125</v>
       </c>
       <c r="D87">
-        <v>38.7939696665216</v>
+        <v>38.40142756278748</v>
       </c>
       <c r="E87">
-        <v>172.171</v>
+        <v>174.2796</v>
       </c>
       <c r="F87">
-        <v>179.231</v>
+        <v>181.3396</v>
       </c>
       <c r="G87">
         <v>2.38</v>
@@ -8409,37 +8409,37 @@
         <v>9.503</v>
       </c>
       <c r="M87">
-        <v>42.2626698</v>
+        <v>42.75987768000001</v>
       </c>
       <c r="N87">
-        <v>-32.7596698</v>
+        <v>-33.25687768000001</v>
       </c>
       <c r="O87">
-        <v>-6.55193396</v>
+        <v>-6.651375536000002</v>
       </c>
       <c r="P87">
-        <v>-26.20773584</v>
+        <v>-26.60550214400001</v>
       </c>
       <c r="Q87">
-        <v>-25.85073584</v>
+        <v>-26.24850214400001</v>
       </c>
       <c r="R87">
-        <v>5.666666666666666</v>
+        <v>6.142857142857142</v>
       </c>
       <c r="S87">
-        <v>0.2683725711242406</v>
+        <v>0.2842706119188292</v>
       </c>
       <c r="T87">
-        <v>4.338353685320227</v>
+        <v>4.648236091414529</v>
       </c>
       <c r="U87">
         <v>0.2358</v>
       </c>
       <c r="V87">
-        <v>0.04497112958064945</v>
+        <v>0.04444820946924654</v>
       </c>
       <c r="W87">
-        <v>0.2251958076448829</v>
+        <v>0.2253191122071517</v>
       </c>
       <c r="X87" t="inlineStr">
         <is>
@@ -8447,7 +8447,7 @@
         </is>
       </c>
       <c r="Y87">
-        <v>0.2248556479032472</v>
+        <v>0.2222410473462327</v>
       </c>
       <c r="Z87">
         <v>0</v>
@@ -8455,22 +8455,22 @@
     </row>
     <row r="88">
       <c r="A88">
-        <v>0.86</v>
+        <v>0.87</v>
       </c>
       <c r="B88">
-        <v>0.2335723221667865</v>
+        <v>0.2354723221667865</v>
       </c>
       <c r="C88">
-        <v>-140.5581724372125</v>
+        <v>-143.0514501357601</v>
       </c>
       <c r="D88">
-        <v>38.40142756278748</v>
+        <v>38.0167498642399</v>
       </c>
       <c r="E88">
-        <v>174.2796</v>
+        <v>176.3882</v>
       </c>
       <c r="F88">
-        <v>181.3396</v>
+        <v>183.4482</v>
       </c>
       <c r="G88">
         <v>2.38</v>
@@ -8491,37 +8491,37 @@
         <v>9.503</v>
       </c>
       <c r="M88">
-        <v>42.75987768000001</v>
+        <v>43.25708556000001</v>
       </c>
       <c r="N88">
-        <v>-33.25687768000001</v>
+        <v>-33.75408556000001</v>
       </c>
       <c r="O88">
-        <v>-6.651375536000002</v>
+        <v>-6.750817112000002</v>
       </c>
       <c r="P88">
-        <v>-26.60550214400001</v>
+        <v>-27.00326844800001</v>
       </c>
       <c r="Q88">
-        <v>-26.24850214400001</v>
+        <v>-26.64626844800001</v>
       </c>
       <c r="R88">
-        <v>6.142857142857142</v>
+        <v>6.692307692307692</v>
       </c>
       <c r="S88">
-        <v>0.2842706119188292</v>
+        <v>0.3026145051433545</v>
       </c>
       <c r="T88">
-        <v>4.648236091414529</v>
+        <v>5.00579271383103</v>
       </c>
       <c r="U88">
         <v>0.2358</v>
       </c>
       <c r="V88">
-        <v>0.04444820946924654</v>
+        <v>0.04393731050982991</v>
       </c>
       <c r="W88">
-        <v>0.2253191122071517</v>
+        <v>0.2254395821817821</v>
       </c>
       <c r="X88" t="inlineStr">
         <is>
@@ -8529,7 +8529,7 @@
         </is>
       </c>
       <c r="Y88">
-        <v>0.2222410473462327</v>
+        <v>0.2196865525491496</v>
       </c>
       <c r="Z88">
         <v>0</v>
@@ -8537,22 +8537,22 @@
     </row>
     <row r="89">
       <c r="A89">
-        <v>0.87</v>
+        <v>0.88</v>
       </c>
       <c r="B89">
-        <v>0.2354723221667865</v>
+        <v>0.2373723221667865</v>
       </c>
       <c r="C89">
-        <v>-143.0514501357601</v>
+        <v>-145.5370974248731</v>
       </c>
       <c r="D89">
-        <v>38.0167498642399</v>
+        <v>37.63970257512695</v>
       </c>
       <c r="E89">
-        <v>176.3882</v>
+        <v>178.4968</v>
       </c>
       <c r="F89">
-        <v>183.4482</v>
+        <v>185.5568</v>
       </c>
       <c r="G89">
         <v>2.38</v>
@@ -8573,37 +8573,37 @@
         <v>9.503</v>
       </c>
       <c r="M89">
-        <v>43.25708556000001</v>
+        <v>43.75429344</v>
       </c>
       <c r="N89">
-        <v>-33.75408556000001</v>
+        <v>-34.25129344</v>
       </c>
       <c r="O89">
-        <v>-6.750817112000002</v>
+        <v>-6.850258688000001</v>
       </c>
       <c r="P89">
-        <v>-27.00326844800001</v>
+        <v>-27.401034752</v>
       </c>
       <c r="Q89">
-        <v>-26.64626844800001</v>
+        <v>-27.04403475200001</v>
       </c>
       <c r="R89">
-        <v>6.692307692307692</v>
+        <v>7.333333333333334</v>
       </c>
       <c r="S89">
-        <v>0.3026145051433545</v>
+        <v>0.3240157139053008</v>
       </c>
       <c r="T89">
-        <v>5.00579271383103</v>
+        <v>5.422942106650284</v>
       </c>
       <c r="U89">
         <v>0.2358</v>
       </c>
       <c r="V89">
-        <v>0.04393731050982991</v>
+        <v>0.04343802289040003</v>
       </c>
       <c r="W89">
-        <v>0.2254395821817821</v>
+        <v>0.2255573142024437</v>
       </c>
       <c r="X89" t="inlineStr">
         <is>
@@ -8611,7 +8611,7 @@
         </is>
       </c>
       <c r="Y89">
-        <v>0.2196865525491496</v>
+        <v>0.2171901144520001</v>
       </c>
       <c r="Z89">
         <v>0</v>
@@ -8619,22 +8619,22 @@
     </row>
     <row r="90">
       <c r="A90">
-        <v>0.88</v>
+        <v>0.89</v>
       </c>
       <c r="B90">
-        <v>0.2373723221667865</v>
+        <v>0.2392723221667865</v>
       </c>
       <c r="C90">
-        <v>-145.5370974248731</v>
+        <v>-148.0153391084576</v>
       </c>
       <c r="D90">
-        <v>37.63970257512695</v>
+        <v>37.27006089154241</v>
       </c>
       <c r="E90">
-        <v>178.4968</v>
+        <v>180.6054</v>
       </c>
       <c r="F90">
-        <v>185.5568</v>
+        <v>187.6654</v>
       </c>
       <c r="G90">
         <v>2.38</v>
@@ -8655,37 +8655,37 @@
         <v>9.503</v>
       </c>
       <c r="M90">
-        <v>43.75429344</v>
+        <v>44.25150132</v>
       </c>
       <c r="N90">
-        <v>-34.25129344</v>
+        <v>-34.74850132</v>
       </c>
       <c r="O90">
-        <v>-6.850258688000001</v>
+        <v>-6.949700264000001</v>
       </c>
       <c r="P90">
-        <v>-27.401034752</v>
+        <v>-27.798801056</v>
       </c>
       <c r="Q90">
-        <v>-27.04403475200001</v>
+        <v>-27.441801056</v>
       </c>
       <c r="R90">
-        <v>7.333333333333334</v>
+        <v>8.090909090909092</v>
       </c>
       <c r="S90">
-        <v>0.3240157139053008</v>
+        <v>0.3493080515330554</v>
       </c>
       <c r="T90">
-        <v>5.422942106650284</v>
+        <v>5.915936843618492</v>
       </c>
       <c r="U90">
         <v>0.2358</v>
       </c>
       <c r="V90">
-        <v>0.04343802289040003</v>
+        <v>0.04294995521747419</v>
       </c>
       <c r="W90">
-        <v>0.2255573142024437</v>
+        <v>0.2256724005597196</v>
       </c>
       <c r="X90" t="inlineStr">
         <is>
@@ -8693,7 +8693,7 @@
         </is>
       </c>
       <c r="Y90">
-        <v>0.2171901144520001</v>
+        <v>0.2147497760873709</v>
       </c>
       <c r="Z90">
         <v>0</v>
@@ -8701,22 +8701,22 @@
     </row>
     <row r="91">
       <c r="A91">
-        <v>0.89</v>
+        <v>0.9</v>
       </c>
       <c r="B91">
-        <v>0.2392723221667865</v>
+        <v>0.2411723221667866</v>
       </c>
       <c r="C91">
-        <v>-148.0153391084576</v>
+        <v>-150.4863912455289</v>
       </c>
       <c r="D91">
-        <v>37.27006089154241</v>
+        <v>36.90760875447113</v>
       </c>
       <c r="E91">
-        <v>180.6054</v>
+        <v>182.714</v>
       </c>
       <c r="F91">
-        <v>187.6654</v>
+        <v>189.774</v>
       </c>
       <c r="G91">
         <v>2.38</v>
@@ -8737,37 +8737,37 @@
         <v>9.503</v>
       </c>
       <c r="M91">
-        <v>44.25150132</v>
+        <v>44.74870920000001</v>
       </c>
       <c r="N91">
-        <v>-34.74850132</v>
+        <v>-35.24570920000001</v>
       </c>
       <c r="O91">
-        <v>-6.949700264000001</v>
+        <v>-7.049141840000002</v>
       </c>
       <c r="P91">
-        <v>-27.798801056</v>
+        <v>-28.19656736000001</v>
       </c>
       <c r="Q91">
-        <v>-27.441801056</v>
+        <v>-27.83956736000001</v>
       </c>
       <c r="R91">
-        <v>8.090909090909092</v>
+        <v>9.000000000000002</v>
       </c>
       <c r="S91">
-        <v>0.3493080515330554</v>
+        <v>0.379658856686361</v>
       </c>
       <c r="T91">
-        <v>5.915936843618492</v>
+        <v>6.507530527980342</v>
       </c>
       <c r="U91">
         <v>0.2358</v>
       </c>
       <c r="V91">
-        <v>0.04294995521747419</v>
+        <v>0.04247273349283558</v>
       </c>
       <c r="W91">
-        <v>0.2256724005597196</v>
+        <v>0.2257849294423894</v>
       </c>
       <c r="X91" t="inlineStr">
         <is>
@@ -8775,7 +8775,7 @@
         </is>
       </c>
       <c r="Y91">
-        <v>0.2147497760873709</v>
+        <v>0.2123636674641779</v>
       </c>
       <c r="Z91">
         <v>0</v>
@@ -8783,22 +8783,22 @@
     </row>
     <row r="92">
       <c r="A92">
-        <v>0.9</v>
+        <v>0.91</v>
       </c>
       <c r="B92">
-        <v>0.2411723221667866</v>
+        <v>0.2430723221667865</v>
       </c>
       <c r="C92">
-        <v>-150.4863912455289</v>
+        <v>-152.9504615713367</v>
       </c>
       <c r="D92">
-        <v>36.90760875447113</v>
+        <v>36.5521384286633</v>
       </c>
       <c r="E92">
-        <v>182.714</v>
+        <v>184.8226</v>
       </c>
       <c r="F92">
-        <v>189.774</v>
+        <v>191.8826</v>
       </c>
       <c r="G92">
         <v>2.38</v>
@@ -8819,37 +8819,37 @@
         <v>9.503</v>
       </c>
       <c r="M92">
-        <v>44.74870920000001</v>
+        <v>45.24591708000001</v>
       </c>
       <c r="N92">
-        <v>-35.24570920000001</v>
+        <v>-35.74291708000001</v>
       </c>
       <c r="O92">
-        <v>-7.049141840000002</v>
+        <v>-7.148583416000001</v>
       </c>
       <c r="P92">
-        <v>-28.19656736000001</v>
+        <v>-28.594333664</v>
       </c>
       <c r="Q92">
-        <v>-27.83956736000001</v>
+        <v>-28.237333664</v>
       </c>
       <c r="R92">
-        <v>9.000000000000002</v>
+        <v>10.11111111111111</v>
       </c>
       <c r="S92">
-        <v>0.379658856686361</v>
+        <v>0.4167542852070678</v>
       </c>
       <c r="T92">
-        <v>6.507530527980342</v>
+        <v>7.230589475533714</v>
       </c>
       <c r="U92">
         <v>0.2358</v>
       </c>
       <c r="V92">
-        <v>0.04247273349283558</v>
+        <v>0.04200600015774948</v>
       </c>
       <c r="W92">
-        <v>0.2257849294423894</v>
+        <v>0.2258949851628027</v>
       </c>
       <c r="X92" t="inlineStr">
         <is>
@@ -8857,7 +8857,7 @@
         </is>
       </c>
       <c r="Y92">
-        <v>0.2123636674641779</v>
+        <v>0.2100300007887473</v>
       </c>
       <c r="Z92">
         <v>0</v>
@@ -8865,22 +8865,22 @@
     </row>
     <row r="93">
       <c r="A93">
-        <v>0.91</v>
+        <v>0.92</v>
       </c>
       <c r="B93">
-        <v>0.2430723221667865</v>
+        <v>0.2449723221667865</v>
       </c>
       <c r="C93">
-        <v>-152.9504615713367</v>
+        <v>-155.4077498943875</v>
       </c>
       <c r="D93">
-        <v>36.5521384286633</v>
+        <v>36.20345010561255</v>
       </c>
       <c r="E93">
-        <v>184.8226</v>
+        <v>186.9312</v>
       </c>
       <c r="F93">
-        <v>191.8826</v>
+        <v>193.9912</v>
       </c>
       <c r="G93">
         <v>2.38</v>
@@ -8901,37 +8901,37 @@
         <v>9.503</v>
       </c>
       <c r="M93">
-        <v>45.24591708000001</v>
+        <v>45.74312496000001</v>
       </c>
       <c r="N93">
-        <v>-35.74291708000001</v>
+        <v>-36.24012496000001</v>
       </c>
       <c r="O93">
-        <v>-7.148583416000001</v>
+        <v>-7.248024992000002</v>
       </c>
       <c r="P93">
-        <v>-28.594333664</v>
+        <v>-28.99209996800001</v>
       </c>
       <c r="Q93">
-        <v>-28.237333664</v>
+        <v>-28.63509996800001</v>
       </c>
       <c r="R93">
-        <v>10.11111111111111</v>
+        <v>11.50000000000001</v>
       </c>
       <c r="S93">
-        <v>0.4167542852070678</v>
+        <v>0.4631235708579514</v>
       </c>
       <c r="T93">
-        <v>7.230589475533714</v>
+        <v>8.134413159975431</v>
       </c>
       <c r="U93">
         <v>0.2358</v>
       </c>
       <c r="V93">
-        <v>0.04200600015774948</v>
+        <v>0.04154941319951307</v>
       </c>
       <c r="W93">
-        <v>0.2258949851628027</v>
+        <v>0.2260026483675548</v>
       </c>
       <c r="X93" t="inlineStr">
         <is>
@@ -8939,7 +8939,7 @@
         </is>
       </c>
       <c r="Y93">
-        <v>0.2100300007887473</v>
+        <v>0.2077470659975653</v>
       </c>
       <c r="Z93">
         <v>0</v>
@@ -8947,22 +8947,22 @@
     </row>
     <row r="94">
       <c r="A94">
-        <v>0.92</v>
+        <v>0.93</v>
       </c>
       <c r="B94">
-        <v>0.2449723221667865</v>
+        <v>0.2468723221667865</v>
       </c>
       <c r="C94">
-        <v>-155.4077498943875</v>
+        <v>-157.8584484709564</v>
       </c>
       <c r="D94">
-        <v>36.20345010561255</v>
+        <v>35.86135152904365</v>
       </c>
       <c r="E94">
-        <v>186.9312</v>
+        <v>189.0398</v>
       </c>
       <c r="F94">
-        <v>193.9912</v>
+        <v>196.0998</v>
       </c>
       <c r="G94">
         <v>2.38</v>
@@ -8983,37 +8983,37 @@
         <v>9.503</v>
       </c>
       <c r="M94">
-        <v>45.74312496000001</v>
+        <v>46.24033284000001</v>
       </c>
       <c r="N94">
-        <v>-36.24012496000001</v>
+        <v>-36.73733284000001</v>
       </c>
       <c r="O94">
-        <v>-7.248024992000002</v>
+        <v>-7.347466568000002</v>
       </c>
       <c r="P94">
-        <v>-28.99209996800001</v>
+        <v>-29.38986627200001</v>
       </c>
       <c r="Q94">
-        <v>-28.63509996800001</v>
+        <v>-29.03286627200001</v>
       </c>
       <c r="R94">
-        <v>11.50000000000001</v>
+        <v>13.2857142857143</v>
       </c>
       <c r="S94">
-        <v>0.4631235708579514</v>
+        <v>0.5227412238376588</v>
       </c>
       <c r="T94">
-        <v>8.134413159975431</v>
+        <v>9.296472182829065</v>
       </c>
       <c r="U94">
         <v>0.2358</v>
       </c>
       <c r="V94">
-        <v>0.04154941319951307</v>
+        <v>0.04110264531564733</v>
       </c>
       <c r="W94">
-        <v>0.2260026483675548</v>
+        <v>0.2261079962345704</v>
       </c>
       <c r="X94" t="inlineStr">
         <is>
@@ -9021,7 +9021,7 @@
         </is>
       </c>
       <c r="Y94">
-        <v>0.2077470659975653</v>
+        <v>0.2055132265782367</v>
       </c>
       <c r="Z94">
         <v>0</v>
@@ -9029,22 +9029,22 @@
     </row>
     <row r="95">
       <c r="A95">
-        <v>0.93</v>
+        <v>0.9400000000000001</v>
       </c>
       <c r="B95">
-        <v>0.2468723221667865</v>
+        <v>0.2487723221667865</v>
       </c>
       <c r="C95">
-        <v>-157.8584484709564</v>
+        <v>-160.3027423585653</v>
       </c>
       <c r="D95">
-        <v>35.86135152904365</v>
+        <v>35.52565764143471</v>
       </c>
       <c r="E95">
-        <v>189.0398</v>
+        <v>191.1484</v>
       </c>
       <c r="F95">
-        <v>196.0998</v>
+        <v>198.2084</v>
       </c>
       <c r="G95">
         <v>2.38</v>
@@ -9065,37 +9065,37 @@
         <v>9.503</v>
       </c>
       <c r="M95">
-        <v>46.24033284000001</v>
+        <v>46.73754072000001</v>
       </c>
       <c r="N95">
-        <v>-36.73733284000001</v>
+        <v>-37.23454072000001</v>
       </c>
       <c r="O95">
-        <v>-7.347466568000002</v>
+        <v>-7.446908144000002</v>
       </c>
       <c r="P95">
-        <v>-29.38986627200001</v>
+        <v>-29.787632576</v>
       </c>
       <c r="Q95">
-        <v>-29.03286627200001</v>
+        <v>-29.430632576</v>
       </c>
       <c r="R95">
-        <v>13.2857142857143</v>
+        <v>15.66666666666668</v>
       </c>
       <c r="S95">
-        <v>0.5227412238376588</v>
+        <v>0.602231427810602</v>
       </c>
       <c r="T95">
-        <v>9.296472182829065</v>
+        <v>10.84588421330058</v>
       </c>
       <c r="U95">
         <v>0.2358</v>
       </c>
       <c r="V95">
-        <v>0.04110264531564733</v>
+        <v>0.04066538313143833</v>
       </c>
       <c r="W95">
-        <v>0.2261079962345704</v>
+        <v>0.2262111026576069</v>
       </c>
       <c r="X95" t="inlineStr">
         <is>
@@ -9103,7 +9103,7 @@
         </is>
       </c>
       <c r="Y95">
-        <v>0.2055132265782367</v>
+        <v>0.2033269156571916</v>
       </c>
       <c r="Z95">
         <v>0</v>
@@ -9111,22 +9111,22 @@
     </row>
     <row r="96">
       <c r="A96">
-        <v>0.9400000000000001</v>
+        <v>0.9500000000000001</v>
       </c>
       <c r="B96">
-        <v>0.2487723221667865</v>
+        <v>0.2506723221667865</v>
       </c>
       <c r="C96">
-        <v>-160.3027423585653</v>
+        <v>-162.7408097497914</v>
       </c>
       <c r="D96">
-        <v>35.52565764143471</v>
+        <v>35.1961902502086</v>
       </c>
       <c r="E96">
-        <v>191.1484</v>
+        <v>193.257</v>
       </c>
       <c r="F96">
-        <v>198.2084</v>
+        <v>200.317</v>
       </c>
       <c r="G96">
         <v>2.38</v>
@@ -9147,37 +9147,37 @@
         <v>9.503</v>
       </c>
       <c r="M96">
-        <v>46.73754072000001</v>
+        <v>47.23474860000001</v>
       </c>
       <c r="N96">
-        <v>-37.23454072000001</v>
+        <v>-37.73174860000001</v>
       </c>
       <c r="O96">
-        <v>-7.446908144000002</v>
+        <v>-7.546349720000002</v>
       </c>
       <c r="P96">
-        <v>-29.787632576</v>
+        <v>-30.18539888000001</v>
       </c>
       <c r="Q96">
-        <v>-29.430632576</v>
+        <v>-29.82839888000001</v>
       </c>
       <c r="R96">
-        <v>15.66666666666668</v>
+        <v>19.00000000000003</v>
       </c>
       <c r="S96">
-        <v>0.602231427810602</v>
+        <v>0.7135177133727226</v>
       </c>
       <c r="T96">
-        <v>10.84588421330058</v>
+        <v>13.0150610559607</v>
       </c>
       <c r="U96">
         <v>0.2358</v>
       </c>
       <c r="V96">
-        <v>0.04066538313143833</v>
+        <v>0.04023732646689687</v>
       </c>
       <c r="W96">
-        <v>0.2262111026576069</v>
+        <v>0.2263120384191057</v>
       </c>
       <c r="X96" t="inlineStr">
         <is>
@@ -9185,7 +9185,7 @@
         </is>
       </c>
       <c r="Y96">
-        <v>0.2033269156571916</v>
+        <v>0.2011866323344843</v>
       </c>
       <c r="Z96">
         <v>0</v>
@@ -9193,22 +9193,22 @@
     </row>
     <row r="97">
       <c r="A97">
-        <v>0.9500000000000001</v>
+        <v>0.9600000000000001</v>
       </c>
       <c r="B97">
-        <v>0.2506723221667865</v>
+        <v>0.2525723221667865</v>
       </c>
       <c r="C97">
-        <v>-162.7408097497914</v>
+        <v>-165.1728222876719</v>
       </c>
       <c r="D97">
-        <v>35.1961902502086</v>
+        <v>34.87277771232813</v>
       </c>
       <c r="E97">
-        <v>193.257</v>
+        <v>195.3656</v>
       </c>
       <c r="F97">
-        <v>200.317</v>
+        <v>202.4256</v>
       </c>
       <c r="G97">
         <v>2.38</v>
@@ -9229,37 +9229,37 @@
         <v>9.503</v>
       </c>
       <c r="M97">
-        <v>47.23474860000001</v>
+        <v>47.73195648000001</v>
       </c>
       <c r="N97">
-        <v>-37.73174860000001</v>
+        <v>-38.22895648000001</v>
       </c>
       <c r="O97">
-        <v>-7.546349720000002</v>
+        <v>-7.645791296000002</v>
       </c>
       <c r="P97">
-        <v>-30.18539888000001</v>
+        <v>-30.58316518400001</v>
       </c>
       <c r="Q97">
-        <v>-29.82839888000001</v>
+        <v>-30.22616518400001</v>
       </c>
       <c r="R97">
-        <v>19.00000000000003</v>
+        <v>24.00000000000005</v>
       </c>
       <c r="S97">
-        <v>0.7135177133727226</v>
+        <v>0.8804471417159038</v>
       </c>
       <c r="T97">
-        <v>13.0150610559607</v>
+        <v>16.26882631995088</v>
       </c>
       <c r="U97">
         <v>0.2358</v>
       </c>
       <c r="V97">
-        <v>0.04023732646689687</v>
+        <v>0.03981818764953336</v>
       </c>
       <c r="W97">
-        <v>0.2263120384191057</v>
+        <v>0.22641087135224</v>
       </c>
       <c r="X97" t="inlineStr">
         <is>
@@ -9267,7 +9267,7 @@
         </is>
       </c>
       <c r="Y97">
-        <v>0.2011866323344843</v>
+        <v>0.1990909382476668</v>
       </c>
       <c r="Z97">
         <v>0</v>
@@ -9275,22 +9275,22 @@
     </row>
     <row r="98">
       <c r="A98">
-        <v>0.96</v>
+        <v>0.97</v>
       </c>
       <c r="B98">
-        <v>0.2525723221667865</v>
+        <v>0.2544723221667866</v>
       </c>
       <c r="C98">
-        <v>-165.1728222876719</v>
+        <v>-167.5989453638778</v>
       </c>
       <c r="D98">
-        <v>34.87277771232815</v>
+        <v>34.55525463612225</v>
       </c>
       <c r="E98">
-        <v>195.3656</v>
+        <v>197.4742</v>
       </c>
       <c r="F98">
-        <v>202.4256</v>
+        <v>204.5342</v>
       </c>
       <c r="G98">
         <v>2.38</v>
@@ -9311,37 +9311,37 @@
         <v>9.503</v>
       </c>
       <c r="M98">
-        <v>47.73195648</v>
+        <v>48.22916436</v>
       </c>
       <c r="N98">
-        <v>-38.22895648</v>
+        <v>-38.72616436</v>
       </c>
       <c r="O98">
-        <v>-7.645791296000001</v>
+        <v>-7.745232872</v>
       </c>
       <c r="P98">
-        <v>-30.583165184</v>
+        <v>-30.980931488</v>
       </c>
       <c r="Q98">
-        <v>-30.226165184</v>
+        <v>-30.623931488</v>
       </c>
       <c r="R98">
-        <v>23.99999999999998</v>
+        <v>32.33333333333331</v>
       </c>
       <c r="S98">
-        <v>0.8804471417159015</v>
+        <v>1.158662855621202</v>
       </c>
       <c r="T98">
-        <v>16.26882631995084</v>
+        <v>21.69176842660112</v>
       </c>
       <c r="U98">
         <v>0.2358</v>
       </c>
       <c r="V98">
-        <v>0.03981818764953337</v>
+        <v>0.03940769086964127</v>
       </c>
       <c r="W98">
-        <v>0.22641087135224</v>
+        <v>0.2265076664929386</v>
       </c>
       <c r="X98" t="inlineStr">
         <is>
@@ -9349,7 +9349,7 @@
         </is>
       </c>
       <c r="Y98">
-        <v>0.1990909382476668</v>
+        <v>0.1970384543482063</v>
       </c>
       <c r="Z98">
         <v>0</v>
@@ -9357,22 +9357,22 @@
     </row>
     <row r="99">
       <c r="A99">
-        <v>0.97</v>
+        <v>0.98</v>
       </c>
       <c r="B99">
-        <v>0.2544723221667866</v>
+        <v>0.2563723221667865</v>
       </c>
       <c r="C99">
-        <v>-167.5989453638778</v>
+        <v>-170.0193384007453</v>
       </c>
       <c r="D99">
-        <v>34.55525463612225</v>
+        <v>34.24346159925471</v>
       </c>
       <c r="E99">
-        <v>197.4742</v>
+        <v>199.5828</v>
       </c>
       <c r="F99">
-        <v>204.5342</v>
+        <v>206.6428</v>
       </c>
       <c r="G99">
         <v>2.38</v>
@@ -9393,37 +9393,37 @@
         <v>9.503</v>
       </c>
       <c r="M99">
-        <v>48.22916436</v>
+        <v>48.72637224000001</v>
       </c>
       <c r="N99">
-        <v>-38.72616436</v>
+        <v>-39.22337224000001</v>
       </c>
       <c r="O99">
-        <v>-7.745232872</v>
+        <v>-7.844674448000003</v>
       </c>
       <c r="P99">
-        <v>-30.980931488</v>
+        <v>-31.37869779200001</v>
       </c>
       <c r="Q99">
-        <v>-30.623931488</v>
+        <v>-31.02169779200001</v>
       </c>
       <c r="R99">
-        <v>32.33333333333331</v>
+        <v>48.99999999999996</v>
       </c>
       <c r="S99">
-        <v>1.158662855621202</v>
+        <v>1.715094283431803</v>
       </c>
       <c r="T99">
-        <v>21.69176842660112</v>
+        <v>32.53765263990168</v>
       </c>
       <c r="U99">
         <v>0.2358</v>
       </c>
       <c r="V99">
-        <v>0.03940769086964127</v>
+        <v>0.03900557157505308</v>
       </c>
       <c r="W99">
-        <v>0.2265076664929386</v>
+        <v>0.2266024862226025</v>
       </c>
       <c r="X99" t="inlineStr">
         <is>
@@ -9431,7 +9431,7 @@
         </is>
       </c>
       <c r="Y99">
-        <v>0.1970384543482063</v>
+        <v>0.1950278578752654</v>
       </c>
       <c r="Z99">
         <v>0</v>
@@ -9439,22 +9439,22 @@
     </row>
     <row r="100">
       <c r="A100">
-        <v>0.98</v>
+        <v>0.99</v>
       </c>
       <c r="B100">
-        <v>0.2563723221667865</v>
+        <v>0.2582723221667865</v>
       </c>
       <c r="C100">
-        <v>-170.0193384007453</v>
+        <v>-172.434155118175</v>
       </c>
       <c r="D100">
-        <v>34.24346159925471</v>
+        <v>33.93724488182499</v>
       </c>
       <c r="E100">
-        <v>199.5828</v>
+        <v>201.6914</v>
       </c>
       <c r="F100">
-        <v>206.6428</v>
+        <v>208.7514</v>
       </c>
       <c r="G100">
         <v>2.38</v>
@@ -9475,37 +9475,37 @@
         <v>9.503</v>
       </c>
       <c r="M100">
-        <v>48.72637224000001</v>
+        <v>49.22358012000001</v>
       </c>
       <c r="N100">
-        <v>-39.22337224000001</v>
+        <v>-39.72058012000001</v>
       </c>
       <c r="O100">
-        <v>-7.844674448000003</v>
+        <v>-7.944116024000002</v>
       </c>
       <c r="P100">
-        <v>-31.37869779200001</v>
+        <v>-31.77646409600001</v>
       </c>
       <c r="Q100">
-        <v>-31.02169779200001</v>
+        <v>-31.41946409600001</v>
       </c>
       <c r="R100">
-        <v>48.99999999999996</v>
+        <v>98.99999999999991</v>
       </c>
       <c r="S100">
-        <v>1.715094283431803</v>
+        <v>3.384388566863606</v>
       </c>
       <c r="T100">
-        <v>32.53765263990168</v>
+        <v>65.07530527980336</v>
       </c>
       <c r="U100">
         <v>0.2358</v>
       </c>
       <c r="V100">
-        <v>0.03900557157505308</v>
+        <v>0.0386115759025778</v>
       </c>
       <c r="W100">
-        <v>0.2266024862226025</v>
+        <v>0.2266953904021722</v>
       </c>
       <c r="X100" t="inlineStr">
         <is>
@@ -9513,91 +9513,9 @@
         </is>
       </c>
       <c r="Y100">
-        <v>0.1950278578752654</v>
+        <v>0.193057879512889</v>
       </c>
       <c r="Z100">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="101">
-      <c r="A101">
-        <v>0.99</v>
-      </c>
-      <c r="B101">
-        <v>0.2582723221667865</v>
-      </c>
-      <c r="C101">
-        <v>-172.434155118175</v>
-      </c>
-      <c r="D101">
-        <v>33.93724488182499</v>
-      </c>
-      <c r="E101">
-        <v>201.6914</v>
-      </c>
-      <c r="F101">
-        <v>208.7514</v>
-      </c>
-      <c r="G101">
-        <v>2.38</v>
-      </c>
-      <c r="H101">
-        <v>203.8</v>
-      </c>
-      <c r="I101">
-        <v>0</v>
-      </c>
-      <c r="J101">
-        <v>9.859999999999999</v>
-      </c>
-      <c r="K101">
-        <v>0.357</v>
-      </c>
-      <c r="L101">
-        <v>9.503</v>
-      </c>
-      <c r="M101">
-        <v>49.22358012000001</v>
-      </c>
-      <c r="N101">
-        <v>-39.72058012000001</v>
-      </c>
-      <c r="O101">
-        <v>-7.944116024000002</v>
-      </c>
-      <c r="P101">
-        <v>-31.77646409600001</v>
-      </c>
-      <c r="Q101">
-        <v>-31.41946409600001</v>
-      </c>
-      <c r="R101">
-        <v>98.99999999999991</v>
-      </c>
-      <c r="S101">
-        <v>3.384388566863606</v>
-      </c>
-      <c r="T101">
-        <v>65.07530527980336</v>
-      </c>
-      <c r="U101">
-        <v>0.2358</v>
-      </c>
-      <c r="V101">
-        <v>0.0386115759025778</v>
-      </c>
-      <c r="W101">
-        <v>0.2266953904021722</v>
-      </c>
-      <c r="X101" t="inlineStr">
-        <is>
-          <t>D2/D</t>
-        </is>
-      </c>
-      <c r="Y101">
-        <v>0.193057879512889</v>
-      </c>
-      <c r="Z101">
         <v>0</v>
       </c>
     </row>
